--- a/statistics_files/2026/2026_99_gb_requests.xlsx
+++ b/statistics_files/2026/2026_99_gb_requests.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73CFE65C-7021-40CC-AB2B-43EBE2AAD09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54905E78-38CC-4C5E-8BEE-081D1D41F27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="843"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="843" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="October" sheetId="10" r:id="rId10"/>
     <sheet name="November" sheetId="11" r:id="rId11"/>
     <sheet name="December" sheetId="12" r:id="rId12"/>
-    <sheet name="Yearly totals" sheetId="13" r:id="rId13"/>
+    <sheet name="Yearly total" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">April!$A$1:$J$57</definedName>
@@ -40,10 +40,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">November!$A$1:$J$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">October!$A$1:$J$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">September!$A$1:$J$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Yearly totals'!$A$1:$J$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Yearly total'!$A$1:$J$57</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -258,7 +267,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1326,7 +1335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3187,13 +3196,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4100,13 +4109,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5013,13 +5022,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5926,13 +5935,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8270,13 +8279,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-00000C000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9183,13 +9192,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10096,13 +10105,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11009,13 +11018,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11922,13 +11931,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12835,13 +12844,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13748,13 +13757,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14661,13 +14670,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15574,7 +15583,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J57" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/statistics_files/2026/2026_99_gb_requests.xlsx
+++ b/statistics_files/2026/2026_99_gb_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54905E78-38CC-4C5E-8BEE-081D1D41F27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB166A45-A7A3-423B-A9A2-8CF4ACAA1D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="843" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5988,39 +5988,39 @@
       </c>
       <c r="B2" s="4">
         <f>SUM(January:December!B2)</f>
-        <v>2760</v>
+        <v>5710</v>
       </c>
       <c r="C2" s="4">
         <f>SUM(January:December!C2)</f>
-        <v>1272</v>
+        <v>2496</v>
       </c>
       <c r="D2" s="4">
         <f>SUM(January:December!D2)</f>
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="E2" s="4">
         <f>SUM(January:December!E2)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4">
         <f>SUM(January:December!F2)</f>
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="G2" s="4">
         <f>SUM(January:December!G2)</f>
-        <v>169</v>
+        <v>330</v>
       </c>
       <c r="H2" s="4">
         <f>SUM(January:December!H2)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2" s="4">
         <f>SUM(January:December!I2)</f>
-        <v>404</v>
+        <v>874</v>
       </c>
       <c r="J2" s="5">
         <f>SUM(January:December!J2)</f>
-        <v>2356</v>
+        <v>4836</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6029,39 +6029,39 @@
       </c>
       <c r="B3" s="7">
         <f>SUM(January:December!B3)</f>
-        <v>1320</v>
+        <v>2446</v>
       </c>
       <c r="C3" s="7">
         <f>SUM(January:December!C3)</f>
-        <v>539</v>
+        <v>1129</v>
       </c>
       <c r="D3" s="7">
         <f>SUM(January:December!D3)</f>
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="E3" s="7">
         <f>SUM(January:December!E3)</f>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F3" s="7">
         <f>SUM(January:December!F3)</f>
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="G3" s="7">
         <f>SUM(January:December!G3)</f>
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="H3" s="7">
         <f>SUM(January:December!H3)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" s="7">
         <f>SUM(January:December!I3)</f>
-        <v>178</v>
+        <v>356</v>
       </c>
       <c r="J3" s="8">
         <f>SUM(January:December!J3)</f>
-        <v>1142</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B4" s="10">
         <f>SUM(January:December!B4)</f>
-        <v>3182</v>
+        <v>5668</v>
       </c>
       <c r="C4" s="10">
         <f>SUM(January:December!C4)</f>
-        <v>1318</v>
+        <v>2414</v>
       </c>
       <c r="D4" s="10">
         <f>SUM(January:December!D4)</f>
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="E4" s="10">
         <f>SUM(January:December!E4)</f>
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F4" s="10">
         <f>SUM(January:December!F4)</f>
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="G4" s="10">
         <f>SUM(January:December!G4)</f>
-        <v>249</v>
+        <v>478</v>
       </c>
       <c r="H4" s="10">
         <f>SUM(January:December!H4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="10">
         <f>SUM(January:December!I4)</f>
-        <v>530</v>
+        <v>862</v>
       </c>
       <c r="J4" s="11">
         <f>SUM(January:December!J4)</f>
-        <v>2652</v>
+        <v>4806</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6111,15 +6111,15 @@
       </c>
       <c r="B5" s="7">
         <f>SUM(January:December!B5)</f>
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C5" s="7">
         <f>SUM(January:December!C5)</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D5" s="7">
         <f>SUM(January:December!D5)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="7">
         <f>SUM(January:December!E5)</f>
@@ -6127,11 +6127,11 @@
       </c>
       <c r="F5" s="7">
         <f>SUM(January:December!F5)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="7">
         <f>SUM(January:December!G5)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" s="7">
         <f>SUM(January:December!H5)</f>
@@ -6139,11 +6139,11 @@
       </c>
       <c r="I5" s="7">
         <f>SUM(January:December!I5)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" s="8">
         <f>SUM(January:December!J5)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -6152,39 +6152,39 @@
       </c>
       <c r="B6" s="10">
         <f>SUM(January:December!B6)</f>
-        <v>3254</v>
+        <v>6120</v>
       </c>
       <c r="C6" s="10">
         <f>SUM(January:December!C6)</f>
-        <v>1313</v>
+        <v>2465</v>
       </c>
       <c r="D6" s="10">
         <f>SUM(January:December!D6)</f>
-        <v>247</v>
+        <v>530</v>
       </c>
       <c r="E6" s="10">
         <f>SUM(January:December!E6)</f>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F6" s="10">
         <f>SUM(January:December!F6)</f>
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="G6" s="10">
         <f>SUM(January:December!G6)</f>
-        <v>321</v>
+        <v>674</v>
       </c>
       <c r="H6" s="10">
         <f>SUM(January:December!H6)</f>
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I6" s="10">
         <f>SUM(January:December!I6)</f>
-        <v>910</v>
+        <v>1722</v>
       </c>
       <c r="J6" s="11">
         <f>SUM(January:December!J6)</f>
-        <v>2344</v>
+        <v>4398</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -6193,15 +6193,15 @@
       </c>
       <c r="B7" s="7">
         <f>SUM(January:December!B7)</f>
-        <v>326</v>
+        <v>516</v>
       </c>
       <c r="C7" s="7">
         <f>SUM(January:December!C7)</f>
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="D7" s="7">
         <f>SUM(January:December!D7)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(January:December!E7)</f>
@@ -6209,23 +6209,23 @@
       </c>
       <c r="F7" s="7">
         <f>SUM(January:December!F7)</f>
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G7" s="7">
         <f>SUM(January:December!G7)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H7" s="7">
         <f>SUM(January:December!H7)</f>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I7" s="7">
         <f>SUM(January:December!I7)</f>
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="J7" s="8">
         <f>SUM(January:December!J7)</f>
-        <v>260</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -6234,15 +6234,15 @@
       </c>
       <c r="B8" s="10">
         <f>SUM(January:December!B8)</f>
-        <v>206</v>
+        <v>516</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(January:December!C8)</f>
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="D8" s="10">
         <f>SUM(January:December!D8)</f>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E8" s="10">
         <f>SUM(January:December!E8)</f>
@@ -6250,11 +6250,11 @@
       </c>
       <c r="F8" s="10">
         <f>SUM(January:December!F8)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" s="10">
         <f>SUM(January:December!G8)</f>
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H8" s="10">
         <f>SUM(January:December!H8)</f>
@@ -6262,11 +6262,11 @@
       </c>
       <c r="I8" s="10">
         <f>SUM(January:December!I8)</f>
-        <v>94</v>
+        <v>200</v>
       </c>
       <c r="J8" s="11">
         <f>SUM(January:December!J8)</f>
-        <v>112</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -6275,11 +6275,11 @@
       </c>
       <c r="B9" s="7">
         <f>SUM(January:December!B9)</f>
-        <v>120</v>
+        <v>196</v>
       </c>
       <c r="C9" s="7">
         <f>SUM(January:December!C9)</f>
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="D9" s="7">
         <f>SUM(January:December!D9)</f>
@@ -6291,11 +6291,11 @@
       </c>
       <c r="F9" s="7">
         <f>SUM(January:December!F9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="7">
         <f>SUM(January:December!G9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="7">
         <f>SUM(January:December!H9)</f>
@@ -6303,11 +6303,11 @@
       </c>
       <c r="I9" s="7">
         <f>SUM(January:December!I9)</f>
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J9" s="8">
         <f>SUM(January:December!J9)</f>
-        <v>102</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C10" s="10">
         <f>SUM(January:December!C10)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="10">
         <f>SUM(January:December!D10)</f>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D11" s="7">
         <f>SUM(January:December!D11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7">
         <f>SUM(January:December!E11)</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="G11" s="7">
         <f>SUM(January:December!G11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="7">
         <f>SUM(January:December!H11)</f>
@@ -6402,11 +6402,11 @@
       </c>
       <c r="C12" s="13">
         <f>SUM(January:December!C12)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" s="13">
         <f>SUM(January:December!D12)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="13">
         <f>SUM(January:December!E12)</f>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="G12" s="13">
         <f>SUM(January:December!G12)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="13">
         <f>SUM(January:December!H12)</f>
@@ -6439,15 +6439,15 @@
       </c>
       <c r="B13" s="16">
         <f>SUM(January:December!B13)</f>
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="C13" s="16">
         <f>SUM(January:December!C13)</f>
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D13" s="16">
         <f>SUM(January:December!D13)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="16">
         <f>SUM(January:December!E13)</f>
@@ -6455,11 +6455,11 @@
       </c>
       <c r="F13" s="16">
         <f>SUM(January:December!F13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" s="16">
         <f>SUM(January:December!G13)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" s="16">
         <f>SUM(January:December!H13)</f>
@@ -6467,11 +6467,11 @@
       </c>
       <c r="I13" s="16">
         <f>SUM(January:December!I13)</f>
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="J13" s="17">
         <f>SUM(January:December!J13)</f>
-        <v>70</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -6480,15 +6480,15 @@
       </c>
       <c r="B14" s="13">
         <f>SUM(January:December!B14)</f>
-        <v>544</v>
+        <v>880</v>
       </c>
       <c r="C14" s="13">
         <f>SUM(January:December!C14)</f>
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="D14" s="13">
         <f>SUM(January:December!D14)</f>
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E14" s="13">
         <f>SUM(January:December!E14)</f>
@@ -6496,11 +6496,11 @@
       </c>
       <c r="F14" s="13">
         <f>SUM(January:December!F14)</f>
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G14" s="13">
         <f>SUM(January:December!G14)</f>
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="H14" s="13">
         <f>SUM(January:December!H14)</f>
@@ -6508,11 +6508,11 @@
       </c>
       <c r="I14" s="13">
         <f>SUM(January:December!I14)</f>
-        <v>266</v>
+        <v>426</v>
       </c>
       <c r="J14" s="14">
         <f>SUM(January:December!J14)</f>
-        <v>278</v>
+        <v>454</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -6521,15 +6521,15 @@
       </c>
       <c r="B15" s="16">
         <f>SUM(January:December!B15)</f>
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="C15" s="16">
         <f>SUM(January:December!C15)</f>
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="D15" s="16">
         <f>SUM(January:December!D15)</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E15" s="16">
         <f>SUM(January:December!E15)</f>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="G15" s="16">
         <f>SUM(January:December!G15)</f>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H15" s="16">
         <f>SUM(January:December!H15)</f>
@@ -6549,11 +6549,11 @@
       </c>
       <c r="I15" s="16">
         <f>SUM(January:December!I15)</f>
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="J15" s="17">
         <f>SUM(January:December!J15)</f>
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -6562,15 +6562,15 @@
       </c>
       <c r="B16" s="10">
         <f>SUM(January:December!B16)</f>
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="C16" s="10">
         <f>SUM(January:December!C16)</f>
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="D16" s="10">
         <f>SUM(January:December!D16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="10">
         <f>SUM(January:December!E16)</f>
@@ -6578,11 +6578,11 @@
       </c>
       <c r="F16" s="10">
         <f>SUM(January:December!F16)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G16" s="10">
         <f>SUM(January:December!G16)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H16" s="10">
         <f>SUM(January:December!H16)</f>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="I16" s="10">
         <f>SUM(January:December!I16)</f>
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="J16" s="11">
         <f>SUM(January:December!J16)</f>
-        <v>56</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -6603,27 +6603,27 @@
       </c>
       <c r="B17" s="7">
         <f>SUM(January:December!B17)</f>
-        <v>1322</v>
+        <v>2534</v>
       </c>
       <c r="C17" s="7">
         <f>SUM(January:December!C17)</f>
-        <v>597</v>
+        <v>1103</v>
       </c>
       <c r="D17" s="7">
         <f>SUM(January:December!D17)</f>
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="E17" s="7">
         <f>SUM(January:December!E17)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F17" s="7">
         <f>SUM(January:December!F17)</f>
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="G17" s="7">
         <f>SUM(January:December!G17)</f>
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="H17" s="7">
         <f>SUM(January:December!H17)</f>
@@ -6631,11 +6631,11 @@
       </c>
       <c r="I17" s="7">
         <f>SUM(January:December!I17)</f>
-        <v>366</v>
+        <v>720</v>
       </c>
       <c r="J17" s="8">
         <f>SUM(January:December!J17)</f>
-        <v>956</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -6644,19 +6644,19 @@
       </c>
       <c r="B18" s="10">
         <f>SUM(January:December!B18)</f>
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="C18" s="10">
         <f>SUM(January:December!C18)</f>
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="D18" s="10">
         <f>SUM(January:December!D18)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="10">
         <f>SUM(January:December!E18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="10">
         <f>SUM(January:December!F18)</f>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="G18" s="10">
         <f>SUM(January:December!G18)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(January:December!H18)</f>
@@ -6672,11 +6672,11 @@
       </c>
       <c r="I18" s="10">
         <f>SUM(January:December!I18)</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J18" s="11">
         <f>SUM(January:December!J18)</f>
-        <v>48</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -6685,15 +6685,15 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(January:December!B19)</f>
-        <v>1140</v>
+        <v>2396</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(January:December!C19)</f>
-        <v>415</v>
+        <v>1006</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(January:December!D19)</f>
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(January:December!E19)</f>
@@ -6701,11 +6701,11 @@
       </c>
       <c r="F19" s="7">
         <f>SUM(January:December!F19)</f>
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G19" s="7">
         <f>SUM(January:December!G19)</f>
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="H19" s="7">
         <f>SUM(January:December!H19)</f>
@@ -6713,11 +6713,11 @@
       </c>
       <c r="I19" s="7">
         <f>SUM(January:December!I19)</f>
-        <v>302</v>
+        <v>560</v>
       </c>
       <c r="J19" s="8">
         <f>SUM(January:December!J19)</f>
-        <v>838</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6726,15 +6726,15 @@
       </c>
       <c r="B20" s="10">
         <f>SUM(January:December!B20)</f>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C20" s="10">
         <f>SUM(January:December!C20)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="10">
         <f>SUM(January:December!D20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="10">
         <f>SUM(January:December!E20)</f>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="G20" s="10">
         <f>SUM(January:December!G20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="10">
         <f>SUM(January:December!H20)</f>
@@ -6754,11 +6754,11 @@
       </c>
       <c r="I20" s="10">
         <f>SUM(January:December!I20)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J20" s="11">
         <f>SUM(January:December!J20)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -6767,27 +6767,27 @@
       </c>
       <c r="B21" s="7">
         <f>SUM(January:December!B21)</f>
-        <v>966</v>
+        <v>1846</v>
       </c>
       <c r="C21" s="7">
         <f>SUM(January:December!C21)</f>
-        <v>442</v>
+        <v>852</v>
       </c>
       <c r="D21" s="7">
         <f>SUM(January:December!D21)</f>
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(January:December!E21)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="7">
         <f>SUM(January:December!F21)</f>
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="G21" s="7">
         <f>SUM(January:December!G21)</f>
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="H21" s="7">
         <f>SUM(January:December!H21)</f>
@@ -6795,11 +6795,11 @@
       </c>
       <c r="I21" s="7">
         <f>SUM(January:December!I21)</f>
-        <v>192</v>
+        <v>406</v>
       </c>
       <c r="J21" s="8">
         <f>SUM(January:December!J21)</f>
-        <v>774</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -6808,15 +6808,15 @@
       </c>
       <c r="B22" s="10">
         <f>SUM(January:December!B22)</f>
-        <v>86</v>
+        <v>246</v>
       </c>
       <c r="C22" s="10">
         <f>SUM(January:December!C22)</f>
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="D22" s="10">
         <f>SUM(January:December!D22)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E22" s="10">
         <f>SUM(January:December!E22)</f>
@@ -6824,11 +6824,11 @@
       </c>
       <c r="F22" s="10">
         <f>SUM(January:December!F22)</f>
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G22" s="10">
         <f>SUM(January:December!G22)</f>
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H22" s="10">
         <f>SUM(January:December!H22)</f>
@@ -6836,11 +6836,11 @@
       </c>
       <c r="I22" s="10">
         <f>SUM(January:December!I22)</f>
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="J22" s="11">
         <f>SUM(January:December!J22)</f>
-        <v>64</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -6849,39 +6849,39 @@
       </c>
       <c r="B23" s="7">
         <f>SUM(January:December!B23)</f>
-        <v>1382</v>
+        <v>2560</v>
       </c>
       <c r="C23" s="7">
         <f>SUM(January:December!C23)</f>
-        <v>487</v>
+        <v>892</v>
       </c>
       <c r="D23" s="7">
         <f>SUM(January:December!D23)</f>
-        <v>93</v>
+        <v>238</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(January:December!E23)</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F23" s="7">
         <f>SUM(January:December!F23)</f>
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="G23" s="7">
         <f>SUM(January:December!G23)</f>
-        <v>141</v>
+        <v>328</v>
       </c>
       <c r="H23" s="7">
         <f>SUM(January:December!H23)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I23" s="7">
         <f>SUM(January:December!I23)</f>
-        <v>230</v>
+        <v>516</v>
       </c>
       <c r="J23" s="8">
         <f>SUM(January:December!J23)</f>
-        <v>1152</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -6890,39 +6890,39 @@
       </c>
       <c r="B24" s="10">
         <f>SUM(January:December!B24)</f>
-        <v>4004</v>
+        <v>7630</v>
       </c>
       <c r="C24" s="10">
         <f>SUM(January:December!C24)</f>
-        <v>1782</v>
+        <v>3425</v>
       </c>
       <c r="D24" s="10">
         <f>SUM(January:December!D24)</f>
-        <v>161</v>
+        <v>314</v>
       </c>
       <c r="E24" s="10">
         <f>SUM(January:December!E24)</f>
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F24" s="10">
         <f>SUM(January:December!F24)</f>
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="G24" s="10">
         <f>SUM(January:December!G24)</f>
-        <v>254</v>
+        <v>509</v>
       </c>
       <c r="H24" s="10">
         <f>SUM(January:December!H24)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" s="10">
         <f>SUM(January:December!I24)</f>
-        <v>488</v>
+        <v>926</v>
       </c>
       <c r="J24" s="11">
         <f>SUM(January:December!J24)</f>
-        <v>3516</v>
+        <v>6704</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -6931,15 +6931,15 @@
       </c>
       <c r="B25" s="7">
         <f>SUM(January:December!B25)</f>
-        <v>320</v>
+        <v>572</v>
       </c>
       <c r="C25" s="7">
         <f>SUM(January:December!C25)</f>
-        <v>139</v>
+        <v>265</v>
       </c>
       <c r="D25" s="7">
         <f>SUM(January:December!D25)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(January:December!E25)</f>
@@ -6947,11 +6947,11 @@
       </c>
       <c r="F25" s="7">
         <f>SUM(January:December!F25)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G25" s="7">
         <f>SUM(January:December!G25)</f>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H25" s="7">
         <f>SUM(January:December!H25)</f>
@@ -6959,11 +6959,11 @@
       </c>
       <c r="I25" s="7">
         <f>SUM(January:December!I25)</f>
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="J25" s="8">
         <f>SUM(January:December!J25)</f>
-        <v>272</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -7013,27 +7013,27 @@
       </c>
       <c r="B27" s="7">
         <f>SUM(January:December!B27)</f>
-        <v>334</v>
+        <v>594</v>
       </c>
       <c r="C27" s="7">
         <f>SUM(January:December!C27)</f>
-        <v>163</v>
+        <v>290</v>
       </c>
       <c r="D27" s="7">
         <f>SUM(January:December!D27)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(January:December!E27)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="7">
         <f>SUM(January:December!F27)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G27" s="7">
         <f>SUM(January:December!G27)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H27" s="7">
         <f>SUM(January:December!H27)</f>
@@ -7041,11 +7041,11 @@
       </c>
       <c r="I27" s="7">
         <f>SUM(January:December!I27)</f>
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="J27" s="8">
         <f>SUM(January:December!J27)</f>
-        <v>224</v>
+        <v>394</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -7054,15 +7054,15 @@
       </c>
       <c r="B28" s="10">
         <f>SUM(January:December!B28)</f>
-        <v>244</v>
+        <v>458</v>
       </c>
       <c r="C28" s="10">
         <f>SUM(January:December!C28)</f>
-        <v>98</v>
+        <v>191</v>
       </c>
       <c r="D28" s="10">
         <f>SUM(January:December!D28)</f>
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E28" s="10">
         <f>SUM(January:December!E28)</f>
@@ -7070,11 +7070,11 @@
       </c>
       <c r="F28" s="10">
         <f>SUM(January:December!F28)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G28" s="10">
         <f>SUM(January:December!G28)</f>
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H28" s="10">
         <f>SUM(January:December!H28)</f>
@@ -7082,11 +7082,11 @@
       </c>
       <c r="I28" s="10">
         <f>SUM(January:December!I28)</f>
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="J28" s="11">
         <f>SUM(January:December!J28)</f>
-        <v>206</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -7095,27 +7095,27 @@
       </c>
       <c r="B29" s="7">
         <f>SUM(January:December!B29)</f>
-        <v>1718</v>
+        <v>2904</v>
       </c>
       <c r="C29" s="7">
         <f>SUM(January:December!C29)</f>
-        <v>787</v>
+        <v>1370</v>
       </c>
       <c r="D29" s="7">
         <f>SUM(January:December!D29)</f>
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(January:December!E29)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" s="7">
         <f>SUM(January:December!F29)</f>
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="G29" s="7">
         <f>SUM(January:December!G29)</f>
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="H29" s="7">
         <f>SUM(January:December!H29)</f>
@@ -7123,11 +7123,11 @@
       </c>
       <c r="I29" s="7">
         <f>SUM(January:December!I29)</f>
-        <v>424</v>
+        <v>776</v>
       </c>
       <c r="J29" s="8">
         <f>SUM(January:December!J29)</f>
-        <v>1294</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -7136,11 +7136,11 @@
       </c>
       <c r="B30" s="10">
         <f>SUM(January:December!B30)</f>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C30" s="10">
         <f>SUM(January:December!C30)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D30" s="10">
         <f>SUM(January:December!D30)</f>
@@ -7152,23 +7152,23 @@
       </c>
       <c r="F30" s="10">
         <f>SUM(January:December!F30)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G30" s="10">
         <f>SUM(January:December!G30)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H30" s="10">
         <f>SUM(January:December!H30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="10">
         <f>SUM(January:December!I30)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J30" s="11">
         <f>SUM(January:December!J30)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -7177,15 +7177,15 @@
       </c>
       <c r="B31" s="7">
         <f>SUM(January:December!B31)</f>
-        <v>238</v>
+        <v>548</v>
       </c>
       <c r="C31" s="7">
         <f>SUM(January:December!C31)</f>
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="D31" s="7">
         <f>SUM(January:December!D31)</f>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(January:December!E31)</f>
@@ -7193,23 +7193,23 @@
       </c>
       <c r="F31" s="7">
         <f>SUM(January:December!F31)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G31" s="7">
         <f>SUM(January:December!G31)</f>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H31" s="7">
         <f>SUM(January:December!H31)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I31" s="7">
         <f>SUM(January:December!I31)</f>
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J31" s="8">
         <f>SUM(January:December!J31)</f>
-        <v>222</v>
+        <v>518</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -7218,39 +7218,39 @@
       </c>
       <c r="B32" s="10">
         <f>SUM(January:December!B32)</f>
-        <v>1032</v>
+        <v>2114</v>
       </c>
       <c r="C32" s="10">
         <f>SUM(January:December!C32)</f>
-        <v>384</v>
+        <v>744</v>
       </c>
       <c r="D32" s="10">
         <f>SUM(January:December!D32)</f>
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="E32" s="10">
         <f>SUM(January:December!E32)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" s="10">
         <f>SUM(January:December!F32)</f>
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="G32" s="10">
         <f>SUM(January:December!G32)</f>
-        <v>146</v>
+        <v>269</v>
       </c>
       <c r="H32" s="10">
         <f>SUM(January:December!H32)</f>
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I32" s="10">
         <f>SUM(January:December!I32)</f>
-        <v>382</v>
+        <v>802</v>
       </c>
       <c r="J32" s="11">
         <f>SUM(January:December!J32)</f>
-        <v>650</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -7259,39 +7259,39 @@
       </c>
       <c r="B33" s="7">
         <f>SUM(January:December!B33)</f>
-        <v>876</v>
+        <v>1774</v>
       </c>
       <c r="C33" s="7">
         <f>SUM(January:December!C33)</f>
-        <v>369</v>
+        <v>750</v>
       </c>
       <c r="D33" s="7">
         <f>SUM(January:December!D33)</f>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(January:December!E33)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F33" s="7">
         <f>SUM(January:December!F33)</f>
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="G33" s="7">
         <f>SUM(January:December!G33)</f>
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="H33" s="7">
         <f>SUM(January:December!H33)</f>
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I33" s="7">
         <f>SUM(January:December!I33)</f>
-        <v>388</v>
+        <v>732</v>
       </c>
       <c r="J33" s="8">
         <f>SUM(January:December!J33)</f>
-        <v>488</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -7300,27 +7300,27 @@
       </c>
       <c r="B34" s="10">
         <f>SUM(January:December!B34)</f>
-        <v>264</v>
+        <v>582</v>
       </c>
       <c r="C34" s="10">
         <f>SUM(January:December!C34)</f>
-        <v>141</v>
+        <v>276</v>
       </c>
       <c r="D34" s="10">
         <f>SUM(January:December!D34)</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E34" s="10">
         <f>SUM(January:December!E34)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="10">
         <f>SUM(January:December!F34)</f>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G34" s="10">
         <f>SUM(January:December!G34)</f>
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H34" s="10">
         <f>SUM(January:December!H34)</f>
@@ -7328,11 +7328,11 @@
       </c>
       <c r="I34" s="10">
         <f>SUM(January:December!I34)</f>
-        <v>88</v>
+        <v>218</v>
       </c>
       <c r="J34" s="11">
         <f>SUM(January:December!J34)</f>
-        <v>176</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -7341,39 +7341,39 @@
       </c>
       <c r="B35" s="7">
         <f>SUM(January:December!B35)</f>
-        <v>2456</v>
+        <v>4808</v>
       </c>
       <c r="C35" s="7">
         <f>SUM(January:December!C35)</f>
-        <v>996</v>
+        <v>1959</v>
       </c>
       <c r="D35" s="7">
         <f>SUM(January:December!D35)</f>
-        <v>175</v>
+        <v>346</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(January:December!E35)</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F35" s="7">
         <f>SUM(January:December!F35)</f>
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="G35" s="7">
         <f>SUM(January:December!G35)</f>
-        <v>236</v>
+        <v>455</v>
       </c>
       <c r="H35" s="7">
         <f>SUM(January:December!H35)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I35" s="7">
         <f>SUM(January:December!I35)</f>
-        <v>544</v>
+        <v>1170</v>
       </c>
       <c r="J35" s="8">
         <f>SUM(January:December!J35)</f>
-        <v>1912</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -7382,15 +7382,15 @@
       </c>
       <c r="B36" s="10">
         <f>SUM(January:December!B36)</f>
-        <v>388</v>
+        <v>708</v>
       </c>
       <c r="C36" s="10">
         <f>SUM(January:December!C36)</f>
-        <v>186</v>
+        <v>334</v>
       </c>
       <c r="D36" s="10">
         <f>SUM(January:December!D36)</f>
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E36" s="10">
         <f>SUM(January:December!E36)</f>
@@ -7398,11 +7398,11 @@
       </c>
       <c r="F36" s="10">
         <f>SUM(January:December!F36)</f>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G36" s="10">
         <f>SUM(January:December!G36)</f>
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H36" s="10">
         <f>SUM(January:December!H36)</f>
@@ -7410,11 +7410,11 @@
       </c>
       <c r="I36" s="10">
         <f>SUM(January:December!I36)</f>
-        <v>128</v>
+        <v>264</v>
       </c>
       <c r="J36" s="11">
         <f>SUM(January:December!J36)</f>
-        <v>260</v>
+        <v>444</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -7423,39 +7423,39 @@
       </c>
       <c r="B37" s="7">
         <f>SUM(January:December!B37)</f>
-        <v>1014</v>
+        <v>2114</v>
       </c>
       <c r="C37" s="7">
         <f>SUM(January:December!C37)</f>
-        <v>359</v>
+        <v>763</v>
       </c>
       <c r="D37" s="7">
         <f>SUM(January:December!D37)</f>
-        <v>101</v>
+        <v>188</v>
       </c>
       <c r="E37" s="7">
         <f>SUM(January:December!E37)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F37" s="7">
         <f>SUM(January:December!F37)</f>
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="G37" s="7">
         <f>SUM(January:December!G37)</f>
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H37" s="7">
         <f>SUM(January:December!H37)</f>
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="I37" s="7">
         <f>SUM(January:December!I37)</f>
-        <v>278</v>
+        <v>574</v>
       </c>
       <c r="J37" s="8">
         <f>SUM(January:December!J37)</f>
-        <v>736</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -7464,11 +7464,11 @@
       </c>
       <c r="B38" s="10">
         <f>SUM(January:December!B38)</f>
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="C38" s="10">
         <f>SUM(January:December!C38)</f>
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D38" s="10">
         <f>SUM(January:December!D38)</f>
@@ -7492,11 +7492,11 @@
       </c>
       <c r="I38" s="10">
         <f>SUM(January:December!I38)</f>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J38" s="11">
         <f>SUM(January:December!J38)</f>
-        <v>11</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -7505,27 +7505,27 @@
       </c>
       <c r="B39" s="7">
         <f>SUM(January:December!B39)</f>
-        <v>510</v>
+        <v>1316</v>
       </c>
       <c r="C39" s="7">
         <f>SUM(January:December!C39)</f>
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="D39" s="7">
         <f>SUM(January:December!D39)</f>
-        <v>134</v>
+        <v>467</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(January:December!E39)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F39" s="7">
         <f>SUM(January:December!F39)</f>
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="G39" s="7">
         <f>SUM(January:December!G39)</f>
-        <v>139</v>
+        <v>621</v>
       </c>
       <c r="H39" s="7">
         <f>SUM(January:December!H39)</f>
@@ -7533,11 +7533,11 @@
       </c>
       <c r="I39" s="7">
         <f>SUM(January:December!I39)</f>
-        <v>226</v>
+        <v>700</v>
       </c>
       <c r="J39" s="8">
         <f>SUM(January:December!J39)</f>
-        <v>284</v>
+        <v>616</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -7546,11 +7546,11 @@
       </c>
       <c r="B40" s="19">
         <f>SUM(January:December!B40)</f>
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="C40" s="19">
         <f>SUM(January:December!C40)</f>
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D40" s="19">
         <f>SUM(January:December!D40)</f>
@@ -7574,11 +7574,11 @@
       </c>
       <c r="I40" s="19">
         <f>SUM(January:December!I40)</f>
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J40" s="20">
         <f>SUM(January:December!J40)</f>
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -7587,15 +7587,15 @@
       </c>
       <c r="B41" s="22">
         <f>SUM(January:December!B41)</f>
-        <v>192</v>
+        <v>496</v>
       </c>
       <c r="C41" s="22">
         <f>SUM(January:December!C41)</f>
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="D41" s="22">
         <f>SUM(January:December!D41)</f>
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E41" s="22">
         <f>SUM(January:December!E41)</f>
@@ -7603,11 +7603,11 @@
       </c>
       <c r="F41" s="22">
         <f>SUM(January:December!F41)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="22">
         <f>SUM(January:December!G41)</f>
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H41" s="22">
         <f>SUM(January:December!H41)</f>
@@ -7615,11 +7615,11 @@
       </c>
       <c r="I41" s="22">
         <f>SUM(January:December!I41)</f>
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="J41" s="23">
         <f>SUM(January:December!J41)</f>
-        <v>68</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -7628,11 +7628,11 @@
       </c>
       <c r="B42" s="19">
         <f>SUM(January:December!B42)</f>
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C42" s="19">
         <f>SUM(January:December!C42)</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D42" s="19">
         <f>SUM(January:December!D42)</f>
@@ -7656,11 +7656,11 @@
       </c>
       <c r="I42" s="19">
         <f>SUM(January:December!I42)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J42" s="20">
         <f>SUM(January:December!J42)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -7669,15 +7669,15 @@
       </c>
       <c r="B43" s="22">
         <f>SUM(January:December!B43)</f>
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="C43" s="22">
         <f>SUM(January:December!C43)</f>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D43" s="22">
         <f>SUM(January:December!D43)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E43" s="22">
         <f>SUM(January:December!E43)</f>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="G43" s="22">
         <f>SUM(January:December!G43)</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H43" s="22">
         <f>SUM(January:December!H43)</f>
@@ -7697,11 +7697,11 @@
       </c>
       <c r="I43" s="22">
         <f>SUM(January:December!I43)</f>
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J43" s="23">
         <f>SUM(January:December!J43)</f>
-        <v>12</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -7710,11 +7710,11 @@
       </c>
       <c r="B44" s="7">
         <f>SUM(January:December!B44)</f>
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="C44" s="7">
         <f>SUM(January:December!C44)</f>
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D44" s="7">
         <f>SUM(January:December!D44)</f>
@@ -7738,11 +7738,11 @@
       </c>
       <c r="I44" s="7">
         <f>SUM(January:December!I44)</f>
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="J44" s="8">
         <f>SUM(January:December!J44)</f>
-        <v>46</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -7751,27 +7751,27 @@
       </c>
       <c r="B45" s="10">
         <f>SUM(January:December!B45)</f>
-        <v>1066</v>
+        <v>1832</v>
       </c>
       <c r="C45" s="10">
         <f>SUM(January:December!C45)</f>
-        <v>429</v>
+        <v>856</v>
       </c>
       <c r="D45" s="10">
         <f>SUM(January:December!D45)</f>
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E45" s="10">
         <f>SUM(January:December!E45)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F45" s="10">
         <f>SUM(January:December!F45)</f>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G45" s="10">
         <f>SUM(January:December!G45)</f>
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="H45" s="10">
         <f>SUM(January:December!H45)</f>
@@ -7779,11 +7779,11 @@
       </c>
       <c r="I45" s="10">
         <f>SUM(January:December!I45)</f>
-        <v>264</v>
+        <v>450</v>
       </c>
       <c r="J45" s="11">
         <f>SUM(January:December!J45)</f>
-        <v>802</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -7792,27 +7792,27 @@
       </c>
       <c r="B46" s="7">
         <f>SUM(January:December!B46)</f>
-        <v>1934</v>
+        <v>3424</v>
       </c>
       <c r="C46" s="7">
         <f>SUM(January:December!C46)</f>
-        <v>906</v>
+        <v>1587</v>
       </c>
       <c r="D46" s="7">
         <f>SUM(January:December!D46)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" s="7">
         <f>SUM(January:December!E46)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F46" s="7">
         <f>SUM(January:December!F46)</f>
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="G46" s="7">
         <f>SUM(January:December!G46)</f>
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H46" s="7">
         <f>SUM(January:December!H46)</f>
@@ -7820,11 +7820,11 @@
       </c>
       <c r="I46" s="7">
         <f>SUM(January:December!I46)</f>
-        <v>240</v>
+        <v>376</v>
       </c>
       <c r="J46" s="8">
         <f>SUM(January:December!J46)</f>
-        <v>1694</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -7833,27 +7833,27 @@
       </c>
       <c r="B47" s="10">
         <f>SUM(January:December!B47)</f>
-        <v>424</v>
+        <v>852</v>
       </c>
       <c r="C47" s="10">
         <f>SUM(January:December!C47)</f>
-        <v>179</v>
+        <v>364</v>
       </c>
       <c r="D47" s="10">
         <f>SUM(January:December!D47)</f>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E47" s="10">
         <f>SUM(January:December!E47)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F47" s="10">
         <f>SUM(January:December!F47)</f>
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G47" s="10">
         <f>SUM(January:December!G47)</f>
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="H47" s="10">
         <f>SUM(January:December!H47)</f>
@@ -7861,11 +7861,11 @@
       </c>
       <c r="I47" s="10">
         <f>SUM(January:December!I47)</f>
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="J47" s="11">
         <f>SUM(January:December!J47)</f>
-        <v>306</v>
+        <v>664</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -7874,27 +7874,27 @@
       </c>
       <c r="B48" s="7">
         <f>SUM(January:December!B48)</f>
-        <v>786</v>
+        <v>1532</v>
       </c>
       <c r="C48" s="7">
         <f>SUM(January:December!C48)</f>
-        <v>294</v>
+        <v>655</v>
       </c>
       <c r="D48" s="7">
         <f>SUM(January:December!D48)</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(January:December!E48)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(January:December!F48)</f>
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="G48" s="7">
         <f>SUM(January:December!G48)</f>
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(January:December!H48)</f>
@@ -7902,11 +7902,11 @@
       </c>
       <c r="I48" s="7">
         <f>SUM(January:December!I48)</f>
-        <v>120</v>
+        <v>238</v>
       </c>
       <c r="J48" s="8">
         <f>SUM(January:December!J48)</f>
-        <v>666</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -7915,39 +7915,39 @@
       </c>
       <c r="B49" s="10">
         <f>SUM(January:December!B49)</f>
-        <v>1916</v>
+        <v>3398</v>
       </c>
       <c r="C49" s="10">
         <f>SUM(January:December!C49)</f>
-        <v>792</v>
+        <v>1475</v>
       </c>
       <c r="D49" s="10">
         <f>SUM(January:December!D49)</f>
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="E49" s="10">
         <f>SUM(January:December!E49)</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F49" s="10">
         <f>SUM(January:December!F49)</f>
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G49" s="10">
         <f>SUM(January:December!G49)</f>
-        <v>116</v>
+        <v>249</v>
       </c>
       <c r="H49" s="10">
         <f>SUM(January:December!H49)</f>
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I49" s="10">
         <f>SUM(January:December!I49)</f>
-        <v>432</v>
+        <v>740</v>
       </c>
       <c r="J49" s="11">
         <f>SUM(January:December!J49)</f>
-        <v>1484</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -7956,15 +7956,15 @@
       </c>
       <c r="B50" s="7">
         <f>SUM(January:December!B50)</f>
-        <v>256</v>
+        <v>486</v>
       </c>
       <c r="C50" s="7">
         <f>SUM(January:December!C50)</f>
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="D50" s="7">
         <f>SUM(January:December!D50)</f>
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E50" s="7">
         <f>SUM(January:December!E50)</f>
@@ -7972,11 +7972,11 @@
       </c>
       <c r="F50" s="7">
         <f>SUM(January:December!F50)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G50" s="7">
         <f>SUM(January:December!G50)</f>
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="H50" s="7">
         <f>SUM(January:December!H50)</f>
@@ -7984,11 +7984,11 @@
       </c>
       <c r="I50" s="7">
         <f>SUM(January:December!I50)</f>
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="J50" s="8">
         <f>SUM(January:December!J50)</f>
-        <v>146</v>
+        <v>304</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -7997,27 +7997,27 @@
       </c>
       <c r="B51" s="10">
         <f>SUM(January:December!B51)</f>
-        <v>1388</v>
+        <v>2354</v>
       </c>
       <c r="C51" s="10">
         <f>SUM(January:December!C51)</f>
-        <v>520</v>
+        <v>947</v>
       </c>
       <c r="D51" s="10">
         <f>SUM(January:December!D51)</f>
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="E51" s="10">
         <f>SUM(January:December!E51)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F51" s="10">
         <f>SUM(January:December!F51)</f>
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G51" s="10">
         <f>SUM(January:December!G51)</f>
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="H51" s="10">
         <f>SUM(January:December!H51)</f>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="I51" s="10">
         <f>SUM(January:December!I51)</f>
-        <v>120</v>
+        <v>266</v>
       </c>
       <c r="J51" s="11">
         <f>SUM(January:December!J51)</f>
-        <v>1268</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -8038,15 +8038,15 @@
       </c>
       <c r="B52" s="7">
         <f>SUM(January:December!B52)</f>
-        <v>148</v>
+        <v>476</v>
       </c>
       <c r="C52" s="7">
         <f>SUM(January:December!C52)</f>
-        <v>53</v>
+        <v>181</v>
       </c>
       <c r="D52" s="7">
         <f>SUM(January:December!D52)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(January:December!E52)</f>
@@ -8054,23 +8054,23 @@
       </c>
       <c r="F52" s="7">
         <f>SUM(January:December!F52)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G52" s="7">
         <f>SUM(January:December!G52)</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H52" s="7">
         <f>SUM(January:December!H52)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" s="7">
         <f>SUM(January:December!I52)</f>
-        <v>30</v>
+        <v>182</v>
       </c>
       <c r="J52" s="8">
         <f>SUM(January:December!J52)</f>
-        <v>118</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -8079,15 +8079,15 @@
       </c>
       <c r="B53" s="10">
         <f>SUM(January:December!B53)</f>
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C53" s="10">
         <f>SUM(January:December!C53)</f>
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D53" s="10">
         <f>SUM(January:December!D53)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53" s="10">
         <f>SUM(January:December!E53)</f>
@@ -8095,11 +8095,11 @@
       </c>
       <c r="F53" s="10">
         <f>SUM(January:December!F53)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="10">
         <f>SUM(January:December!G53)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" s="10">
         <f>SUM(January:December!H53)</f>
@@ -8107,11 +8107,11 @@
       </c>
       <c r="I53" s="10">
         <f>SUM(January:December!I53)</f>
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J53" s="11">
         <f>SUM(January:December!J53)</f>
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -8120,15 +8120,15 @@
       </c>
       <c r="B54" s="7">
         <f>SUM(January:December!B54)</f>
-        <v>440</v>
+        <v>1282</v>
       </c>
       <c r="C54" s="7">
         <f>SUM(January:December!C54)</f>
-        <v>255</v>
+        <v>651</v>
       </c>
       <c r="D54" s="7">
         <f>SUM(January:December!D54)</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(January:December!E54)</f>
@@ -8136,11 +8136,11 @@
       </c>
       <c r="F54" s="7">
         <f>SUM(January:December!F54)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G54" s="7">
         <f>SUM(January:December!G54)</f>
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H54" s="7">
         <f>SUM(January:December!H54)</f>
@@ -8148,11 +8148,11 @@
       </c>
       <c r="I54" s="7">
         <f>SUM(January:December!I54)</f>
-        <v>144</v>
+        <v>348</v>
       </c>
       <c r="J54" s="8">
         <f>SUM(January:December!J54)</f>
-        <v>296</v>
+        <v>934</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -8161,15 +8161,15 @@
       </c>
       <c r="B55" s="31">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>816</v>
+        <v>1350</v>
       </c>
       <c r="C55" s="31">
         <f t="shared" ref="C55:J55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>342</v>
+        <v>652</v>
       </c>
       <c r="D55" s="31">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E55" s="31">
         <f t="shared" si="0"/>
@@ -8177,11 +8177,11 @@
       </c>
       <c r="F55" s="31">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G55" s="31">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="H55" s="31">
         <f t="shared" si="0"/>
@@ -8189,11 +8189,11 @@
       </c>
       <c r="I55" s="31">
         <f t="shared" si="0"/>
-        <v>366</v>
+        <v>624</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>726</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -8202,15 +8202,15 @@
       </c>
       <c r="B56" s="28">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>280</v>
+        <v>708</v>
       </c>
       <c r="C56" s="28">
         <f t="shared" ref="C56:J56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>126</v>
+        <v>270</v>
       </c>
       <c r="D56" s="28">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" si="1"/>
@@ -8218,11 +8218,11 @@
       </c>
       <c r="F56" s="28">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="1"/>
@@ -8230,11 +8230,11 @@
       </c>
       <c r="I56" s="28">
         <f t="shared" si="1"/>
-        <v>175</v>
+        <v>367</v>
       </c>
       <c r="J56" s="29">
         <f t="shared" si="1"/>
-        <v>105</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -8243,39 +8243,39 @@
       </c>
       <c r="B57" s="25">
         <f>SUM(B2:B54)</f>
-        <v>39279</v>
+        <v>75374</v>
       </c>
       <c r="C57" s="25">
         <f t="shared" ref="C57:J57" si="2">SUM(C2:C54)</f>
-        <v>16535</v>
+        <v>32039</v>
       </c>
       <c r="D57" s="25">
         <f t="shared" si="2"/>
-        <v>1741</v>
+        <v>3653</v>
       </c>
       <c r="E57" s="25">
         <f t="shared" si="2"/>
-        <v>179</v>
+        <v>293</v>
       </c>
       <c r="F57" s="25">
         <f t="shared" si="2"/>
-        <v>883</v>
+        <v>1936</v>
       </c>
       <c r="G57" s="25">
         <f t="shared" si="2"/>
-        <v>2803</v>
+        <v>5882</v>
       </c>
       <c r="H57" s="25">
         <f t="shared" si="2"/>
-        <v>127</v>
+        <v>218</v>
       </c>
       <c r="I57" s="25">
         <f t="shared" si="2"/>
-        <v>8754</v>
+        <v>17358</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="2"/>
-        <v>30525</v>
+        <v>58016</v>
       </c>
     </row>
   </sheetData>
@@ -8330,743 +8330,1697 @@
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
+      <c r="B2" s="4">
+        <v>2950</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1224</v>
+      </c>
+      <c r="D2" s="4">
+        <v>88</v>
+      </c>
+      <c r="E2" s="4">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4">
+        <v>68</v>
+      </c>
+      <c r="G2" s="4">
+        <v>161</v>
+      </c>
+      <c r="H2" s="4">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4">
+        <v>470</v>
+      </c>
+      <c r="J2" s="5">
+        <v>2480</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
+      <c r="B3" s="7">
+        <v>1126</v>
+      </c>
+      <c r="C3" s="7">
+        <v>590</v>
+      </c>
+      <c r="D3" s="7">
+        <v>35</v>
+      </c>
+      <c r="E3" s="7">
+        <v>10</v>
+      </c>
+      <c r="F3" s="7">
+        <v>19</v>
+      </c>
+      <c r="G3" s="7">
+        <v>64</v>
+      </c>
+      <c r="H3" s="7">
+        <v>2</v>
+      </c>
+      <c r="I3" s="7">
+        <v>178</v>
+      </c>
+      <c r="J3" s="8">
+        <v>948</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
+      <c r="B4" s="10">
+        <v>2486</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1096</v>
+      </c>
+      <c r="D4" s="10">
+        <v>123</v>
+      </c>
+      <c r="E4" s="10">
+        <v>15</v>
+      </c>
+      <c r="F4" s="10">
+        <v>91</v>
+      </c>
+      <c r="G4" s="10">
+        <v>229</v>
+      </c>
+      <c r="H4" s="10">
+        <v>1</v>
+      </c>
+      <c r="I4" s="10">
+        <v>332</v>
+      </c>
+      <c r="J4" s="11">
+        <v>2154</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
+      <c r="B5" s="7">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>2</v>
+      </c>
+      <c r="G5" s="7">
+        <v>4</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>2</v>
+      </c>
+      <c r="J5" s="8">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="11"/>
+      <c r="B6" s="10">
+        <v>2866</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1152</v>
+      </c>
+      <c r="D6" s="10">
+        <v>283</v>
+      </c>
+      <c r="E6" s="10">
+        <v>10</v>
+      </c>
+      <c r="F6" s="10">
+        <v>60</v>
+      </c>
+      <c r="G6" s="10">
+        <v>353</v>
+      </c>
+      <c r="H6" s="10">
+        <v>13</v>
+      </c>
+      <c r="I6" s="10">
+        <v>812</v>
+      </c>
+      <c r="J6" s="11">
+        <v>2054</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8"/>
+      <c r="B7" s="7">
+        <v>190</v>
+      </c>
+      <c r="C7" s="7">
+        <v>119</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>14</v>
+      </c>
+      <c r="G7" s="7">
+        <v>15</v>
+      </c>
+      <c r="H7" s="7">
+        <v>12</v>
+      </c>
+      <c r="I7" s="7">
+        <v>66</v>
+      </c>
+      <c r="J7" s="8">
+        <v>124</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="11"/>
+      <c r="B8" s="10">
+        <v>310</v>
+      </c>
+      <c r="C8" s="10">
+        <v>100</v>
+      </c>
+      <c r="D8" s="10">
+        <v>14</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>2</v>
+      </c>
+      <c r="G8" s="10">
+        <v>16</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>106</v>
+      </c>
+      <c r="J8" s="11">
+        <v>204</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8"/>
+      <c r="B9" s="7">
+        <v>76</v>
+      </c>
+      <c r="C9" s="7">
+        <v>49</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>18</v>
+      </c>
+      <c r="J9" s="8">
+        <v>58</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="11"/>
+      <c r="B10" s="10">
+        <v>0</v>
+      </c>
+      <c r="C10" s="10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
+      <c r="B11" s="7">
+        <v>0</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
+      <c r="B12" s="13">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13">
+        <v>2</v>
+      </c>
+      <c r="D12" s="13">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>0</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
+      <c r="B13" s="16">
+        <v>148</v>
+      </c>
+      <c r="C13" s="16">
+        <v>66</v>
+      </c>
+      <c r="D13" s="16">
+        <v>1</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1</v>
+      </c>
+      <c r="G13" s="16">
+        <v>2</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
+        <v>72</v>
+      </c>
+      <c r="J13" s="17">
+        <v>76</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
+      <c r="B14" s="13">
+        <v>336</v>
+      </c>
+      <c r="C14" s="13">
+        <v>191</v>
+      </c>
+      <c r="D14" s="13">
+        <v>12</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13">
+        <v>13</v>
+      </c>
+      <c r="G14" s="13">
+        <v>25</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>160</v>
+      </c>
+      <c r="J14" s="14">
+        <v>176</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
+      <c r="B15" s="16">
+        <v>50</v>
+      </c>
+      <c r="C15" s="16">
+        <v>51</v>
+      </c>
+      <c r="D15" s="16">
+        <v>7</v>
+      </c>
+      <c r="E15" s="16">
+        <v>0</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0</v>
+      </c>
+      <c r="G15" s="16">
+        <v>7</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0</v>
+      </c>
+      <c r="I15" s="16">
+        <v>26</v>
+      </c>
+      <c r="J15" s="17">
+        <v>24</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="11"/>
+      <c r="B16" s="10">
+        <v>100</v>
+      </c>
+      <c r="C16" s="10">
+        <v>51</v>
+      </c>
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0</v>
+      </c>
+      <c r="F16" s="10">
+        <v>3</v>
+      </c>
+      <c r="G16" s="10">
+        <v>4</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
+        <v>30</v>
+      </c>
+      <c r="J16" s="11">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="8"/>
+      <c r="B17" s="7">
+        <v>1212</v>
+      </c>
+      <c r="C17" s="7">
+        <v>506</v>
+      </c>
+      <c r="D17" s="7">
+        <v>51</v>
+      </c>
+      <c r="E17" s="7">
+        <v>8</v>
+      </c>
+      <c r="F17" s="7">
+        <v>28</v>
+      </c>
+      <c r="G17" s="7">
+        <v>87</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7">
+        <v>354</v>
+      </c>
+      <c r="J17" s="8">
+        <v>858</v>
+      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="11"/>
+      <c r="B18" s="10">
+        <v>64</v>
+      </c>
+      <c r="C18" s="10">
+        <v>50</v>
+      </c>
+      <c r="D18" s="10">
+        <v>3</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10">
+        <v>0</v>
+      </c>
+      <c r="G18" s="10">
+        <v>4</v>
+      </c>
+      <c r="H18" s="10">
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
+        <v>10</v>
+      </c>
+      <c r="J18" s="11">
+        <v>54</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
+      <c r="B19" s="7">
+        <v>1256</v>
+      </c>
+      <c r="C19" s="7">
+        <v>591</v>
+      </c>
+      <c r="D19" s="7">
+        <v>35</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0</v>
+      </c>
+      <c r="F19" s="7">
+        <v>11</v>
+      </c>
+      <c r="G19" s="7">
+        <v>46</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7">
+        <v>258</v>
+      </c>
+      <c r="J19" s="8">
+        <v>998</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="11"/>
+      <c r="B20" s="10">
+        <v>10</v>
+      </c>
+      <c r="C20" s="10">
+        <v>2</v>
+      </c>
+      <c r="D20" s="10">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0</v>
+      </c>
+      <c r="F20" s="10">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10">
+        <v>1</v>
+      </c>
+      <c r="H20" s="10">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10">
+        <v>6</v>
+      </c>
+      <c r="J20" s="11">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="8"/>
+      <c r="B21" s="7">
+        <v>880</v>
+      </c>
+      <c r="C21" s="7">
+        <v>410</v>
+      </c>
+      <c r="D21" s="7">
+        <v>27</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7">
+        <v>26</v>
+      </c>
+      <c r="G21" s="7">
+        <v>54</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0</v>
+      </c>
+      <c r="I21" s="7">
+        <v>214</v>
+      </c>
+      <c r="J21" s="8">
+        <v>666</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="11"/>
+      <c r="B22" s="10">
+        <v>160</v>
+      </c>
+      <c r="C22" s="10">
+        <v>98</v>
+      </c>
+      <c r="D22" s="10">
+        <v>3</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10">
+        <v>11</v>
+      </c>
+      <c r="G22" s="10">
+        <v>14</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
+        <v>56</v>
+      </c>
+      <c r="J22" s="11">
+        <v>104</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="8"/>
+      <c r="B23" s="7">
+        <v>1178</v>
+      </c>
+      <c r="C23" s="7">
+        <v>405</v>
+      </c>
+      <c r="D23" s="7">
+        <v>145</v>
+      </c>
+      <c r="E23" s="7">
+        <v>5</v>
+      </c>
+      <c r="F23" s="7">
+        <v>37</v>
+      </c>
+      <c r="G23" s="7">
+        <v>187</v>
+      </c>
+      <c r="H23" s="7">
+        <v>3</v>
+      </c>
+      <c r="I23" s="7">
+        <v>286</v>
+      </c>
+      <c r="J23" s="8">
+        <v>892</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="11"/>
+      <c r="B24" s="10">
+        <v>3626</v>
+      </c>
+      <c r="C24" s="10">
+        <v>1643</v>
+      </c>
+      <c r="D24" s="10">
+        <v>153</v>
+      </c>
+      <c r="E24" s="10">
+        <v>21</v>
+      </c>
+      <c r="F24" s="10">
+        <v>81</v>
+      </c>
+      <c r="G24" s="10">
+        <v>255</v>
+      </c>
+      <c r="H24" s="10">
+        <v>2</v>
+      </c>
+      <c r="I24" s="10">
+        <v>438</v>
+      </c>
+      <c r="J24" s="11">
+        <v>3188</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="8"/>
+      <c r="B25" s="7">
+        <v>252</v>
+      </c>
+      <c r="C25" s="7">
+        <v>126</v>
+      </c>
+      <c r="D25" s="7">
+        <v>4</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0</v>
+      </c>
+      <c r="F25" s="7">
+        <v>5</v>
+      </c>
+      <c r="G25" s="7">
+        <v>9</v>
+      </c>
+      <c r="H25" s="7">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7">
+        <v>86</v>
+      </c>
+      <c r="J25" s="8">
+        <v>166</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="11"/>
+      <c r="B26" s="10">
+        <v>0</v>
+      </c>
+      <c r="C26" s="10">
+        <v>0</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10">
+        <v>0</v>
+      </c>
+      <c r="J26" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="8"/>
+      <c r="B27" s="7">
+        <v>260</v>
+      </c>
+      <c r="C27" s="7">
+        <v>127</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1</v>
+      </c>
+      <c r="F27" s="7">
+        <v>3</v>
+      </c>
+      <c r="G27" s="7">
+        <v>6</v>
+      </c>
+      <c r="H27" s="7">
+        <v>0</v>
+      </c>
+      <c r="I27" s="7">
+        <v>90</v>
+      </c>
+      <c r="J27" s="8">
+        <v>170</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="11"/>
+      <c r="B28" s="10">
+        <v>214</v>
+      </c>
+      <c r="C28" s="10">
+        <v>93</v>
+      </c>
+      <c r="D28" s="10">
+        <v>11</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0</v>
+      </c>
+      <c r="F28" s="10">
+        <v>6</v>
+      </c>
+      <c r="G28" s="10">
+        <v>17</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
+        <v>82</v>
+      </c>
+      <c r="J28" s="11">
+        <v>132</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="8"/>
+      <c r="B29" s="7">
+        <v>1186</v>
+      </c>
+      <c r="C29" s="7">
+        <v>583</v>
+      </c>
+      <c r="D29" s="7">
+        <v>13</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1</v>
+      </c>
+      <c r="F29" s="7">
+        <v>21</v>
+      </c>
+      <c r="G29" s="7">
+        <v>35</v>
+      </c>
+      <c r="H29" s="7">
+        <v>0</v>
+      </c>
+      <c r="I29" s="7">
+        <v>352</v>
+      </c>
+      <c r="J29" s="8">
+        <v>834</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="11"/>
+      <c r="B30" s="10">
+        <v>6</v>
+      </c>
+      <c r="C30" s="10">
+        <v>4</v>
+      </c>
+      <c r="D30" s="10">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0</v>
+      </c>
+      <c r="F30" s="10">
+        <v>3</v>
+      </c>
+      <c r="G30" s="10">
+        <v>3</v>
+      </c>
+      <c r="H30" s="10">
+        <v>1</v>
+      </c>
+      <c r="I30" s="10">
+        <v>2</v>
+      </c>
+      <c r="J30" s="11">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="8"/>
+      <c r="B31" s="7">
+        <v>310</v>
+      </c>
+      <c r="C31" s="7">
+        <v>88</v>
+      </c>
+      <c r="D31" s="7">
+        <v>9</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7">
+        <v>4</v>
+      </c>
+      <c r="G31" s="7">
+        <v>13</v>
+      </c>
+      <c r="H31" s="7">
+        <v>3</v>
+      </c>
+      <c r="I31" s="7">
+        <v>14</v>
+      </c>
+      <c r="J31" s="8">
+        <v>296</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="11"/>
+      <c r="B32" s="10">
+        <v>1082</v>
+      </c>
+      <c r="C32" s="10">
+        <v>360</v>
+      </c>
+      <c r="D32" s="10">
+        <v>63</v>
+      </c>
+      <c r="E32" s="10">
+        <v>1</v>
+      </c>
+      <c r="F32" s="10">
+        <v>59</v>
+      </c>
+      <c r="G32" s="10">
+        <v>123</v>
+      </c>
+      <c r="H32" s="10">
+        <v>10</v>
+      </c>
+      <c r="I32" s="10">
+        <v>420</v>
+      </c>
+      <c r="J32" s="11">
+        <v>662</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="8"/>
+      <c r="B33" s="7">
+        <v>898</v>
+      </c>
+      <c r="C33" s="7">
+        <v>381</v>
+      </c>
+      <c r="D33" s="7">
+        <v>9</v>
+      </c>
+      <c r="E33" s="7">
+        <v>4</v>
+      </c>
+      <c r="F33" s="7">
+        <v>31</v>
+      </c>
+      <c r="G33" s="7">
+        <v>44</v>
+      </c>
+      <c r="H33" s="7">
+        <v>8</v>
+      </c>
+      <c r="I33" s="7">
+        <v>344</v>
+      </c>
+      <c r="J33" s="8">
+        <v>554</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="11"/>
+      <c r="B34" s="10">
+        <v>318</v>
+      </c>
+      <c r="C34" s="10">
+        <v>135</v>
+      </c>
+      <c r="D34" s="10">
+        <v>11</v>
+      </c>
+      <c r="E34" s="10">
+        <v>2</v>
+      </c>
+      <c r="F34" s="10">
+        <v>9</v>
+      </c>
+      <c r="G34" s="10">
+        <v>22</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
+        <v>130</v>
+      </c>
+      <c r="J34" s="11">
+        <v>188</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="8"/>
+      <c r="B35" s="7">
+        <v>2352</v>
+      </c>
+      <c r="C35" s="7">
+        <v>963</v>
+      </c>
+      <c r="D35" s="7">
+        <v>171</v>
+      </c>
+      <c r="E35" s="7">
+        <v>5</v>
+      </c>
+      <c r="F35" s="7">
+        <v>43</v>
+      </c>
+      <c r="G35" s="7">
+        <v>219</v>
+      </c>
+      <c r="H35" s="7">
+        <v>4</v>
+      </c>
+      <c r="I35" s="7">
+        <v>626</v>
+      </c>
+      <c r="J35" s="8">
+        <v>1726</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="11"/>
+      <c r="B36" s="10">
+        <v>320</v>
+      </c>
+      <c r="C36" s="10">
+        <v>148</v>
+      </c>
+      <c r="D36" s="10">
+        <v>16</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0</v>
+      </c>
+      <c r="F36" s="10">
+        <v>13</v>
+      </c>
+      <c r="G36" s="10">
+        <v>29</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0</v>
+      </c>
+      <c r="I36" s="10">
+        <v>136</v>
+      </c>
+      <c r="J36" s="11">
+        <v>184</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="8"/>
+      <c r="B37" s="7">
+        <v>1100</v>
+      </c>
+      <c r="C37" s="7">
+        <v>404</v>
+      </c>
+      <c r="D37" s="7">
+        <v>87</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1</v>
+      </c>
+      <c r="F37" s="7">
+        <v>42</v>
+      </c>
+      <c r="G37" s="7">
+        <v>130</v>
+      </c>
+      <c r="H37" s="7">
+        <v>17</v>
+      </c>
+      <c r="I37" s="7">
+        <v>296</v>
+      </c>
+      <c r="J37" s="8">
+        <v>804</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="11"/>
+      <c r="B38" s="10">
+        <v>100</v>
+      </c>
+      <c r="C38" s="10">
+        <v>38</v>
+      </c>
+      <c r="D38" s="10">
+        <v>0</v>
+      </c>
+      <c r="E38" s="10">
+        <v>0</v>
+      </c>
+      <c r="F38" s="10">
+        <v>0</v>
+      </c>
+      <c r="G38" s="10">
+        <v>0</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0</v>
+      </c>
+      <c r="I38" s="10">
+        <v>14</v>
+      </c>
+      <c r="J38" s="11">
+        <v>86</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="8"/>
+      <c r="B39" s="7">
+        <v>806</v>
+      </c>
+      <c r="C39" s="7">
+        <v>42</v>
+      </c>
+      <c r="D39" s="7">
+        <v>333</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3</v>
+      </c>
+      <c r="F39" s="7">
+        <v>146</v>
+      </c>
+      <c r="G39" s="7">
+        <v>482</v>
+      </c>
+      <c r="H39" s="7">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7">
+        <v>474</v>
+      </c>
+      <c r="J39" s="8">
+        <v>332</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="20"/>
+      <c r="B40" s="19">
+        <v>58</v>
+      </c>
+      <c r="C40" s="19">
+        <v>19</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19">
+        <v>0</v>
+      </c>
+      <c r="F40" s="19">
+        <v>0</v>
+      </c>
+      <c r="G40" s="19">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19">
+        <v>0</v>
+      </c>
+      <c r="I40" s="19">
+        <v>30</v>
+      </c>
+      <c r="J40" s="20">
+        <v>28</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="23"/>
+      <c r="B41" s="22">
+        <v>304</v>
+      </c>
+      <c r="C41" s="22">
+        <v>110</v>
+      </c>
+      <c r="D41" s="22">
+        <v>13</v>
+      </c>
+      <c r="E41" s="22">
+        <v>0</v>
+      </c>
+      <c r="F41" s="22">
+        <v>2</v>
+      </c>
+      <c r="G41" s="22">
+        <v>15</v>
+      </c>
+      <c r="H41" s="22">
+        <v>0</v>
+      </c>
+      <c r="I41" s="22">
+        <v>142</v>
+      </c>
+      <c r="J41" s="23">
+        <v>162</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="20"/>
+      <c r="B42" s="19">
+        <v>14</v>
+      </c>
+      <c r="C42" s="19">
+        <v>5</v>
+      </c>
+      <c r="D42" s="19">
+        <v>0</v>
+      </c>
+      <c r="E42" s="19">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19">
+        <v>0</v>
+      </c>
+      <c r="G42" s="19">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19">
+        <v>0</v>
+      </c>
+      <c r="I42" s="19">
+        <v>8</v>
+      </c>
+      <c r="J42" s="20">
+        <v>6</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="23"/>
+      <c r="B43" s="22">
+        <v>52</v>
+      </c>
+      <c r="C43" s="22">
+        <v>10</v>
+      </c>
+      <c r="D43" s="22">
+        <v>9</v>
+      </c>
+      <c r="E43" s="22">
+        <v>0</v>
+      </c>
+      <c r="F43" s="22">
+        <v>0</v>
+      </c>
+      <c r="G43" s="22">
+        <v>9</v>
+      </c>
+      <c r="H43" s="22">
+        <v>0</v>
+      </c>
+      <c r="I43" s="22">
+        <v>12</v>
+      </c>
+      <c r="J43" s="23">
+        <v>40</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="8"/>
+      <c r="B44" s="7">
+        <v>98</v>
+      </c>
+      <c r="C44" s="7">
+        <v>63</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7">
+        <v>40</v>
+      </c>
+      <c r="J44" s="8">
+        <v>58</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="11"/>
+      <c r="B45" s="10">
+        <v>766</v>
+      </c>
+      <c r="C45" s="10">
+        <v>427</v>
+      </c>
+      <c r="D45" s="10">
+        <v>17</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1</v>
+      </c>
+      <c r="F45" s="10">
+        <v>15</v>
+      </c>
+      <c r="G45" s="10">
+        <v>33</v>
+      </c>
+      <c r="H45" s="10">
+        <v>0</v>
+      </c>
+      <c r="I45" s="10">
+        <v>186</v>
+      </c>
+      <c r="J45" s="11">
+        <v>580</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="8"/>
+      <c r="B46" s="7">
+        <v>1490</v>
+      </c>
+      <c r="C46" s="7">
+        <v>681</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1</v>
+      </c>
+      <c r="F46" s="7">
+        <v>29</v>
+      </c>
+      <c r="G46" s="7">
+        <v>31</v>
+      </c>
+      <c r="H46" s="7">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7">
+        <v>136</v>
+      </c>
+      <c r="J46" s="8">
+        <v>1354</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="11"/>
+      <c r="B47" s="10">
+        <v>428</v>
+      </c>
+      <c r="C47" s="10">
+        <v>185</v>
+      </c>
+      <c r="D47" s="10">
+        <v>12</v>
+      </c>
+      <c r="E47" s="10">
+        <v>2</v>
+      </c>
+      <c r="F47" s="10">
+        <v>20</v>
+      </c>
+      <c r="G47" s="10">
+        <v>34</v>
+      </c>
+      <c r="H47" s="10">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10">
+        <v>70</v>
+      </c>
+      <c r="J47" s="11">
+        <v>358</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="8"/>
+      <c r="B48" s="7">
+        <v>746</v>
+      </c>
+      <c r="C48" s="7">
+        <v>361</v>
+      </c>
+      <c r="D48" s="7">
+        <v>7</v>
+      </c>
+      <c r="E48" s="7">
+        <v>3</v>
+      </c>
+      <c r="F48" s="7">
+        <v>36</v>
+      </c>
+      <c r="G48" s="7">
+        <v>46</v>
+      </c>
+      <c r="H48" s="7">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7">
+        <v>118</v>
+      </c>
+      <c r="J48" s="8">
+        <v>628</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="11"/>
+      <c r="B49" s="10">
+        <v>1482</v>
+      </c>
+      <c r="C49" s="10">
+        <v>683</v>
+      </c>
+      <c r="D49" s="10">
+        <v>76</v>
+      </c>
+      <c r="E49" s="10">
+        <v>7</v>
+      </c>
+      <c r="F49" s="10">
+        <v>50</v>
+      </c>
+      <c r="G49" s="10">
+        <v>133</v>
+      </c>
+      <c r="H49" s="10">
+        <v>10</v>
+      </c>
+      <c r="I49" s="10">
+        <v>308</v>
+      </c>
+      <c r="J49" s="11">
+        <v>1174</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="8"/>
+      <c r="B50" s="7">
+        <v>230</v>
+      </c>
+      <c r="C50" s="7">
+        <v>81</v>
+      </c>
+      <c r="D50" s="7">
+        <v>14</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7">
+        <v>2</v>
+      </c>
+      <c r="G50" s="7">
+        <v>16</v>
+      </c>
+      <c r="H50" s="7">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7">
+        <v>72</v>
+      </c>
+      <c r="J50" s="8">
+        <v>158</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="11"/>
+      <c r="B51" s="10">
+        <v>966</v>
+      </c>
+      <c r="C51" s="10">
+        <v>427</v>
+      </c>
+      <c r="D51" s="10">
+        <v>35</v>
+      </c>
+      <c r="E51" s="10">
+        <v>6</v>
+      </c>
+      <c r="F51" s="10">
+        <v>32</v>
+      </c>
+      <c r="G51" s="10">
+        <v>73</v>
+      </c>
+      <c r="H51" s="10">
+        <v>0</v>
+      </c>
+      <c r="I51" s="10">
+        <v>146</v>
+      </c>
+      <c r="J51" s="11">
+        <v>820</v>
+      </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="8"/>
+      <c r="B52" s="7">
+        <v>328</v>
+      </c>
+      <c r="C52" s="7">
+        <v>128</v>
+      </c>
+      <c r="D52" s="7">
+        <v>6</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>3</v>
+      </c>
+      <c r="G52" s="7">
+        <v>9</v>
+      </c>
+      <c r="H52" s="7">
+        <v>1</v>
+      </c>
+      <c r="I52" s="7">
+        <v>152</v>
+      </c>
+      <c r="J52" s="8">
+        <v>176</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="11"/>
+      <c r="B53" s="10">
+        <v>56</v>
+      </c>
+      <c r="C53" s="10">
+        <v>29</v>
+      </c>
+      <c r="D53" s="10">
+        <v>2</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0</v>
+      </c>
+      <c r="F53" s="10">
+        <v>1</v>
+      </c>
+      <c r="G53" s="10">
+        <v>3</v>
+      </c>
+      <c r="H53" s="10">
+        <v>0</v>
+      </c>
+      <c r="I53" s="10">
+        <v>20</v>
+      </c>
+      <c r="J53" s="11">
+        <v>36</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="8"/>
+      <c r="B54" s="7">
+        <v>842</v>
+      </c>
+      <c r="C54" s="7">
+        <v>396</v>
+      </c>
+      <c r="D54" s="7">
+        <v>4</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0</v>
+      </c>
+      <c r="F54" s="7">
+        <v>10</v>
+      </c>
+      <c r="G54" s="7">
+        <v>14</v>
+      </c>
+      <c r="H54" s="7">
+        <v>0</v>
+      </c>
+      <c r="I54" s="7">
+        <v>204</v>
+      </c>
+      <c r="J54" s="8">
+        <v>638</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
@@ -9074,15 +10028,15 @@
       </c>
       <c r="B55" s="31">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>534</v>
       </c>
       <c r="C55" s="31">
         <f t="shared" ref="C55:J55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="D55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E55" s="31">
         <f t="shared" si="0"/>
@@ -9090,11 +10044,11 @@
       </c>
       <c r="F55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H55" s="31">
         <f t="shared" si="0"/>
@@ -9102,11 +10056,11 @@
       </c>
       <c r="I55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -9115,15 +10069,15 @@
       </c>
       <c r="B56" s="28">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="C56" s="28">
         <f t="shared" ref="C56:J56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="D56" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" si="1"/>
@@ -9131,11 +10085,11 @@
       </c>
       <c r="F56" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="1"/>
@@ -9143,11 +10097,11 @@
       </c>
       <c r="I56" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="J56" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -9156,39 +10110,39 @@
       </c>
       <c r="B57" s="25">
         <f>SUM(B2:B54)</f>
-        <v>0</v>
+        <v>36095</v>
       </c>
       <c r="C57" s="25">
         <f t="shared" ref="C57:J57" si="2">SUM(C2:C54)</f>
-        <v>0</v>
+        <v>15504</v>
       </c>
       <c r="D57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1912</v>
       </c>
       <c r="E57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1053</v>
       </c>
       <c r="G57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3079</v>
       </c>
       <c r="H57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="I57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8604</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>27491</v>
       </c>
     </row>
   </sheetData>

--- a/statistics_files/2026/2026_99_gb_requests.xlsx
+++ b/statistics_files/2026/2026_99_gb_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA64327-3A99-426E-AB19-6C2AA9285444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DE30A3-1AEB-458F-9A86-931A59A88538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="843" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5988,39 +5988,39 @@
       </c>
       <c r="B2" s="4">
         <f>SUM(January:December!B2)</f>
-        <v>11158</v>
+        <v>13470</v>
       </c>
       <c r="C2" s="4">
         <f>SUM(January:December!C2)</f>
-        <v>5062</v>
+        <v>6071</v>
       </c>
       <c r="D2" s="4">
         <f>SUM(January:December!D2)</f>
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="E2" s="4">
         <f>SUM(January:December!E2)</f>
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F2" s="4">
         <f>SUM(January:December!F2)</f>
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="G2" s="4">
         <f>SUM(January:December!G2)</f>
-        <v>562</v>
+        <v>704</v>
       </c>
       <c r="H2" s="4">
         <f>SUM(January:December!H2)</f>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I2" s="4">
         <f>SUM(January:December!I2)</f>
-        <v>1626</v>
+        <v>1972</v>
       </c>
       <c r="J2" s="5">
         <f>SUM(January:December!J2)</f>
-        <v>9532</v>
+        <v>11498</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6029,39 +6029,39 @@
       </c>
       <c r="B3" s="7">
         <f>SUM(January:December!B3)</f>
-        <v>4450</v>
+        <v>5660</v>
       </c>
       <c r="C3" s="7">
         <f>SUM(January:December!C3)</f>
-        <v>1994</v>
+        <v>2410</v>
       </c>
       <c r="D3" s="7">
         <f>SUM(January:December!D3)</f>
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="E3" s="7">
         <f>SUM(January:December!E3)</f>
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F3" s="7">
         <f>SUM(January:December!F3)</f>
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="G3" s="7">
         <f>SUM(January:December!G3)</f>
-        <v>252</v>
+        <v>332</v>
       </c>
       <c r="H3" s="7">
         <f>SUM(January:December!H3)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I3" s="7">
         <f>SUM(January:December!I3)</f>
-        <v>684</v>
+        <v>838</v>
       </c>
       <c r="J3" s="8">
         <f>SUM(January:December!J3)</f>
-        <v>3766</v>
+        <v>4822</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B4" s="10">
         <f>SUM(January:December!B4)</f>
-        <v>10936</v>
+        <v>12168</v>
       </c>
       <c r="C4" s="10">
         <f>SUM(January:December!C4)</f>
-        <v>4548</v>
+        <v>5500</v>
       </c>
       <c r="D4" s="10">
         <f>SUM(January:December!D4)</f>
-        <v>540</v>
+        <v>640</v>
       </c>
       <c r="E4" s="10">
         <f>SUM(January:December!E4)</f>
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F4" s="10">
         <f>SUM(January:December!F4)</f>
-        <v>372</v>
+        <v>455</v>
       </c>
       <c r="G4" s="10">
         <f>SUM(January:December!G4)</f>
-        <v>964</v>
+        <v>1163</v>
       </c>
       <c r="H4" s="10">
         <f>SUM(January:December!H4)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="10">
         <f>SUM(January:December!I4)</f>
-        <v>1766</v>
+        <v>1982</v>
       </c>
       <c r="J4" s="11">
         <f>SUM(January:December!J4)</f>
-        <v>9170</v>
+        <v>10186</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6111,11 +6111,11 @@
       </c>
       <c r="B5" s="7">
         <f>SUM(January:December!B5)</f>
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C5" s="7">
         <f>SUM(January:December!C5)</f>
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D5" s="7">
         <f>SUM(January:December!D5)</f>
@@ -6139,11 +6139,11 @@
       </c>
       <c r="I5" s="7">
         <f>SUM(January:December!I5)</f>
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="J5" s="8">
         <f>SUM(January:December!J5)</f>
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -6152,39 +6152,39 @@
       </c>
       <c r="B6" s="10">
         <f>SUM(January:December!B6)</f>
-        <v>11940</v>
+        <v>13242</v>
       </c>
       <c r="C6" s="10">
         <f>SUM(January:December!C6)</f>
-        <v>4588</v>
+        <v>5542</v>
       </c>
       <c r="D6" s="10">
         <f>SUM(January:December!D6)</f>
-        <v>1121</v>
+        <v>1408</v>
       </c>
       <c r="E6" s="10">
         <f>SUM(January:December!E6)</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6" s="10">
         <f>SUM(January:December!F6)</f>
-        <v>239</v>
+        <v>343</v>
       </c>
       <c r="G6" s="10">
         <f>SUM(January:December!G6)</f>
-        <v>1380</v>
+        <v>1776</v>
       </c>
       <c r="H6" s="10">
         <f>SUM(January:December!H6)</f>
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="I6" s="10">
         <f>SUM(January:December!I6)</f>
-        <v>3462</v>
+        <v>3824</v>
       </c>
       <c r="J6" s="11">
         <f>SUM(January:December!J6)</f>
-        <v>8478</v>
+        <v>9418</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -6193,15 +6193,15 @@
       </c>
       <c r="B7" s="7">
         <f>SUM(January:December!B7)</f>
-        <v>1286</v>
+        <v>1704</v>
       </c>
       <c r="C7" s="7">
         <f>SUM(January:December!C7)</f>
-        <v>615</v>
+        <v>817</v>
       </c>
       <c r="D7" s="7">
         <f>SUM(January:December!D7)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(January:December!E7)</f>
@@ -6209,11 +6209,11 @@
       </c>
       <c r="F7" s="7">
         <f>SUM(January:December!F7)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" s="7">
         <f>SUM(January:December!G7)</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H7" s="7">
         <f>SUM(January:December!H7)</f>
@@ -6221,11 +6221,11 @@
       </c>
       <c r="I7" s="7">
         <f>SUM(January:December!I7)</f>
-        <v>426</v>
+        <v>622</v>
       </c>
       <c r="J7" s="8">
         <f>SUM(January:December!J7)</f>
-        <v>860</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -6234,27 +6234,27 @@
       </c>
       <c r="B8" s="10">
         <f>SUM(January:December!B8)</f>
-        <v>864</v>
+        <v>1084</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(January:December!C8)</f>
-        <v>384</v>
+        <v>459</v>
       </c>
       <c r="D8" s="10">
         <f>SUM(January:December!D8)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" s="10">
         <f>SUM(January:December!E8)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="10">
         <f>SUM(January:December!F8)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G8" s="10">
         <f>SUM(January:December!G8)</f>
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" s="10">
         <f>SUM(January:December!H8)</f>
@@ -6262,11 +6262,11 @@
       </c>
       <c r="I8" s="10">
         <f>SUM(January:December!I8)</f>
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="J8" s="11">
         <f>SUM(January:December!J8)</f>
-        <v>564</v>
+        <v>748</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -6275,15 +6275,15 @@
       </c>
       <c r="B9" s="7">
         <f>SUM(January:December!B9)</f>
-        <v>328</v>
+        <v>452</v>
       </c>
       <c r="C9" s="7">
         <f>SUM(January:December!C9)</f>
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="D9" s="7">
         <f>SUM(January:December!D9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7">
         <f>SUM(January:December!E9)</f>
@@ -6291,11 +6291,11 @@
       </c>
       <c r="F9" s="7">
         <f>SUM(January:December!F9)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="7">
         <f>SUM(January:December!G9)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H9" s="7">
         <f>SUM(January:December!H9)</f>
@@ -6303,11 +6303,11 @@
       </c>
       <c r="I9" s="7">
         <f>SUM(January:December!I9)</f>
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="J9" s="8">
         <f>SUM(January:December!J9)</f>
-        <v>250</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -6398,11 +6398,11 @@
       </c>
       <c r="B12" s="13">
         <f>SUM(January:December!B12)</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(January:December!C12)</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D12" s="13">
         <f>SUM(January:December!D12)</f>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="I12" s="13">
         <f>SUM(January:December!I12)</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J12" s="14">
         <f>SUM(January:December!J12)</f>
@@ -6439,27 +6439,27 @@
       </c>
       <c r="B13" s="16">
         <f>SUM(January:December!B13)</f>
-        <v>520</v>
+        <v>636</v>
       </c>
       <c r="C13" s="16">
         <f>SUM(January:December!C13)</f>
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="D13" s="16">
         <f>SUM(January:December!D13)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E13" s="16">
         <f>SUM(January:December!E13)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="16">
         <f>SUM(January:December!F13)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G13" s="16">
         <f>SUM(January:December!G13)</f>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H13" s="16">
         <f>SUM(January:December!H13)</f>
@@ -6467,11 +6467,11 @@
       </c>
       <c r="I13" s="16">
         <f>SUM(January:December!I13)</f>
-        <v>234</v>
+        <v>300</v>
       </c>
       <c r="J13" s="17">
         <f>SUM(January:December!J13)</f>
-        <v>286</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -6480,15 +6480,15 @@
       </c>
       <c r="B14" s="13">
         <f>SUM(January:December!B14)</f>
-        <v>1654</v>
+        <v>1956</v>
       </c>
       <c r="C14" s="13">
         <f>SUM(January:December!C14)</f>
-        <v>787</v>
+        <v>909</v>
       </c>
       <c r="D14" s="13">
         <f>SUM(January:December!D14)</f>
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E14" s="13">
         <f>SUM(January:December!E14)</f>
@@ -6496,11 +6496,11 @@
       </c>
       <c r="F14" s="13">
         <f>SUM(January:December!F14)</f>
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G14" s="13">
         <f>SUM(January:December!G14)</f>
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="H14" s="13">
         <f>SUM(January:December!H14)</f>
@@ -6508,11 +6508,11 @@
       </c>
       <c r="I14" s="13">
         <f>SUM(January:December!I14)</f>
-        <v>812</v>
+        <v>964</v>
       </c>
       <c r="J14" s="14">
         <f>SUM(January:December!J14)</f>
-        <v>842</v>
+        <v>992</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -6521,15 +6521,15 @@
       </c>
       <c r="B15" s="16">
         <f>SUM(January:December!B15)</f>
-        <v>426</v>
+        <v>564</v>
       </c>
       <c r="C15" s="16">
         <f>SUM(January:December!C15)</f>
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="D15" s="16">
         <f>SUM(January:December!D15)</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E15" s="16">
         <f>SUM(January:December!E15)</f>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="G15" s="16">
         <f>SUM(January:December!G15)</f>
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H15" s="16">
         <f>SUM(January:December!H15)</f>
@@ -6549,11 +6549,11 @@
       </c>
       <c r="I15" s="16">
         <f>SUM(January:December!I15)</f>
-        <v>198</v>
+        <v>254</v>
       </c>
       <c r="J15" s="17">
         <f>SUM(January:December!J15)</f>
-        <v>228</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B16" s="10">
         <f>SUM(January:December!B16)</f>
-        <v>534</v>
+        <v>630</v>
       </c>
       <c r="C16" s="10">
         <f>SUM(January:December!C16)</f>
-        <v>261</v>
+        <v>309</v>
       </c>
       <c r="D16" s="10">
         <f>SUM(January:December!D16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="10">
         <f>SUM(January:December!E16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="10">
         <f>SUM(January:December!F16)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G16" s="10">
         <f>SUM(January:December!G16)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H16" s="10">
         <f>SUM(January:December!H16)</f>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="I16" s="10">
         <f>SUM(January:December!I16)</f>
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="J16" s="11">
         <f>SUM(January:December!J16)</f>
-        <v>284</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -6603,39 +6603,39 @@
       </c>
       <c r="B17" s="7">
         <f>SUM(January:December!B17)</f>
-        <v>4818</v>
+        <v>5976</v>
       </c>
       <c r="C17" s="7">
         <f>SUM(January:December!C17)</f>
-        <v>2091</v>
+        <v>2520</v>
       </c>
       <c r="D17" s="7">
         <f>SUM(January:December!D17)</f>
-        <v>226</v>
+        <v>297</v>
       </c>
       <c r="E17" s="7">
         <f>SUM(January:December!E17)</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F17" s="7">
         <f>SUM(January:December!F17)</f>
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="G17" s="7">
         <f>SUM(January:December!G17)</f>
-        <v>353</v>
+        <v>451</v>
       </c>
       <c r="H17" s="7">
         <f>SUM(January:December!H17)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="7">
         <f>SUM(January:December!I17)</f>
-        <v>1370</v>
+        <v>1708</v>
       </c>
       <c r="J17" s="8">
         <f>SUM(January:December!J17)</f>
-        <v>3448</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -6644,11 +6644,11 @@
       </c>
       <c r="B18" s="10">
         <f>SUM(January:December!B18)</f>
-        <v>302</v>
+        <v>436</v>
       </c>
       <c r="C18" s="10">
         <f>SUM(January:December!C18)</f>
-        <v>195</v>
+        <v>239</v>
       </c>
       <c r="D18" s="10">
         <f>SUM(January:December!D18)</f>
@@ -6656,15 +6656,15 @@
       </c>
       <c r="E18" s="10">
         <f>SUM(January:December!E18)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="10">
         <f>SUM(January:December!F18)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G18" s="10">
         <f>SUM(January:December!G18)</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(January:December!H18)</f>
@@ -6672,11 +6672,11 @@
       </c>
       <c r="I18" s="10">
         <f>SUM(January:December!I18)</f>
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="J18" s="11">
         <f>SUM(January:December!J18)</f>
-        <v>258</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -6685,39 +6685,39 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(January:December!B19)</f>
-        <v>4132</v>
+        <v>4788</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(January:December!C19)</f>
-        <v>1814</v>
+        <v>2105</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(January:December!D19)</f>
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(January:December!E19)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F19" s="7">
         <f>SUM(January:December!F19)</f>
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="G19" s="7">
         <f>SUM(January:December!G19)</f>
-        <v>213</v>
+        <v>265</v>
       </c>
       <c r="H19" s="7">
         <f>SUM(January:December!H19)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
         <f>SUM(January:December!I19)</f>
-        <v>1126</v>
+        <v>1370</v>
       </c>
       <c r="J19" s="8">
         <f>SUM(January:December!J19)</f>
-        <v>3006</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6726,11 +6726,11 @@
       </c>
       <c r="B20" s="10">
         <f>SUM(January:December!B20)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="10">
         <f>SUM(January:December!C20)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="10">
         <f>SUM(January:December!D20)</f>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="J20" s="11">
         <f>SUM(January:December!J20)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -6767,27 +6767,27 @@
       </c>
       <c r="B21" s="7">
         <f>SUM(January:December!B21)</f>
-        <v>3628</v>
+        <v>4640</v>
       </c>
       <c r="C21" s="7">
         <f>SUM(January:December!C21)</f>
-        <v>1672</v>
+        <v>2059</v>
       </c>
       <c r="D21" s="7">
         <f>SUM(January:December!D21)</f>
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(January:December!E21)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F21" s="7">
         <f>SUM(January:December!F21)</f>
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G21" s="7">
         <f>SUM(January:December!G21)</f>
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="H21" s="7">
         <f>SUM(January:December!H21)</f>
@@ -6795,11 +6795,11 @@
       </c>
       <c r="I21" s="7">
         <f>SUM(January:December!I21)</f>
-        <v>826</v>
+        <v>1108</v>
       </c>
       <c r="J21" s="8">
         <f>SUM(January:December!J21)</f>
-        <v>2802</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -6808,15 +6808,15 @@
       </c>
       <c r="B22" s="10">
         <f>SUM(January:December!B22)</f>
-        <v>580</v>
+        <v>690</v>
       </c>
       <c r="C22" s="10">
         <f>SUM(January:December!C22)</f>
-        <v>282</v>
+        <v>344</v>
       </c>
       <c r="D22" s="10">
         <f>SUM(January:December!D22)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22" s="10">
         <f>SUM(January:December!E22)</f>
@@ -6824,11 +6824,11 @@
       </c>
       <c r="F22" s="10">
         <f>SUM(January:December!F22)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G22" s="10">
         <f>SUM(January:December!G22)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H22" s="10">
         <f>SUM(January:December!H22)</f>
@@ -6836,11 +6836,11 @@
       </c>
       <c r="I22" s="10">
         <f>SUM(January:December!I22)</f>
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="J22" s="11">
         <f>SUM(January:December!J22)</f>
-        <v>410</v>
+        <v>474</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -6849,39 +6849,39 @@
       </c>
       <c r="B23" s="7">
         <f>SUM(January:December!B23)</f>
-        <v>5604</v>
+        <v>6272</v>
       </c>
       <c r="C23" s="7">
         <f>SUM(January:December!C23)</f>
-        <v>1858</v>
+        <v>2073</v>
       </c>
       <c r="D23" s="7">
         <f>SUM(January:December!D23)</f>
-        <v>680</v>
+        <v>780</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(January:December!E23)</f>
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F23" s="7">
         <f>SUM(January:December!F23)</f>
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="G23" s="7">
         <f>SUM(January:December!G23)</f>
-        <v>944</v>
+        <v>1069</v>
       </c>
       <c r="H23" s="7">
         <f>SUM(January:December!H23)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I23" s="7">
         <f>SUM(January:December!I23)</f>
-        <v>1298</v>
+        <v>1402</v>
       </c>
       <c r="J23" s="8">
         <f>SUM(January:December!J23)</f>
-        <v>4306</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -6890,39 +6890,39 @@
       </c>
       <c r="B24" s="10">
         <f>SUM(January:December!B24)</f>
-        <v>15246</v>
+        <v>19584</v>
       </c>
       <c r="C24" s="10">
         <f>SUM(January:December!C24)</f>
-        <v>6690</v>
+        <v>8375</v>
       </c>
       <c r="D24" s="10">
         <f>SUM(January:December!D24)</f>
-        <v>652</v>
+        <v>822</v>
       </c>
       <c r="E24" s="10">
         <f>SUM(January:December!E24)</f>
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F24" s="10">
         <f>SUM(January:December!F24)</f>
-        <v>325</v>
+        <v>489</v>
       </c>
       <c r="G24" s="10">
         <f>SUM(January:December!G24)</f>
-        <v>1052</v>
+        <v>1395</v>
       </c>
       <c r="H24" s="10">
         <f>SUM(January:December!H24)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I24" s="10">
         <f>SUM(January:December!I24)</f>
-        <v>1962</v>
+        <v>2506</v>
       </c>
       <c r="J24" s="11">
         <f>SUM(January:December!J24)</f>
-        <v>13284</v>
+        <v>17078</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -6931,15 +6931,15 @@
       </c>
       <c r="B25" s="7">
         <f>SUM(January:December!B25)</f>
-        <v>1164</v>
+        <v>1352</v>
       </c>
       <c r="C25" s="7">
         <f>SUM(January:December!C25)</f>
-        <v>505</v>
+        <v>595</v>
       </c>
       <c r="D25" s="7">
         <f>SUM(January:December!D25)</f>
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(January:December!E25)</f>
@@ -6947,23 +6947,23 @@
       </c>
       <c r="F25" s="7">
         <f>SUM(January:December!F25)</f>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G25" s="7">
         <f>SUM(January:December!G25)</f>
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H25" s="7">
         <f>SUM(January:December!H25)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="7">
         <f>SUM(January:December!I25)</f>
-        <v>346</v>
+        <v>424</v>
       </c>
       <c r="J25" s="8">
         <f>SUM(January:December!J25)</f>
-        <v>818</v>
+        <v>928</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -7013,39 +7013,39 @@
       </c>
       <c r="B27" s="7">
         <f>SUM(January:December!B27)</f>
-        <v>1190</v>
+        <v>1648</v>
       </c>
       <c r="C27" s="7">
         <f>SUM(January:December!C27)</f>
-        <v>565</v>
+        <v>764</v>
       </c>
       <c r="D27" s="7">
         <f>SUM(January:December!D27)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(January:December!E27)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="7">
         <f>SUM(January:December!F27)</f>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G27" s="7">
         <f>SUM(January:December!G27)</f>
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H27" s="7">
         <f>SUM(January:December!H27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="7">
         <f>SUM(January:December!I27)</f>
-        <v>400</v>
+        <v>496</v>
       </c>
       <c r="J27" s="8">
         <f>SUM(January:December!J27)</f>
-        <v>790</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -7054,15 +7054,15 @@
       </c>
       <c r="B28" s="10">
         <f>SUM(January:December!B28)</f>
-        <v>943</v>
+        <v>1221</v>
       </c>
       <c r="C28" s="10">
         <f>SUM(January:December!C28)</f>
-        <v>428</v>
+        <v>530</v>
       </c>
       <c r="D28" s="10">
         <f>SUM(January:December!D28)</f>
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E28" s="10">
         <f>SUM(January:December!E28)</f>
@@ -7070,11 +7070,11 @@
       </c>
       <c r="F28" s="10">
         <f>SUM(January:December!F28)</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G28" s="10">
         <f>SUM(January:December!G28)</f>
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="H28" s="10">
         <f>SUM(January:December!H28)</f>
@@ -7082,11 +7082,11 @@
       </c>
       <c r="I28" s="10">
         <f>SUM(January:December!I28)</f>
-        <v>300</v>
+        <v>394</v>
       </c>
       <c r="J28" s="11">
         <f>SUM(January:December!J28)</f>
-        <v>643</v>
+        <v>827</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -7095,27 +7095,27 @@
       </c>
       <c r="B29" s="7">
         <f>SUM(January:December!B29)</f>
-        <v>5168</v>
+        <v>6526</v>
       </c>
       <c r="C29" s="7">
         <f>SUM(January:December!C29)</f>
-        <v>2485</v>
+        <v>3030</v>
       </c>
       <c r="D29" s="7">
         <f>SUM(January:December!D29)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(January:December!E29)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F29" s="7">
         <f>SUM(January:December!F29)</f>
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="G29" s="7">
         <f>SUM(January:December!G29)</f>
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="H29" s="7">
         <f>SUM(January:December!H29)</f>
@@ -7123,11 +7123,11 @@
       </c>
       <c r="I29" s="7">
         <f>SUM(January:December!I29)</f>
-        <v>1304</v>
+        <v>1574</v>
       </c>
       <c r="J29" s="8">
         <f>SUM(January:December!J29)</f>
-        <v>3864</v>
+        <v>4952</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -7136,11 +7136,11 @@
       </c>
       <c r="B30" s="10">
         <f>SUM(January:December!B30)</f>
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="C30" s="10">
         <f>SUM(January:December!C30)</f>
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="D30" s="10">
         <f>SUM(January:December!D30)</f>
@@ -7148,15 +7148,15 @@
       </c>
       <c r="E30" s="10">
         <f>SUM(January:December!E30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="10">
         <f>SUM(January:December!F30)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G30" s="10">
         <f>SUM(January:December!G30)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H30" s="10">
         <f>SUM(January:December!H30)</f>
@@ -7164,11 +7164,11 @@
       </c>
       <c r="I30" s="10">
         <f>SUM(January:December!I30)</f>
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="J30" s="11">
         <f>SUM(January:December!J30)</f>
-        <v>106</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -7177,39 +7177,39 @@
       </c>
       <c r="B31" s="7">
         <f>SUM(January:December!B31)</f>
-        <v>777</v>
+        <v>1001</v>
       </c>
       <c r="C31" s="7">
         <f>SUM(January:December!C31)</f>
-        <v>354</v>
+        <v>426</v>
       </c>
       <c r="D31" s="7">
         <f>SUM(January:December!D31)</f>
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(January:December!E31)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F31" s="7">
         <f>SUM(January:December!F31)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G31" s="7">
         <f>SUM(January:December!G31)</f>
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H31" s="7">
         <f>SUM(January:December!H31)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I31" s="7">
         <f>SUM(January:December!I31)</f>
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="J31" s="8">
         <f>SUM(January:December!J31)</f>
-        <v>707</v>
+        <v>909</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -7218,39 +7218,39 @@
       </c>
       <c r="B32" s="10">
         <f>SUM(January:December!B32)</f>
-        <v>4000</v>
+        <v>4924</v>
       </c>
       <c r="C32" s="10">
         <f>SUM(January:December!C32)</f>
-        <v>1444</v>
+        <v>1753</v>
       </c>
       <c r="D32" s="10">
         <f>SUM(January:December!D32)</f>
-        <v>345</v>
+        <v>444</v>
       </c>
       <c r="E32" s="10">
         <f>SUM(January:December!E32)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F32" s="10">
         <f>SUM(January:December!F32)</f>
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="G32" s="10">
         <f>SUM(January:December!G32)</f>
-        <v>530</v>
+        <v>680</v>
       </c>
       <c r="H32" s="10">
         <f>SUM(January:December!H32)</f>
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="I32" s="10">
         <f>SUM(January:December!I32)</f>
-        <v>1606</v>
+        <v>1944</v>
       </c>
       <c r="J32" s="11">
         <f>SUM(January:December!J32)</f>
-        <v>2394</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -7259,39 +7259,39 @@
       </c>
       <c r="B33" s="7">
         <f>SUM(January:December!B33)</f>
-        <v>3384</v>
+        <v>4186</v>
       </c>
       <c r="C33" s="7">
         <f>SUM(January:December!C33)</f>
-        <v>1408</v>
+        <v>1737</v>
       </c>
       <c r="D33" s="7">
         <f>SUM(January:December!D33)</f>
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(January:December!E33)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F33" s="7">
         <f>SUM(January:December!F33)</f>
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="G33" s="7">
         <f>SUM(January:December!G33)</f>
-        <v>231</v>
+        <v>287</v>
       </c>
       <c r="H33" s="7">
         <f>SUM(January:December!H33)</f>
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="I33" s="7">
         <f>SUM(January:December!I33)</f>
-        <v>1382</v>
+        <v>1776</v>
       </c>
       <c r="J33" s="8">
         <f>SUM(January:December!J33)</f>
-        <v>2002</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -7300,27 +7300,27 @@
       </c>
       <c r="B34" s="10">
         <f>SUM(January:December!B34)</f>
-        <v>1046</v>
+        <v>1256</v>
       </c>
       <c r="C34" s="10">
         <f>SUM(January:December!C34)</f>
-        <v>481</v>
+        <v>570</v>
       </c>
       <c r="D34" s="10">
         <f>SUM(January:December!D34)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E34" s="10">
         <f>SUM(January:December!E34)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34" s="10">
         <f>SUM(January:December!F34)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G34" s="10">
         <f>SUM(January:December!G34)</f>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H34" s="10">
         <f>SUM(January:December!H34)</f>
@@ -7328,11 +7328,11 @@
       </c>
       <c r="I34" s="10">
         <f>SUM(January:December!I34)</f>
-        <v>352</v>
+        <v>456</v>
       </c>
       <c r="J34" s="11">
         <f>SUM(January:December!J34)</f>
-        <v>694</v>
+        <v>800</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -7341,39 +7341,39 @@
       </c>
       <c r="B35" s="7">
         <f>SUM(January:December!B35)</f>
-        <v>11166</v>
+        <v>14082</v>
       </c>
       <c r="C35" s="7">
         <f>SUM(January:December!C35)</f>
-        <v>4551</v>
+        <v>5680</v>
       </c>
       <c r="D35" s="7">
         <f>SUM(January:December!D35)</f>
-        <v>750</v>
+        <v>967</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(January:December!E35)</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F35" s="7">
         <f>SUM(January:December!F35)</f>
-        <v>224</v>
+        <v>297</v>
       </c>
       <c r="G35" s="7">
         <f>SUM(January:December!G35)</f>
-        <v>1005</v>
+        <v>1297</v>
       </c>
       <c r="H35" s="7">
         <f>SUM(January:December!H35)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I35" s="7">
         <f>SUM(January:December!I35)</f>
-        <v>2648</v>
+        <v>3150</v>
       </c>
       <c r="J35" s="8">
         <f>SUM(January:December!J35)</f>
-        <v>8518</v>
+        <v>10932</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -7382,27 +7382,27 @@
       </c>
       <c r="B36" s="10">
         <f>SUM(January:December!B36)</f>
-        <v>1358</v>
+        <v>1664</v>
       </c>
       <c r="C36" s="10">
         <f>SUM(January:December!C36)</f>
-        <v>615</v>
+        <v>742</v>
       </c>
       <c r="D36" s="10">
         <f>SUM(January:December!D36)</f>
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E36" s="10">
         <f>SUM(January:December!E36)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="10">
         <f>SUM(January:December!F36)</f>
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G36" s="10">
         <f>SUM(January:December!G36)</f>
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="H36" s="10">
         <f>SUM(January:December!H36)</f>
@@ -7410,11 +7410,11 @@
       </c>
       <c r="I36" s="10">
         <f>SUM(January:December!I36)</f>
-        <v>452</v>
+        <v>560</v>
       </c>
       <c r="J36" s="11">
         <f>SUM(January:December!J36)</f>
-        <v>906</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -7423,27 +7423,27 @@
       </c>
       <c r="B37" s="7">
         <f>SUM(January:December!B37)</f>
-        <v>4632</v>
+        <v>5674</v>
       </c>
       <c r="C37" s="7">
         <f>SUM(January:December!C37)</f>
-        <v>1705</v>
+        <v>2081</v>
       </c>
       <c r="D37" s="7">
         <f>SUM(January:December!D37)</f>
-        <v>440</v>
+        <v>534</v>
       </c>
       <c r="E37" s="7">
         <f>SUM(January:December!E37)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F37" s="7">
         <f>SUM(January:December!F37)</f>
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="G37" s="7">
         <f>SUM(January:December!G37)</f>
-        <v>627</v>
+        <v>736</v>
       </c>
       <c r="H37" s="7">
         <f>SUM(January:December!H37)</f>
@@ -7451,11 +7451,11 @@
       </c>
       <c r="I37" s="7">
         <f>SUM(January:December!I37)</f>
-        <v>1232</v>
+        <v>1440</v>
       </c>
       <c r="J37" s="8">
         <f>SUM(January:December!J37)</f>
-        <v>3400</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -7464,11 +7464,11 @@
       </c>
       <c r="B38" s="10">
         <f>SUM(January:December!B38)</f>
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="C38" s="10">
         <f>SUM(January:December!C38)</f>
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="D38" s="10">
         <f>SUM(January:December!D38)</f>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="E38" s="10">
         <f>SUM(January:December!E38)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="10">
         <f>SUM(January:December!F38)</f>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="G38" s="10">
         <f>SUM(January:December!G38)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H38" s="10">
         <f>SUM(January:December!H38)</f>
@@ -7492,11 +7492,11 @@
       </c>
       <c r="I38" s="10">
         <f>SUM(January:December!I38)</f>
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="J38" s="11">
         <f>SUM(January:December!J38)</f>
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -7505,15 +7505,15 @@
       </c>
       <c r="B39" s="7">
         <f>SUM(January:December!B39)</f>
-        <v>1736</v>
+        <v>1898</v>
       </c>
       <c r="C39" s="7">
         <f>SUM(January:December!C39)</f>
-        <v>248</v>
+        <v>320</v>
       </c>
       <c r="D39" s="7">
         <f>SUM(January:December!D39)</f>
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(January:December!E39)</f>
@@ -7521,11 +7521,11 @@
       </c>
       <c r="F39" s="7">
         <f>SUM(January:December!F39)</f>
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G39" s="7">
         <f>SUM(January:December!G39)</f>
-        <v>697</v>
+        <v>728</v>
       </c>
       <c r="H39" s="7">
         <f>SUM(January:December!H39)</f>
@@ -7533,11 +7533,11 @@
       </c>
       <c r="I39" s="7">
         <f>SUM(January:December!I39)</f>
-        <v>862</v>
+        <v>936</v>
       </c>
       <c r="J39" s="8">
         <f>SUM(January:December!J39)</f>
-        <v>874</v>
+        <v>962</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -7591,15 +7591,15 @@
       </c>
       <c r="C41" s="22">
         <f>SUM(January:December!C41)</f>
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D41" s="22">
         <f>SUM(January:December!D41)</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E41" s="22">
         <f>SUM(January:December!E41)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" s="22">
         <f>SUM(January:December!F41)</f>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="G41" s="22">
         <f>SUM(January:December!G41)</f>
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H41" s="22">
         <f>SUM(January:December!H41)</f>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="B42" s="19">
         <f>SUM(January:December!B42)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C42" s="19">
         <f>SUM(January:December!C42)</f>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="J42" s="20">
         <f>SUM(January:December!J42)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="D43" s="22">
         <f>SUM(January:December!D43)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E43" s="22">
         <f>SUM(January:December!E43)</f>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="G43" s="22">
         <f>SUM(January:December!G43)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H43" s="22">
         <f>SUM(January:December!H43)</f>
@@ -7710,11 +7710,11 @@
       </c>
       <c r="B44" s="7">
         <f>SUM(January:December!B44)</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C44" s="7">
         <f>SUM(January:December!C44)</f>
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="D44" s="7">
         <f>SUM(January:December!D44)</f>
@@ -7738,11 +7738,11 @@
       </c>
       <c r="I44" s="7">
         <f>SUM(January:December!I44)</f>
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="J44" s="8">
         <f>SUM(January:December!J44)</f>
-        <v>234</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -7751,27 +7751,27 @@
       </c>
       <c r="B45" s="10">
         <f>SUM(January:December!B45)</f>
-        <v>3816</v>
+        <v>4646</v>
       </c>
       <c r="C45" s="10">
         <f>SUM(January:December!C45)</f>
-        <v>1712</v>
+        <v>2101</v>
       </c>
       <c r="D45" s="10">
         <f>SUM(January:December!D45)</f>
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="E45" s="10">
         <f>SUM(January:December!E45)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F45" s="10">
         <f>SUM(January:December!F45)</f>
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G45" s="10">
         <f>SUM(January:December!G45)</f>
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="H45" s="10">
         <f>SUM(January:December!H45)</f>
@@ -7779,11 +7779,11 @@
       </c>
       <c r="I45" s="10">
         <f>SUM(January:December!I45)</f>
-        <v>1148</v>
+        <v>1344</v>
       </c>
       <c r="J45" s="11">
         <f>SUM(January:December!J45)</f>
-        <v>2668</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -7792,11 +7792,11 @@
       </c>
       <c r="B46" s="7">
         <f>SUM(January:December!B46)</f>
-        <v>5844</v>
+        <v>7108</v>
       </c>
       <c r="C46" s="7">
         <f>SUM(January:December!C46)</f>
-        <v>2899</v>
+        <v>3448</v>
       </c>
       <c r="D46" s="7">
         <f>SUM(January:December!D46)</f>
@@ -7804,27 +7804,27 @@
       </c>
       <c r="E46" s="7">
         <f>SUM(January:December!E46)</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F46" s="7">
         <f>SUM(January:December!F46)</f>
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="G46" s="7">
         <f>SUM(January:December!G46)</f>
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="H46" s="7">
         <f>SUM(January:December!H46)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7">
         <f>SUM(January:December!I46)</f>
-        <v>704</v>
+        <v>872</v>
       </c>
       <c r="J46" s="8">
         <f>SUM(January:December!J46)</f>
-        <v>5140</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -7833,27 +7833,27 @@
       </c>
       <c r="B47" s="10">
         <f>SUM(January:December!B47)</f>
-        <v>1784</v>
+        <v>2258</v>
       </c>
       <c r="C47" s="10">
         <f>SUM(January:December!C47)</f>
-        <v>747</v>
+        <v>911</v>
       </c>
       <c r="D47" s="10">
         <f>SUM(January:December!D47)</f>
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E47" s="10">
         <f>SUM(January:December!E47)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F47" s="10">
         <f>SUM(January:December!F47)</f>
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G47" s="10">
         <f>SUM(January:December!G47)</f>
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="H47" s="10">
         <f>SUM(January:December!H47)</f>
@@ -7861,11 +7861,11 @@
       </c>
       <c r="I47" s="10">
         <f>SUM(January:December!I47)</f>
-        <v>340</v>
+        <v>438</v>
       </c>
       <c r="J47" s="11">
         <f>SUM(January:December!J47)</f>
-        <v>1444</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -7874,27 +7874,27 @@
       </c>
       <c r="B48" s="7">
         <f>SUM(January:December!B48)</f>
-        <v>2948</v>
+        <v>3354</v>
       </c>
       <c r="C48" s="7">
         <f>SUM(January:December!C48)</f>
-        <v>1232</v>
+        <v>1429</v>
       </c>
       <c r="D48" s="7">
         <f>SUM(January:December!D48)</f>
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(January:December!E48)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(January:December!F48)</f>
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G48" s="7">
         <f>SUM(January:December!G48)</f>
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(January:December!H48)</f>
@@ -7902,11 +7902,11 @@
       </c>
       <c r="I48" s="7">
         <f>SUM(January:December!I48)</f>
-        <v>524</v>
+        <v>622</v>
       </c>
       <c r="J48" s="8">
         <f>SUM(January:December!J48)</f>
-        <v>2424</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -7915,39 +7915,39 @@
       </c>
       <c r="B49" s="10">
         <f>SUM(January:December!B49)</f>
-        <v>6898</v>
+        <v>8812</v>
       </c>
       <c r="C49" s="10">
         <f>SUM(January:December!C49)</f>
-        <v>2994</v>
+        <v>3784</v>
       </c>
       <c r="D49" s="10">
         <f>SUM(January:December!D49)</f>
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="E49" s="10">
         <f>SUM(January:December!E49)</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F49" s="10">
         <f>SUM(January:December!F49)</f>
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="G49" s="10">
         <f>SUM(January:December!G49)</f>
-        <v>473</v>
+        <v>576</v>
       </c>
       <c r="H49" s="10">
         <f>SUM(January:December!H49)</f>
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="I49" s="10">
         <f>SUM(January:December!I49)</f>
-        <v>1428</v>
+        <v>1826</v>
       </c>
       <c r="J49" s="11">
         <f>SUM(January:December!J49)</f>
-        <v>5470</v>
+        <v>6986</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -7956,27 +7956,27 @@
       </c>
       <c r="B50" s="7">
         <f>SUM(January:December!B50)</f>
-        <v>1014</v>
+        <v>1182</v>
       </c>
       <c r="C50" s="7">
         <f>SUM(January:December!C50)</f>
-        <v>402</v>
+        <v>481</v>
       </c>
       <c r="D50" s="7">
         <f>SUM(January:December!D50)</f>
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E50" s="7">
         <f>SUM(January:December!E50)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="7">
         <f>SUM(January:December!F50)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G50" s="7">
         <f>SUM(January:December!G50)</f>
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="H50" s="7">
         <f>SUM(January:December!H50)</f>
@@ -7984,11 +7984,11 @@
       </c>
       <c r="I50" s="7">
         <f>SUM(January:December!I50)</f>
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="J50" s="8">
         <f>SUM(January:December!J50)</f>
-        <v>664</v>
+        <v>772</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -7997,27 +7997,27 @@
       </c>
       <c r="B51" s="10">
         <f>SUM(January:December!B51)</f>
-        <v>3536</v>
+        <v>4072</v>
       </c>
       <c r="C51" s="10">
         <f>SUM(January:December!C51)</f>
-        <v>1557</v>
+        <v>1756</v>
       </c>
       <c r="D51" s="10">
         <f>SUM(January:December!D51)</f>
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="E51" s="10">
         <f>SUM(January:December!E51)</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F51" s="10">
         <f>SUM(January:December!F51)</f>
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G51" s="10">
         <f>SUM(January:December!G51)</f>
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="H51" s="10">
         <f>SUM(January:December!H51)</f>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="I51" s="10">
         <f>SUM(January:December!I51)</f>
-        <v>508</v>
+        <v>588</v>
       </c>
       <c r="J51" s="11">
         <f>SUM(January:December!J51)</f>
-        <v>3028</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -8038,15 +8038,15 @@
       </c>
       <c r="B52" s="7">
         <f>SUM(January:December!B52)</f>
-        <v>726</v>
+        <v>770</v>
       </c>
       <c r="C52" s="7">
         <f>SUM(January:December!C52)</f>
-        <v>371</v>
+        <v>421</v>
       </c>
       <c r="D52" s="7">
         <f>SUM(January:December!D52)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(January:December!E52)</f>
@@ -8054,23 +8054,23 @@
       </c>
       <c r="F52" s="7">
         <f>SUM(January:December!F52)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G52" s="7">
         <f>SUM(January:December!G52)</f>
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H52" s="7">
         <f>SUM(January:December!H52)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" s="7">
         <f>SUM(January:December!I52)</f>
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="J52" s="8">
         <f>SUM(January:December!J52)</f>
-        <v>496</v>
+        <v>528</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -8079,15 +8079,15 @@
       </c>
       <c r="B53" s="10">
         <f>SUM(January:December!B53)</f>
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C53" s="10">
         <f>SUM(January:December!C53)</f>
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D53" s="10">
         <f>SUM(January:December!D53)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E53" s="10">
         <f>SUM(January:December!E53)</f>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="G53" s="10">
         <f>SUM(January:December!G53)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H53" s="10">
         <f>SUM(January:December!H53)</f>
@@ -8107,11 +8107,11 @@
       </c>
       <c r="I53" s="10">
         <f>SUM(January:December!I53)</f>
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J53" s="11">
         <f>SUM(January:December!J53)</f>
-        <v>89</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -8120,39 +8120,39 @@
       </c>
       <c r="B54" s="7">
         <f>SUM(January:December!B54)</f>
-        <v>3078</v>
+        <v>3744</v>
       </c>
       <c r="C54" s="7">
         <f>SUM(January:December!C54)</f>
-        <v>1468</v>
+        <v>1774</v>
       </c>
       <c r="D54" s="7">
         <f>SUM(January:December!D54)</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(January:December!E54)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="7">
         <f>SUM(January:December!F54)</f>
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G54" s="7">
         <f>SUM(January:December!G54)</f>
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H54" s="7">
         <f>SUM(January:December!H54)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54" s="7">
         <f>SUM(January:December!I54)</f>
-        <v>892</v>
+        <v>1092</v>
       </c>
       <c r="J54" s="8">
         <f>SUM(January:December!J54)</f>
-        <v>2186</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -8161,27 +8161,27 @@
       </c>
       <c r="B55" s="31">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>2638</v>
+        <v>3197</v>
       </c>
       <c r="C55" s="31">
         <f t="shared" ref="C55:J55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>1279</v>
+        <v>1496</v>
       </c>
       <c r="D55" s="31">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E55" s="31">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F55" s="31">
         <f t="shared" si="0"/>
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="G55" s="31">
         <f t="shared" si="0"/>
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="H55" s="31">
         <f t="shared" si="0"/>
@@ -8189,11 +8189,11 @@
       </c>
       <c r="I55" s="31">
         <f t="shared" si="0"/>
-        <v>1268</v>
+        <v>1545</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>1370</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -8202,19 +8202,19 @@
       </c>
       <c r="B56" s="28">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C56" s="28">
         <f t="shared" ref="C56:J56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D56" s="28">
         <f t="shared" si="1"/>
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" si="1"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="G56" s="28">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="1"/>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="J56" s="29">
         <f t="shared" si="1"/>
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -8243,39 +8243,39 @@
       </c>
       <c r="B57" s="25">
         <f>SUM(B2:B54)</f>
-        <v>146911</v>
+        <v>177886</v>
       </c>
       <c r="C57" s="25">
         <f t="shared" ref="C57:J57" si="2">SUM(C2:C54)</f>
-        <v>62764</v>
+        <v>76089</v>
       </c>
       <c r="D57" s="25">
         <f t="shared" si="2"/>
-        <v>7302</v>
+        <v>8942</v>
       </c>
       <c r="E57" s="25">
         <f t="shared" si="2"/>
-        <v>551</v>
+        <v>669</v>
       </c>
       <c r="F57" s="25">
         <f t="shared" si="2"/>
-        <v>3760</v>
+        <v>4667</v>
       </c>
       <c r="G57" s="25">
         <f t="shared" si="2"/>
-        <v>11613</v>
+        <v>14278</v>
       </c>
       <c r="H57" s="25">
         <f t="shared" si="2"/>
-        <v>377</v>
+        <v>491</v>
       </c>
       <c r="I57" s="25">
         <f t="shared" si="2"/>
-        <v>34722</v>
+        <v>41691</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="2"/>
-        <v>112189</v>
+        <v>136195</v>
       </c>
     </row>
   </sheetData>
@@ -13931,743 +13931,1697 @@
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
+      <c r="B2" s="4">
+        <v>2312</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1009</v>
+      </c>
+      <c r="D2" s="4">
+        <v>93</v>
+      </c>
+      <c r="E2" s="4">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4">
+        <v>43</v>
+      </c>
+      <c r="G2" s="4">
+        <v>142</v>
+      </c>
+      <c r="H2" s="4">
+        <v>11</v>
+      </c>
+      <c r="I2" s="4">
+        <v>346</v>
+      </c>
+      <c r="J2" s="5">
+        <v>1966</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
+      <c r="B3" s="7">
+        <v>1210</v>
+      </c>
+      <c r="C3" s="7">
+        <v>416</v>
+      </c>
+      <c r="D3" s="7">
+        <v>45</v>
+      </c>
+      <c r="E3" s="7">
+        <v>10</v>
+      </c>
+      <c r="F3" s="7">
+        <v>25</v>
+      </c>
+      <c r="G3" s="7">
+        <v>80</v>
+      </c>
+      <c r="H3" s="7">
+        <v>2</v>
+      </c>
+      <c r="I3" s="7">
+        <v>154</v>
+      </c>
+      <c r="J3" s="8">
+        <v>1056</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
+      <c r="B4" s="10">
+        <v>1232</v>
+      </c>
+      <c r="C4" s="10">
+        <v>952</v>
+      </c>
+      <c r="D4" s="10">
+        <v>100</v>
+      </c>
+      <c r="E4" s="10">
+        <v>16</v>
+      </c>
+      <c r="F4" s="10">
+        <v>83</v>
+      </c>
+      <c r="G4" s="10">
+        <v>199</v>
+      </c>
+      <c r="H4" s="10">
+        <v>1</v>
+      </c>
+      <c r="I4" s="10">
+        <v>216</v>
+      </c>
+      <c r="J4" s="11">
+        <v>1016</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
+      <c r="B5" s="7">
+        <v>26</v>
+      </c>
+      <c r="C5" s="7">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>10</v>
+      </c>
+      <c r="J5" s="8">
+        <v>16</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="11"/>
+      <c r="B6" s="10">
+        <v>1302</v>
+      </c>
+      <c r="C6" s="10">
+        <v>954</v>
+      </c>
+      <c r="D6" s="10">
+        <v>287</v>
+      </c>
+      <c r="E6" s="10">
+        <v>5</v>
+      </c>
+      <c r="F6" s="10">
+        <v>104</v>
+      </c>
+      <c r="G6" s="10">
+        <v>396</v>
+      </c>
+      <c r="H6" s="10">
+        <v>16</v>
+      </c>
+      <c r="I6" s="10">
+        <v>362</v>
+      </c>
+      <c r="J6" s="11">
+        <v>940</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8"/>
+      <c r="B7" s="7">
+        <v>418</v>
+      </c>
+      <c r="C7" s="7">
+        <v>202</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7">
+        <v>3</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7">
+        <v>196</v>
+      </c>
+      <c r="J7" s="8">
+        <v>222</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="11"/>
+      <c r="B8" s="10">
+        <v>220</v>
+      </c>
+      <c r="C8" s="10">
+        <v>75</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10">
+        <v>3</v>
+      </c>
+      <c r="G8" s="10">
+        <v>5</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>36</v>
+      </c>
+      <c r="J8" s="11">
+        <v>184</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8"/>
+      <c r="B9" s="7">
+        <v>124</v>
+      </c>
+      <c r="C9" s="7">
+        <v>47</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>32</v>
+      </c>
+      <c r="J9" s="8">
+        <v>92</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="11"/>
+      <c r="B10" s="10">
+        <v>0</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
+      <c r="B11" s="7">
+        <v>0</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
+      <c r="B12" s="13">
+        <v>3</v>
+      </c>
+      <c r="C12" s="13">
+        <v>4</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>3</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
+      <c r="B13" s="16">
+        <v>116</v>
+      </c>
+      <c r="C13" s="16">
+        <v>50</v>
+      </c>
+      <c r="D13" s="16">
+        <v>6</v>
+      </c>
+      <c r="E13" s="16">
+        <v>2</v>
+      </c>
+      <c r="F13" s="16">
+        <v>4</v>
+      </c>
+      <c r="G13" s="16">
+        <v>12</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
+        <v>66</v>
+      </c>
+      <c r="J13" s="17">
+        <v>50</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
+      <c r="B14" s="13">
+        <v>302</v>
+      </c>
+      <c r="C14" s="13">
+        <v>122</v>
+      </c>
+      <c r="D14" s="13">
+        <v>5</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13">
+        <v>20</v>
+      </c>
+      <c r="G14" s="13">
+        <v>25</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>152</v>
+      </c>
+      <c r="J14" s="14">
+        <v>150</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
+      <c r="B15" s="16">
+        <v>138</v>
+      </c>
+      <c r="C15" s="16">
+        <v>41</v>
+      </c>
+      <c r="D15" s="16">
+        <v>7</v>
+      </c>
+      <c r="E15" s="16">
+        <v>0</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0</v>
+      </c>
+      <c r="G15" s="16">
+        <v>7</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0</v>
+      </c>
+      <c r="I15" s="16">
+        <v>56</v>
+      </c>
+      <c r="J15" s="17">
+        <v>82</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="11"/>
+      <c r="B16" s="10">
+        <v>96</v>
+      </c>
+      <c r="C16" s="10">
+        <v>48</v>
+      </c>
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10">
+        <v>3</v>
+      </c>
+      <c r="G16" s="10">
+        <v>5</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
+        <v>46</v>
+      </c>
+      <c r="J16" s="11">
+        <v>50</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="8"/>
+      <c r="B17" s="7">
+        <v>1158</v>
+      </c>
+      <c r="C17" s="7">
+        <v>429</v>
+      </c>
+      <c r="D17" s="7">
+        <v>71</v>
+      </c>
+      <c r="E17" s="7">
+        <v>5</v>
+      </c>
+      <c r="F17" s="7">
+        <v>22</v>
+      </c>
+      <c r="G17" s="7">
+        <v>98</v>
+      </c>
+      <c r="H17" s="7">
+        <v>1</v>
+      </c>
+      <c r="I17" s="7">
+        <v>338</v>
+      </c>
+      <c r="J17" s="8">
+        <v>820</v>
+      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="11"/>
+      <c r="B18" s="10">
+        <v>134</v>
+      </c>
+      <c r="C18" s="10">
+        <v>44</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10">
+        <v>3</v>
+      </c>
+      <c r="G18" s="10">
+        <v>4</v>
+      </c>
+      <c r="H18" s="10">
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
+        <v>40</v>
+      </c>
+      <c r="J18" s="11">
+        <v>94</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
+      <c r="B19" s="7">
+        <v>656</v>
+      </c>
+      <c r="C19" s="7">
+        <v>291</v>
+      </c>
+      <c r="D19" s="7">
+        <v>28</v>
+      </c>
+      <c r="E19" s="7">
+        <v>5</v>
+      </c>
+      <c r="F19" s="7">
+        <v>19</v>
+      </c>
+      <c r="G19" s="7">
+        <v>52</v>
+      </c>
+      <c r="H19" s="7">
+        <v>1</v>
+      </c>
+      <c r="I19" s="7">
+        <v>244</v>
+      </c>
+      <c r="J19" s="8">
+        <v>412</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="11"/>
+      <c r="B20" s="10">
+        <v>1</v>
+      </c>
+      <c r="C20" s="10">
+        <v>1</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0</v>
+      </c>
+      <c r="F20" s="10">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10">
+        <v>0</v>
+      </c>
+      <c r="H20" s="10">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10">
+        <v>0</v>
+      </c>
+      <c r="J20" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="8"/>
+      <c r="B21" s="7">
+        <v>1012</v>
+      </c>
+      <c r="C21" s="7">
+        <v>387</v>
+      </c>
+      <c r="D21" s="7">
+        <v>30</v>
+      </c>
+      <c r="E21" s="7">
+        <v>4</v>
+      </c>
+      <c r="F21" s="7">
+        <v>9</v>
+      </c>
+      <c r="G21" s="7">
+        <v>43</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0</v>
+      </c>
+      <c r="I21" s="7">
+        <v>282</v>
+      </c>
+      <c r="J21" s="8">
+        <v>730</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="11"/>
+      <c r="B22" s="10">
+        <v>110</v>
+      </c>
+      <c r="C22" s="10">
+        <v>62</v>
+      </c>
+      <c r="D22" s="10">
+        <v>1</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10">
+        <v>1</v>
+      </c>
+      <c r="G22" s="10">
+        <v>2</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
+        <v>46</v>
+      </c>
+      <c r="J22" s="11">
+        <v>64</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="8"/>
+      <c r="B23" s="7">
+        <v>668</v>
+      </c>
+      <c r="C23" s="7">
+        <v>215</v>
+      </c>
+      <c r="D23" s="7">
+        <v>100</v>
+      </c>
+      <c r="E23" s="7">
+        <v>5</v>
+      </c>
+      <c r="F23" s="7">
+        <v>20</v>
+      </c>
+      <c r="G23" s="7">
+        <v>125</v>
+      </c>
+      <c r="H23" s="7">
+        <v>2</v>
+      </c>
+      <c r="I23" s="7">
+        <v>104</v>
+      </c>
+      <c r="J23" s="8">
+        <v>564</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="11"/>
+      <c r="B24" s="10">
+        <v>4338</v>
+      </c>
+      <c r="C24" s="10">
+        <v>1685</v>
+      </c>
+      <c r="D24" s="10">
+        <v>170</v>
+      </c>
+      <c r="E24" s="10">
+        <v>9</v>
+      </c>
+      <c r="F24" s="10">
+        <v>164</v>
+      </c>
+      <c r="G24" s="10">
+        <v>343</v>
+      </c>
+      <c r="H24" s="10">
+        <v>8</v>
+      </c>
+      <c r="I24" s="10">
+        <v>544</v>
+      </c>
+      <c r="J24" s="11">
+        <v>3794</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="8"/>
+      <c r="B25" s="7">
+        <v>188</v>
+      </c>
+      <c r="C25" s="7">
+        <v>90</v>
+      </c>
+      <c r="D25" s="7">
+        <v>8</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0</v>
+      </c>
+      <c r="F25" s="7">
+        <v>7</v>
+      </c>
+      <c r="G25" s="7">
+        <v>15</v>
+      </c>
+      <c r="H25" s="7">
+        <v>1</v>
+      </c>
+      <c r="I25" s="7">
+        <v>78</v>
+      </c>
+      <c r="J25" s="8">
+        <v>110</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="11"/>
+      <c r="B26" s="10">
+        <v>0</v>
+      </c>
+      <c r="C26" s="10">
+        <v>0</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10">
+        <v>0</v>
+      </c>
+      <c r="J26" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="8"/>
+      <c r="B27" s="7">
+        <v>458</v>
+      </c>
+      <c r="C27" s="7">
+        <v>199</v>
+      </c>
+      <c r="D27" s="7">
+        <v>3</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1</v>
+      </c>
+      <c r="F27" s="7">
+        <v>7</v>
+      </c>
+      <c r="G27" s="7">
+        <v>11</v>
+      </c>
+      <c r="H27" s="7">
+        <v>1</v>
+      </c>
+      <c r="I27" s="7">
+        <v>96</v>
+      </c>
+      <c r="J27" s="8">
+        <v>362</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="11"/>
+      <c r="B28" s="10">
+        <v>278</v>
+      </c>
+      <c r="C28" s="10">
+        <v>102</v>
+      </c>
+      <c r="D28" s="10">
+        <v>12</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0</v>
+      </c>
+      <c r="F28" s="10">
+        <v>7</v>
+      </c>
+      <c r="G28" s="10">
+        <v>19</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
+        <v>94</v>
+      </c>
+      <c r="J28" s="11">
+        <v>184</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="8"/>
+      <c r="B29" s="7">
+        <v>1358</v>
+      </c>
+      <c r="C29" s="7">
+        <v>545</v>
+      </c>
+      <c r="D29" s="7">
+        <v>3</v>
+      </c>
+      <c r="E29" s="7">
+        <v>4</v>
+      </c>
+      <c r="F29" s="7">
+        <v>56</v>
+      </c>
+      <c r="G29" s="7">
+        <v>63</v>
+      </c>
+      <c r="H29" s="7">
+        <v>0</v>
+      </c>
+      <c r="I29" s="7">
+        <v>270</v>
+      </c>
+      <c r="J29" s="8">
+        <v>1088</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="11"/>
+      <c r="B30" s="10">
+        <v>60</v>
+      </c>
+      <c r="C30" s="10">
+        <v>22</v>
+      </c>
+      <c r="D30" s="10">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10">
+        <v>3</v>
+      </c>
+      <c r="G30" s="10">
+        <v>4</v>
+      </c>
+      <c r="H30" s="10">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10">
+        <v>22</v>
+      </c>
+      <c r="J30" s="11">
+        <v>38</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="8"/>
+      <c r="B31" s="7">
+        <v>224</v>
+      </c>
+      <c r="C31" s="7">
+        <v>72</v>
+      </c>
+      <c r="D31" s="7">
+        <v>2</v>
+      </c>
+      <c r="E31" s="7">
+        <v>5</v>
+      </c>
+      <c r="F31" s="7">
+        <v>2</v>
+      </c>
+      <c r="G31" s="7">
+        <v>9</v>
+      </c>
+      <c r="H31" s="7">
+        <v>1</v>
+      </c>
+      <c r="I31" s="7">
+        <v>22</v>
+      </c>
+      <c r="J31" s="8">
+        <v>202</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="11"/>
+      <c r="B32" s="10">
+        <v>924</v>
+      </c>
+      <c r="C32" s="10">
+        <v>309</v>
+      </c>
+      <c r="D32" s="10">
+        <v>99</v>
+      </c>
+      <c r="E32" s="10">
+        <v>2</v>
+      </c>
+      <c r="F32" s="10">
+        <v>49</v>
+      </c>
+      <c r="G32" s="10">
+        <v>150</v>
+      </c>
+      <c r="H32" s="10">
+        <v>15</v>
+      </c>
+      <c r="I32" s="10">
+        <v>338</v>
+      </c>
+      <c r="J32" s="11">
+        <v>586</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="8"/>
+      <c r="B33" s="7">
+        <v>802</v>
+      </c>
+      <c r="C33" s="7">
+        <v>329</v>
+      </c>
+      <c r="D33" s="7">
+        <v>8</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1</v>
+      </c>
+      <c r="F33" s="7">
+        <v>47</v>
+      </c>
+      <c r="G33" s="7">
+        <v>56</v>
+      </c>
+      <c r="H33" s="7">
+        <v>30</v>
+      </c>
+      <c r="I33" s="7">
+        <v>394</v>
+      </c>
+      <c r="J33" s="8">
+        <v>408</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="11"/>
+      <c r="B34" s="10">
+        <v>210</v>
+      </c>
+      <c r="C34" s="10">
+        <v>89</v>
+      </c>
+      <c r="D34" s="10">
+        <v>2</v>
+      </c>
+      <c r="E34" s="10">
+        <v>1</v>
+      </c>
+      <c r="F34" s="10">
+        <v>3</v>
+      </c>
+      <c r="G34" s="10">
+        <v>6</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
+        <v>104</v>
+      </c>
+      <c r="J34" s="11">
+        <v>106</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="8"/>
+      <c r="B35" s="7">
+        <v>2916</v>
+      </c>
+      <c r="C35" s="7">
+        <v>1129</v>
+      </c>
+      <c r="D35" s="7">
+        <v>217</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2</v>
+      </c>
+      <c r="F35" s="7">
+        <v>73</v>
+      </c>
+      <c r="G35" s="7">
+        <v>292</v>
+      </c>
+      <c r="H35" s="7">
+        <v>4</v>
+      </c>
+      <c r="I35" s="7">
+        <v>502</v>
+      </c>
+      <c r="J35" s="8">
+        <v>2414</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="11"/>
+      <c r="B36" s="10">
+        <v>306</v>
+      </c>
+      <c r="C36" s="10">
+        <v>127</v>
+      </c>
+      <c r="D36" s="10">
+        <v>13</v>
+      </c>
+      <c r="E36" s="10">
+        <v>2</v>
+      </c>
+      <c r="F36" s="10">
+        <v>9</v>
+      </c>
+      <c r="G36" s="10">
+        <v>24</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0</v>
+      </c>
+      <c r="I36" s="10">
+        <v>108</v>
+      </c>
+      <c r="J36" s="11">
+        <v>198</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="8"/>
+      <c r="B37" s="7">
+        <v>1042</v>
+      </c>
+      <c r="C37" s="7">
+        <v>376</v>
+      </c>
+      <c r="D37" s="7">
+        <v>94</v>
+      </c>
+      <c r="E37" s="7">
+        <v>2</v>
+      </c>
+      <c r="F37" s="7">
+        <v>13</v>
+      </c>
+      <c r="G37" s="7">
+        <v>109</v>
+      </c>
+      <c r="H37" s="7">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7">
+        <v>208</v>
+      </c>
+      <c r="J37" s="8">
+        <v>834</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="11"/>
+      <c r="B38" s="10">
+        <v>24</v>
+      </c>
+      <c r="C38" s="10">
+        <v>29</v>
+      </c>
+      <c r="D38" s="10">
+        <v>0</v>
+      </c>
+      <c r="E38" s="10">
+        <v>1</v>
+      </c>
+      <c r="F38" s="10">
+        <v>0</v>
+      </c>
+      <c r="G38" s="10">
+        <v>1</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0</v>
+      </c>
+      <c r="I38" s="10">
+        <v>16</v>
+      </c>
+      <c r="J38" s="11">
+        <v>8</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="8"/>
+      <c r="B39" s="7">
+        <v>162</v>
+      </c>
+      <c r="C39" s="7">
+        <v>72</v>
+      </c>
+      <c r="D39" s="7">
+        <v>30</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7">
+        <v>1</v>
+      </c>
+      <c r="G39" s="7">
+        <v>31</v>
+      </c>
+      <c r="H39" s="7">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7">
+        <v>74</v>
+      </c>
+      <c r="J39" s="8">
+        <v>88</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="20"/>
+      <c r="B40" s="19">
+        <v>0</v>
+      </c>
+      <c r="C40" s="19">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19">
+        <v>0</v>
+      </c>
+      <c r="F40" s="19">
+        <v>0</v>
+      </c>
+      <c r="G40" s="19">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19">
+        <v>0</v>
+      </c>
+      <c r="I40" s="19">
+        <v>0</v>
+      </c>
+      <c r="J40" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="23"/>
+      <c r="B41" s="22">
+        <v>0</v>
+      </c>
+      <c r="C41" s="22">
+        <v>2</v>
+      </c>
+      <c r="D41" s="22">
+        <v>10</v>
+      </c>
+      <c r="E41" s="22">
+        <v>1</v>
+      </c>
+      <c r="F41" s="22">
+        <v>0</v>
+      </c>
+      <c r="G41" s="22">
+        <v>11</v>
+      </c>
+      <c r="H41" s="22">
+        <v>0</v>
+      </c>
+      <c r="I41" s="22">
+        <v>0</v>
+      </c>
+      <c r="J41" s="23">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="20"/>
+      <c r="B42" s="19">
+        <v>1</v>
+      </c>
+      <c r="C42" s="19">
+        <v>0</v>
+      </c>
+      <c r="D42" s="19">
+        <v>0</v>
+      </c>
+      <c r="E42" s="19">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19">
+        <v>0</v>
+      </c>
+      <c r="G42" s="19">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19">
+        <v>0</v>
+      </c>
+      <c r="I42" s="19">
+        <v>0</v>
+      </c>
+      <c r="J42" s="20">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="23"/>
+      <c r="B43" s="22">
+        <v>0</v>
+      </c>
+      <c r="C43" s="22">
+        <v>0</v>
+      </c>
+      <c r="D43" s="22">
+        <v>1</v>
+      </c>
+      <c r="E43" s="22">
+        <v>0</v>
+      </c>
+      <c r="F43" s="22">
+        <v>0</v>
+      </c>
+      <c r="G43" s="22">
+        <v>1</v>
+      </c>
+      <c r="H43" s="22">
+        <v>0</v>
+      </c>
+      <c r="I43" s="22">
+        <v>0</v>
+      </c>
+      <c r="J43" s="23">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="8"/>
+      <c r="B44" s="7">
+        <v>100</v>
+      </c>
+      <c r="C44" s="7">
+        <v>47</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7">
+        <v>50</v>
+      </c>
+      <c r="J44" s="8">
+        <v>50</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="11"/>
+      <c r="B45" s="10">
+        <v>830</v>
+      </c>
+      <c r="C45" s="10">
+        <v>389</v>
+      </c>
+      <c r="D45" s="10">
+        <v>55</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1</v>
+      </c>
+      <c r="F45" s="10">
+        <v>11</v>
+      </c>
+      <c r="G45" s="10">
+        <v>67</v>
+      </c>
+      <c r="H45" s="10">
+        <v>0</v>
+      </c>
+      <c r="I45" s="10">
+        <v>196</v>
+      </c>
+      <c r="J45" s="11">
+        <v>634</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="8"/>
+      <c r="B46" s="7">
+        <v>1264</v>
+      </c>
+      <c r="C46" s="7">
+        <v>549</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7">
+        <v>6</v>
+      </c>
+      <c r="F46" s="7">
+        <v>14</v>
+      </c>
+      <c r="G46" s="7">
+        <v>20</v>
+      </c>
+      <c r="H46" s="7">
+        <v>1</v>
+      </c>
+      <c r="I46" s="7">
+        <v>168</v>
+      </c>
+      <c r="J46" s="8">
+        <v>1096</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="11"/>
+      <c r="B47" s="10">
+        <v>474</v>
+      </c>
+      <c r="C47" s="10">
+        <v>164</v>
+      </c>
+      <c r="D47" s="10">
+        <v>14</v>
+      </c>
+      <c r="E47" s="10">
+        <v>2</v>
+      </c>
+      <c r="F47" s="10">
+        <v>9</v>
+      </c>
+      <c r="G47" s="10">
+        <v>25</v>
+      </c>
+      <c r="H47" s="10">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10">
+        <v>98</v>
+      </c>
+      <c r="J47" s="11">
+        <v>376</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="8"/>
+      <c r="B48" s="7">
+        <v>406</v>
+      </c>
+      <c r="C48" s="7">
+        <v>197</v>
+      </c>
+      <c r="D48" s="7">
+        <v>13</v>
+      </c>
+      <c r="E48" s="7">
+        <v>2</v>
+      </c>
+      <c r="F48" s="7">
+        <v>5</v>
+      </c>
+      <c r="G48" s="7">
+        <v>20</v>
+      </c>
+      <c r="H48" s="7">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7">
+        <v>98</v>
+      </c>
+      <c r="J48" s="8">
+        <v>308</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="11"/>
+      <c r="B49" s="10">
+        <v>1914</v>
+      </c>
+      <c r="C49" s="10">
+        <v>790</v>
+      </c>
+      <c r="D49" s="10">
+        <v>61</v>
+      </c>
+      <c r="E49" s="10">
+        <v>6</v>
+      </c>
+      <c r="F49" s="10">
+        <v>36</v>
+      </c>
+      <c r="G49" s="10">
+        <v>103</v>
+      </c>
+      <c r="H49" s="10">
+        <v>17</v>
+      </c>
+      <c r="I49" s="10">
+        <v>398</v>
+      </c>
+      <c r="J49" s="11">
+        <v>1516</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="8"/>
+      <c r="B50" s="7">
+        <v>168</v>
+      </c>
+      <c r="C50" s="7">
+        <v>79</v>
+      </c>
+      <c r="D50" s="7">
+        <v>15</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1</v>
+      </c>
+      <c r="F50" s="7">
+        <v>1</v>
+      </c>
+      <c r="G50" s="7">
+        <v>17</v>
+      </c>
+      <c r="H50" s="7">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7">
+        <v>60</v>
+      </c>
+      <c r="J50" s="8">
+        <v>108</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="11"/>
+      <c r="B51" s="10">
+        <v>536</v>
+      </c>
+      <c r="C51" s="10">
+        <v>199</v>
+      </c>
+      <c r="D51" s="10">
+        <v>21</v>
+      </c>
+      <c r="E51" s="10">
+        <v>6</v>
+      </c>
+      <c r="F51" s="10">
+        <v>10</v>
+      </c>
+      <c r="G51" s="10">
+        <v>37</v>
+      </c>
+      <c r="H51" s="10">
+        <v>0</v>
+      </c>
+      <c r="I51" s="10">
+        <v>80</v>
+      </c>
+      <c r="J51" s="11">
+        <v>456</v>
+      </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="8"/>
+      <c r="B52" s="7">
+        <v>44</v>
+      </c>
+      <c r="C52" s="7">
+        <v>50</v>
+      </c>
+      <c r="D52" s="7">
+        <v>3</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>5</v>
+      </c>
+      <c r="G52" s="7">
+        <v>8</v>
+      </c>
+      <c r="H52" s="7">
+        <v>1</v>
+      </c>
+      <c r="I52" s="7">
+        <v>12</v>
+      </c>
+      <c r="J52" s="8">
+        <v>32</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="11"/>
+      <c r="B53" s="10">
+        <v>44</v>
+      </c>
+      <c r="C53" s="10">
+        <v>16</v>
+      </c>
+      <c r="D53" s="10">
+        <v>3</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0</v>
+      </c>
+      <c r="F53" s="10">
+        <v>0</v>
+      </c>
+      <c r="G53" s="10">
+        <v>3</v>
+      </c>
+      <c r="H53" s="10">
+        <v>0</v>
+      </c>
+      <c r="I53" s="10">
+        <v>10</v>
+      </c>
+      <c r="J53" s="11">
+        <v>34</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="8"/>
+      <c r="B54" s="7">
+        <v>666</v>
+      </c>
+      <c r="C54" s="7">
+        <v>306</v>
+      </c>
+      <c r="D54" s="7">
+        <v>5</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1</v>
+      </c>
+      <c r="F54" s="7">
+        <v>14</v>
+      </c>
+      <c r="G54" s="7">
+        <v>20</v>
+      </c>
+      <c r="H54" s="7">
+        <v>1</v>
+      </c>
+      <c r="I54" s="7">
+        <v>200</v>
+      </c>
+      <c r="J54" s="8">
+        <v>466</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
@@ -14675,27 +15629,27 @@
       </c>
       <c r="B55" s="31">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="C55" s="31">
         <f t="shared" ref="C55:J55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="D55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H55" s="31">
         <f t="shared" si="0"/>
@@ -14703,11 +15657,11 @@
       </c>
       <c r="I55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -14716,19 +15670,19 @@
       </c>
       <c r="B56" s="28">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="28">
         <f t="shared" ref="C56:J56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D56" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" si="1"/>
@@ -14736,7 +15690,7 @@
       </c>
       <c r="G56" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="1"/>
@@ -14748,7 +15702,7 @@
       </c>
       <c r="J56" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -14757,39 +15711,39 @@
       </c>
       <c r="B57" s="25">
         <f>SUM(B2:B54)</f>
-        <v>0</v>
+        <v>30975</v>
       </c>
       <c r="C57" s="25">
         <f t="shared" ref="C57:J57" si="2">SUM(C2:C54)</f>
-        <v>0</v>
+        <v>13325</v>
       </c>
       <c r="D57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1640</v>
       </c>
       <c r="E57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="F57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="G57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2665</v>
       </c>
       <c r="H57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="I57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6969</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24006</v>
       </c>
     </row>
   </sheetData>

--- a/statistics_files/2026/2026_99_gb_requests.xlsx
+++ b/statistics_files/2026/2026_99_gb_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DE30A3-1AEB-458F-9A86-931A59A88538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E2EE86-C309-4A56-A7C9-64214692946A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="843" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5988,39 +5988,39 @@
       </c>
       <c r="B2" s="4">
         <f>SUM(January:December!B2)</f>
-        <v>13470</v>
+        <v>16698</v>
       </c>
       <c r="C2" s="4">
         <f>SUM(January:December!C2)</f>
-        <v>6071</v>
+        <v>7313</v>
       </c>
       <c r="D2" s="4">
         <f>SUM(January:December!D2)</f>
-        <v>429</v>
+        <v>555</v>
       </c>
       <c r="E2" s="4">
         <f>SUM(January:December!E2)</f>
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="F2" s="4">
         <f>SUM(January:December!F2)</f>
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G2" s="4">
         <f>SUM(January:December!G2)</f>
-        <v>704</v>
+        <v>920</v>
       </c>
       <c r="H2" s="4">
         <f>SUM(January:December!H2)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I2" s="4">
         <f>SUM(January:December!I2)</f>
-        <v>1972</v>
+        <v>2462</v>
       </c>
       <c r="J2" s="5">
         <f>SUM(January:December!J2)</f>
-        <v>11498</v>
+        <v>14236</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6029,39 +6029,39 @@
       </c>
       <c r="B3" s="7">
         <f>SUM(January:December!B3)</f>
-        <v>5660</v>
+        <v>7026</v>
       </c>
       <c r="C3" s="7">
         <f>SUM(January:December!C3)</f>
-        <v>2410</v>
+        <v>2955</v>
       </c>
       <c r="D3" s="7">
         <f>SUM(January:December!D3)</f>
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="E3" s="7">
         <f>SUM(January:December!E3)</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F3" s="7">
         <f>SUM(January:December!F3)</f>
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="G3" s="7">
         <f>SUM(January:December!G3)</f>
-        <v>332</v>
+        <v>428</v>
       </c>
       <c r="H3" s="7">
         <f>SUM(January:December!H3)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I3" s="7">
         <f>SUM(January:December!I3)</f>
-        <v>838</v>
+        <v>1082</v>
       </c>
       <c r="J3" s="8">
         <f>SUM(January:December!J3)</f>
-        <v>4822</v>
+        <v>5944</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B4" s="10">
         <f>SUM(January:December!B4)</f>
-        <v>12168</v>
+        <v>14882</v>
       </c>
       <c r="C4" s="10">
         <f>SUM(January:December!C4)</f>
-        <v>5500</v>
+        <v>6643</v>
       </c>
       <c r="D4" s="10">
         <f>SUM(January:December!D4)</f>
-        <v>640</v>
+        <v>776</v>
       </c>
       <c r="E4" s="10">
         <f>SUM(January:December!E4)</f>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F4" s="10">
         <f>SUM(January:December!F4)</f>
-        <v>455</v>
+        <v>538</v>
       </c>
       <c r="G4" s="10">
         <f>SUM(January:December!G4)</f>
-        <v>1163</v>
+        <v>1392</v>
       </c>
       <c r="H4" s="10">
         <f>SUM(January:December!H4)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="10">
         <f>SUM(January:December!I4)</f>
-        <v>1982</v>
+        <v>2500</v>
       </c>
       <c r="J4" s="11">
         <f>SUM(January:December!J4)</f>
-        <v>10186</v>
+        <v>12382</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6111,15 +6111,15 @@
       </c>
       <c r="B5" s="7">
         <f>SUM(January:December!B5)</f>
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="C5" s="7">
         <f>SUM(January:December!C5)</f>
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D5" s="7">
         <f>SUM(January:December!D5)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E5" s="7">
         <f>SUM(January:December!E5)</f>
@@ -6127,11 +6127,11 @@
       </c>
       <c r="F5" s="7">
         <f>SUM(January:December!F5)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G5" s="7">
         <f>SUM(January:December!G5)</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H5" s="7">
         <f>SUM(January:December!H5)</f>
@@ -6139,11 +6139,11 @@
       </c>
       <c r="I5" s="7">
         <f>SUM(January:December!I5)</f>
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="J5" s="8">
         <f>SUM(January:December!J5)</f>
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -6152,39 +6152,39 @@
       </c>
       <c r="B6" s="10">
         <f>SUM(January:December!B6)</f>
-        <v>13242</v>
+        <v>15916</v>
       </c>
       <c r="C6" s="10">
         <f>SUM(January:December!C6)</f>
-        <v>5542</v>
+        <v>6590</v>
       </c>
       <c r="D6" s="10">
         <f>SUM(January:December!D6)</f>
-        <v>1408</v>
+        <v>1674</v>
       </c>
       <c r="E6" s="10">
         <f>SUM(January:December!E6)</f>
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F6" s="10">
         <f>SUM(January:December!F6)</f>
-        <v>343</v>
+        <v>405</v>
       </c>
       <c r="G6" s="10">
         <f>SUM(January:December!G6)</f>
-        <v>1776</v>
+        <v>2111</v>
       </c>
       <c r="H6" s="10">
         <f>SUM(January:December!H6)</f>
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I6" s="10">
         <f>SUM(January:December!I6)</f>
-        <v>3824</v>
+        <v>4782</v>
       </c>
       <c r="J6" s="11">
         <f>SUM(January:December!J6)</f>
-        <v>9418</v>
+        <v>11134</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -6193,15 +6193,15 @@
       </c>
       <c r="B7" s="7">
         <f>SUM(January:December!B7)</f>
-        <v>1704</v>
+        <v>2072</v>
       </c>
       <c r="C7" s="7">
         <f>SUM(January:December!C7)</f>
-        <v>817</v>
+        <v>946</v>
       </c>
       <c r="D7" s="7">
         <f>SUM(January:December!D7)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(January:December!E7)</f>
@@ -6209,23 +6209,23 @@
       </c>
       <c r="F7" s="7">
         <f>SUM(January:December!F7)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G7" s="7">
         <f>SUM(January:December!G7)</f>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H7" s="7">
         <f>SUM(January:December!H7)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="7">
         <f>SUM(January:December!I7)</f>
-        <v>622</v>
+        <v>714</v>
       </c>
       <c r="J7" s="8">
         <f>SUM(January:December!J7)</f>
-        <v>1082</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -6234,15 +6234,15 @@
       </c>
       <c r="B8" s="10">
         <f>SUM(January:December!B8)</f>
-        <v>1084</v>
+        <v>1272</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(January:December!C8)</f>
-        <v>459</v>
+        <v>559</v>
       </c>
       <c r="D8" s="10">
         <f>SUM(January:December!D8)</f>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8" s="10">
         <f>SUM(January:December!E8)</f>
@@ -6250,11 +6250,11 @@
       </c>
       <c r="F8" s="10">
         <f>SUM(January:December!F8)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G8" s="10">
         <f>SUM(January:December!G8)</f>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H8" s="10">
         <f>SUM(January:December!H8)</f>
@@ -6262,11 +6262,11 @@
       </c>
       <c r="I8" s="10">
         <f>SUM(January:December!I8)</f>
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="J8" s="11">
         <f>SUM(January:December!J8)</f>
-        <v>748</v>
+        <v>902</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -6275,11 +6275,11 @@
       </c>
       <c r="B9" s="7">
         <f>SUM(January:December!B9)</f>
-        <v>452</v>
+        <v>526</v>
       </c>
       <c r="C9" s="7">
         <f>SUM(January:December!C9)</f>
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="D9" s="7">
         <f>SUM(January:December!D9)</f>
@@ -6291,11 +6291,11 @@
       </c>
       <c r="F9" s="7">
         <f>SUM(January:December!F9)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="7">
         <f>SUM(January:December!G9)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H9" s="7">
         <f>SUM(January:December!H9)</f>
@@ -6303,11 +6303,11 @@
       </c>
       <c r="I9" s="7">
         <f>SUM(January:December!I9)</f>
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="J9" s="8">
         <f>SUM(January:December!J9)</f>
-        <v>342</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B10" s="10">
         <f>SUM(January:December!B10)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="10">
         <f>SUM(January:December!C10)</f>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="J10" s="11">
         <f>SUM(January:December!J10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -6398,11 +6398,11 @@
       </c>
       <c r="B12" s="13">
         <f>SUM(January:December!B12)</f>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(January:December!C12)</f>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D12" s="13">
         <f>SUM(January:December!D12)</f>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="I12" s="13">
         <f>SUM(January:December!I12)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J12" s="14">
         <f>SUM(January:December!J12)</f>
@@ -6439,15 +6439,15 @@
       </c>
       <c r="B13" s="16">
         <f>SUM(January:December!B13)</f>
-        <v>636</v>
+        <v>724</v>
       </c>
       <c r="C13" s="16">
         <f>SUM(January:December!C13)</f>
-        <v>298</v>
+        <v>331</v>
       </c>
       <c r="D13" s="16">
         <f>SUM(January:December!D13)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E13" s="16">
         <f>SUM(January:December!E13)</f>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="G13" s="16">
         <f>SUM(January:December!G13)</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H13" s="16">
         <f>SUM(January:December!H13)</f>
@@ -6467,11 +6467,11 @@
       </c>
       <c r="I13" s="16">
         <f>SUM(January:December!I13)</f>
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="J13" s="17">
         <f>SUM(January:December!J13)</f>
-        <v>336</v>
+        <v>386</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -6480,27 +6480,27 @@
       </c>
       <c r="B14" s="13">
         <f>SUM(January:December!B14)</f>
-        <v>1956</v>
+        <v>2284</v>
       </c>
       <c r="C14" s="13">
         <f>SUM(January:December!C14)</f>
-        <v>909</v>
+        <v>1075</v>
       </c>
       <c r="D14" s="13">
         <f>SUM(January:December!D14)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="13">
         <f>SUM(January:December!E14)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" s="13">
         <f>SUM(January:December!F14)</f>
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G14" s="13">
         <f>SUM(January:December!G14)</f>
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="H14" s="13">
         <f>SUM(January:December!H14)</f>
@@ -6508,11 +6508,11 @@
       </c>
       <c r="I14" s="13">
         <f>SUM(January:December!I14)</f>
-        <v>964</v>
+        <v>1112</v>
       </c>
       <c r="J14" s="14">
         <f>SUM(January:December!J14)</f>
-        <v>992</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -6521,27 +6521,27 @@
       </c>
       <c r="B15" s="16">
         <f>SUM(January:December!B15)</f>
-        <v>564</v>
+        <v>766</v>
       </c>
       <c r="C15" s="16">
         <f>SUM(January:December!C15)</f>
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="D15" s="16">
         <f>SUM(January:December!D15)</f>
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E15" s="16">
         <f>SUM(January:December!E15)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" s="16">
         <f>SUM(January:December!F15)</f>
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G15" s="16">
         <f>SUM(January:December!G15)</f>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="H15" s="16">
         <f>SUM(January:December!H15)</f>
@@ -6549,11 +6549,11 @@
       </c>
       <c r="I15" s="16">
         <f>SUM(January:December!I15)</f>
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="J15" s="17">
         <f>SUM(January:December!J15)</f>
-        <v>310</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -6562,11 +6562,11 @@
       </c>
       <c r="B16" s="10">
         <f>SUM(January:December!B16)</f>
-        <v>630</v>
+        <v>732</v>
       </c>
       <c r="C16" s="10">
         <f>SUM(January:December!C16)</f>
-        <v>309</v>
+        <v>357</v>
       </c>
       <c r="D16" s="10">
         <f>SUM(January:December!D16)</f>
@@ -6578,11 +6578,11 @@
       </c>
       <c r="F16" s="10">
         <f>SUM(January:December!F16)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G16" s="10">
         <f>SUM(January:December!G16)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H16" s="10">
         <f>SUM(January:December!H16)</f>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="I16" s="10">
         <f>SUM(January:December!I16)</f>
-        <v>296</v>
+        <v>356</v>
       </c>
       <c r="J16" s="11">
         <f>SUM(January:December!J16)</f>
-        <v>334</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -6603,27 +6603,27 @@
       </c>
       <c r="B17" s="7">
         <f>SUM(January:December!B17)</f>
-        <v>5976</v>
+        <v>7342</v>
       </c>
       <c r="C17" s="7">
         <f>SUM(January:December!C17)</f>
-        <v>2520</v>
+        <v>3080</v>
       </c>
       <c r="D17" s="7">
         <f>SUM(January:December!D17)</f>
-        <v>297</v>
+        <v>368</v>
       </c>
       <c r="E17" s="7">
         <f>SUM(January:December!E17)</f>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F17" s="7">
         <f>SUM(January:December!F17)</f>
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="G17" s="7">
         <f>SUM(January:December!G17)</f>
-        <v>451</v>
+        <v>562</v>
       </c>
       <c r="H17" s="7">
         <f>SUM(January:December!H17)</f>
@@ -6631,11 +6631,11 @@
       </c>
       <c r="I17" s="7">
         <f>SUM(January:December!I17)</f>
-        <v>1708</v>
+        <v>2156</v>
       </c>
       <c r="J17" s="8">
         <f>SUM(January:December!J17)</f>
-        <v>4268</v>
+        <v>5186</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -6644,15 +6644,15 @@
       </c>
       <c r="B18" s="10">
         <f>SUM(January:December!B18)</f>
-        <v>436</v>
+        <v>474</v>
       </c>
       <c r="C18" s="10">
         <f>SUM(January:December!C18)</f>
-        <v>239</v>
+        <v>279</v>
       </c>
       <c r="D18" s="10">
         <f>SUM(January:December!D18)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="10">
         <f>SUM(January:December!E18)</f>
@@ -6660,23 +6660,23 @@
       </c>
       <c r="F18" s="10">
         <f>SUM(January:December!F18)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="10">
         <f>SUM(January:December!G18)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(January:December!H18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="10">
         <f>SUM(January:December!I18)</f>
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="J18" s="11">
         <f>SUM(January:December!J18)</f>
-        <v>352</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -6685,27 +6685,27 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(January:December!B19)</f>
-        <v>4788</v>
+        <v>5468</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(January:December!C19)</f>
-        <v>2105</v>
+        <v>2372</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(January:December!D19)</f>
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(January:December!E19)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="7">
         <f>SUM(January:December!F19)</f>
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="G19" s="7">
         <f>SUM(January:December!G19)</f>
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="H19" s="7">
         <f>SUM(January:December!H19)</f>
@@ -6713,11 +6713,11 @@
       </c>
       <c r="I19" s="7">
         <f>SUM(January:December!I19)</f>
-        <v>1370</v>
+        <v>1570</v>
       </c>
       <c r="J19" s="8">
         <f>SUM(January:December!J19)</f>
-        <v>3418</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6742,11 +6742,11 @@
       </c>
       <c r="F20" s="10">
         <f>SUM(January:December!F20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="10">
         <f>SUM(January:December!G20)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="10">
         <f>SUM(January:December!H20)</f>
@@ -6767,39 +6767,39 @@
       </c>
       <c r="B21" s="7">
         <f>SUM(January:December!B21)</f>
-        <v>4640</v>
+        <v>5544</v>
       </c>
       <c r="C21" s="7">
         <f>SUM(January:December!C21)</f>
-        <v>2059</v>
+        <v>2491</v>
       </c>
       <c r="D21" s="7">
         <f>SUM(January:December!D21)</f>
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(January:December!E21)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="7">
         <f>SUM(January:December!F21)</f>
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G21" s="7">
         <f>SUM(January:December!G21)</f>
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H21" s="7">
         <f>SUM(January:December!H21)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I21" s="7">
         <f>SUM(January:December!I21)</f>
-        <v>1108</v>
+        <v>1338</v>
       </c>
       <c r="J21" s="8">
         <f>SUM(January:December!J21)</f>
-        <v>3532</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -6808,15 +6808,15 @@
       </c>
       <c r="B22" s="10">
         <f>SUM(January:December!B22)</f>
-        <v>690</v>
+        <v>778</v>
       </c>
       <c r="C22" s="10">
         <f>SUM(January:December!C22)</f>
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="D22" s="10">
         <f>SUM(January:December!D22)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="10">
         <f>SUM(January:December!E22)</f>
@@ -6824,11 +6824,11 @@
       </c>
       <c r="F22" s="10">
         <f>SUM(January:December!F22)</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G22" s="10">
         <f>SUM(January:December!G22)</f>
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H22" s="10">
         <f>SUM(January:December!H22)</f>
@@ -6836,11 +6836,11 @@
       </c>
       <c r="I22" s="10">
         <f>SUM(January:December!I22)</f>
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="J22" s="11">
         <f>SUM(January:December!J22)</f>
-        <v>474</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -6849,39 +6849,39 @@
       </c>
       <c r="B23" s="7">
         <f>SUM(January:December!B23)</f>
-        <v>6272</v>
+        <v>7598</v>
       </c>
       <c r="C23" s="7">
         <f>SUM(January:December!C23)</f>
-        <v>2073</v>
+        <v>2466</v>
       </c>
       <c r="D23" s="7">
         <f>SUM(January:December!D23)</f>
-        <v>780</v>
+        <v>939</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(January:December!E23)</f>
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F23" s="7">
         <f>SUM(January:December!F23)</f>
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="G23" s="7">
         <f>SUM(January:December!G23)</f>
-        <v>1069</v>
+        <v>1260</v>
       </c>
       <c r="H23" s="7">
         <f>SUM(January:December!H23)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I23" s="7">
         <f>SUM(January:December!I23)</f>
-        <v>1402</v>
+        <v>1674</v>
       </c>
       <c r="J23" s="8">
         <f>SUM(January:December!J23)</f>
-        <v>4870</v>
+        <v>5924</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -6890,39 +6890,39 @@
       </c>
       <c r="B24" s="10">
         <f>SUM(January:December!B24)</f>
-        <v>19584</v>
+        <v>23608</v>
       </c>
       <c r="C24" s="10">
         <f>SUM(January:December!C24)</f>
-        <v>8375</v>
+        <v>10048</v>
       </c>
       <c r="D24" s="10">
         <f>SUM(January:December!D24)</f>
-        <v>822</v>
+        <v>1056</v>
       </c>
       <c r="E24" s="10">
         <f>SUM(January:December!E24)</f>
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="F24" s="10">
         <f>SUM(January:December!F24)</f>
-        <v>489</v>
+        <v>583</v>
       </c>
       <c r="G24" s="10">
         <f>SUM(January:December!G24)</f>
-        <v>1395</v>
+        <v>1749</v>
       </c>
       <c r="H24" s="10">
         <f>SUM(January:December!H24)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I24" s="10">
         <f>SUM(January:December!I24)</f>
-        <v>2506</v>
+        <v>3174</v>
       </c>
       <c r="J24" s="11">
         <f>SUM(January:December!J24)</f>
-        <v>17078</v>
+        <v>20434</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -6931,15 +6931,15 @@
       </c>
       <c r="B25" s="7">
         <f>SUM(January:December!B25)</f>
-        <v>1352</v>
+        <v>1620</v>
       </c>
       <c r="C25" s="7">
         <f>SUM(January:December!C25)</f>
-        <v>595</v>
+        <v>705</v>
       </c>
       <c r="D25" s="7">
         <f>SUM(January:December!D25)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(January:December!E25)</f>
@@ -6947,11 +6947,11 @@
       </c>
       <c r="F25" s="7">
         <f>SUM(January:December!F25)</f>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G25" s="7">
         <f>SUM(January:December!G25)</f>
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="H25" s="7">
         <f>SUM(January:December!H25)</f>
@@ -6959,11 +6959,11 @@
       </c>
       <c r="I25" s="7">
         <f>SUM(January:December!I25)</f>
-        <v>424</v>
+        <v>494</v>
       </c>
       <c r="J25" s="8">
         <f>SUM(January:December!J25)</f>
-        <v>928</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -7013,15 +7013,15 @@
       </c>
       <c r="B27" s="7">
         <f>SUM(January:December!B27)</f>
-        <v>1648</v>
+        <v>2014</v>
       </c>
       <c r="C27" s="7">
         <f>SUM(January:December!C27)</f>
-        <v>764</v>
+        <v>947</v>
       </c>
       <c r="D27" s="7">
         <f>SUM(January:December!D27)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(January:December!E27)</f>
@@ -7029,23 +7029,23 @@
       </c>
       <c r="F27" s="7">
         <f>SUM(January:December!F27)</f>
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G27" s="7">
         <f>SUM(January:December!G27)</f>
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="H27" s="7">
         <f>SUM(January:December!H27)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27" s="7">
         <f>SUM(January:December!I27)</f>
-        <v>496</v>
+        <v>598</v>
       </c>
       <c r="J27" s="8">
         <f>SUM(January:December!J27)</f>
-        <v>1152</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -7054,15 +7054,15 @@
       </c>
       <c r="B28" s="10">
         <f>SUM(January:December!B28)</f>
-        <v>1221</v>
+        <v>1549</v>
       </c>
       <c r="C28" s="10">
         <f>SUM(January:December!C28)</f>
-        <v>530</v>
+        <v>669</v>
       </c>
       <c r="D28" s="10">
         <f>SUM(January:December!D28)</f>
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E28" s="10">
         <f>SUM(January:December!E28)</f>
@@ -7070,11 +7070,11 @@
       </c>
       <c r="F28" s="10">
         <f>SUM(January:December!F28)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G28" s="10">
         <f>SUM(January:December!G28)</f>
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="H28" s="10">
         <f>SUM(January:December!H28)</f>
@@ -7082,11 +7082,11 @@
       </c>
       <c r="I28" s="10">
         <f>SUM(January:December!I28)</f>
-        <v>394</v>
+        <v>506</v>
       </c>
       <c r="J28" s="11">
         <f>SUM(January:December!J28)</f>
-        <v>827</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -7095,39 +7095,39 @@
       </c>
       <c r="B29" s="7">
         <f>SUM(January:December!B29)</f>
-        <v>6526</v>
+        <v>7964</v>
       </c>
       <c r="C29" s="7">
         <f>SUM(January:December!C29)</f>
-        <v>3030</v>
+        <v>3746</v>
       </c>
       <c r="D29" s="7">
         <f>SUM(January:December!D29)</f>
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(January:December!E29)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F29" s="7">
         <f>SUM(January:December!F29)</f>
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="G29" s="7">
         <f>SUM(January:December!G29)</f>
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="H29" s="7">
         <f>SUM(January:December!H29)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="7">
         <f>SUM(January:December!I29)</f>
-        <v>1574</v>
+        <v>2002</v>
       </c>
       <c r="J29" s="8">
         <f>SUM(January:December!J29)</f>
-        <v>4952</v>
+        <v>5962</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -7136,15 +7136,15 @@
       </c>
       <c r="B30" s="10">
         <f>SUM(January:December!B30)</f>
-        <v>280</v>
+        <v>328</v>
       </c>
       <c r="C30" s="10">
         <f>SUM(January:December!C30)</f>
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D30" s="10">
         <f>SUM(January:December!D30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="10">
         <f>SUM(January:December!E30)</f>
@@ -7152,11 +7152,11 @@
       </c>
       <c r="F30" s="10">
         <f>SUM(January:December!F30)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G30" s="10">
         <f>SUM(January:December!G30)</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H30" s="10">
         <f>SUM(January:December!H30)</f>
@@ -7164,11 +7164,11 @@
       </c>
       <c r="I30" s="10">
         <f>SUM(January:December!I30)</f>
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="J30" s="11">
         <f>SUM(January:December!J30)</f>
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -7177,15 +7177,15 @@
       </c>
       <c r="B31" s="7">
         <f>SUM(January:December!B31)</f>
-        <v>1001</v>
+        <v>1035</v>
       </c>
       <c r="C31" s="7">
         <f>SUM(January:December!C31)</f>
-        <v>426</v>
+        <v>483</v>
       </c>
       <c r="D31" s="7">
         <f>SUM(January:December!D31)</f>
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(January:December!E31)</f>
@@ -7193,23 +7193,23 @@
       </c>
       <c r="F31" s="7">
         <f>SUM(January:December!F31)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G31" s="7">
         <f>SUM(January:December!G31)</f>
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H31" s="7">
         <f>SUM(January:December!H31)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" s="7">
         <f>SUM(January:December!I31)</f>
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="J31" s="8">
         <f>SUM(January:December!J31)</f>
-        <v>909</v>
+        <v>925</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -7218,39 +7218,39 @@
       </c>
       <c r="B32" s="10">
         <f>SUM(January:December!B32)</f>
-        <v>4924</v>
+        <v>5858</v>
       </c>
       <c r="C32" s="10">
         <f>SUM(January:December!C32)</f>
-        <v>1753</v>
+        <v>2088</v>
       </c>
       <c r="D32" s="10">
         <f>SUM(January:December!D32)</f>
-        <v>444</v>
+        <v>503</v>
       </c>
       <c r="E32" s="10">
         <f>SUM(January:December!E32)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F32" s="10">
         <f>SUM(January:December!F32)</f>
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="G32" s="10">
         <f>SUM(January:December!G32)</f>
-        <v>680</v>
+        <v>787</v>
       </c>
       <c r="H32" s="10">
         <f>SUM(January:December!H32)</f>
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="I32" s="10">
         <f>SUM(January:December!I32)</f>
-        <v>1944</v>
+        <v>2336</v>
       </c>
       <c r="J32" s="11">
         <f>SUM(January:December!J32)</f>
-        <v>2980</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -7259,39 +7259,39 @@
       </c>
       <c r="B33" s="7">
         <f>SUM(January:December!B33)</f>
-        <v>4186</v>
+        <v>4888</v>
       </c>
       <c r="C33" s="7">
         <f>SUM(January:December!C33)</f>
-        <v>1737</v>
+        <v>2068</v>
       </c>
       <c r="D33" s="7">
         <f>SUM(January:December!D33)</f>
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(January:December!E33)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F33" s="7">
         <f>SUM(January:December!F33)</f>
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="G33" s="7">
         <f>SUM(January:December!G33)</f>
-        <v>287</v>
+        <v>337</v>
       </c>
       <c r="H33" s="7">
         <f>SUM(January:December!H33)</f>
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="I33" s="7">
         <f>SUM(January:December!I33)</f>
-        <v>1776</v>
+        <v>2094</v>
       </c>
       <c r="J33" s="8">
         <f>SUM(January:December!J33)</f>
-        <v>2410</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -7300,15 +7300,15 @@
       </c>
       <c r="B34" s="10">
         <f>SUM(January:December!B34)</f>
-        <v>1256</v>
+        <v>1504</v>
       </c>
       <c r="C34" s="10">
         <f>SUM(January:December!C34)</f>
-        <v>570</v>
+        <v>678</v>
       </c>
       <c r="D34" s="10">
         <f>SUM(January:December!D34)</f>
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E34" s="10">
         <f>SUM(January:December!E34)</f>
@@ -7316,11 +7316,11 @@
       </c>
       <c r="F34" s="10">
         <f>SUM(January:December!F34)</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G34" s="10">
         <f>SUM(January:December!G34)</f>
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="H34" s="10">
         <f>SUM(January:December!H34)</f>
@@ -7328,11 +7328,11 @@
       </c>
       <c r="I34" s="10">
         <f>SUM(January:December!I34)</f>
-        <v>456</v>
+        <v>554</v>
       </c>
       <c r="J34" s="11">
         <f>SUM(January:December!J34)</f>
-        <v>800</v>
+        <v>950</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -7341,39 +7341,39 @@
       </c>
       <c r="B35" s="7">
         <f>SUM(January:December!B35)</f>
-        <v>14082</v>
+        <v>16682</v>
       </c>
       <c r="C35" s="7">
         <f>SUM(January:December!C35)</f>
-        <v>5680</v>
+        <v>6801</v>
       </c>
       <c r="D35" s="7">
         <f>SUM(January:December!D35)</f>
-        <v>967</v>
+        <v>1170</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(January:December!E35)</f>
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F35" s="7">
         <f>SUM(January:December!F35)</f>
-        <v>297</v>
+        <v>366</v>
       </c>
       <c r="G35" s="7">
         <f>SUM(January:December!G35)</f>
-        <v>1297</v>
+        <v>1577</v>
       </c>
       <c r="H35" s="7">
         <f>SUM(January:December!H35)</f>
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I35" s="7">
         <f>SUM(January:December!I35)</f>
-        <v>3150</v>
+        <v>3660</v>
       </c>
       <c r="J35" s="8">
         <f>SUM(January:December!J35)</f>
-        <v>10932</v>
+        <v>13022</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -7382,15 +7382,15 @@
       </c>
       <c r="B36" s="10">
         <f>SUM(January:December!B36)</f>
-        <v>1664</v>
+        <v>1990</v>
       </c>
       <c r="C36" s="10">
         <f>SUM(January:December!C36)</f>
-        <v>742</v>
+        <v>878</v>
       </c>
       <c r="D36" s="10">
         <f>SUM(January:December!D36)</f>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E36" s="10">
         <f>SUM(January:December!E36)</f>
@@ -7398,23 +7398,23 @@
       </c>
       <c r="F36" s="10">
         <f>SUM(January:December!F36)</f>
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G36" s="10">
         <f>SUM(January:December!G36)</f>
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H36" s="10">
         <f>SUM(January:December!H36)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I36" s="10">
         <f>SUM(January:December!I36)</f>
-        <v>560</v>
+        <v>682</v>
       </c>
       <c r="J36" s="11">
         <f>SUM(January:December!J36)</f>
-        <v>1104</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -7423,27 +7423,27 @@
       </c>
       <c r="B37" s="7">
         <f>SUM(January:December!B37)</f>
-        <v>5674</v>
+        <v>6800</v>
       </c>
       <c r="C37" s="7">
         <f>SUM(January:December!C37)</f>
-        <v>2081</v>
+        <v>2484</v>
       </c>
       <c r="D37" s="7">
         <f>SUM(January:December!D37)</f>
-        <v>534</v>
+        <v>666</v>
       </c>
       <c r="E37" s="7">
         <f>SUM(January:December!E37)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F37" s="7">
         <f>SUM(January:December!F37)</f>
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="G37" s="7">
         <f>SUM(January:December!G37)</f>
-        <v>736</v>
+        <v>910</v>
       </c>
       <c r="H37" s="7">
         <f>SUM(January:December!H37)</f>
@@ -7451,11 +7451,11 @@
       </c>
       <c r="I37" s="7">
         <f>SUM(January:December!I37)</f>
-        <v>1440</v>
+        <v>1758</v>
       </c>
       <c r="J37" s="8">
         <f>SUM(January:December!J37)</f>
-        <v>4234</v>
+        <v>5042</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -7464,11 +7464,11 @@
       </c>
       <c r="B38" s="10">
         <f>SUM(January:December!B38)</f>
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="C38" s="10">
         <f>SUM(January:December!C38)</f>
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="D38" s="10">
         <f>SUM(January:December!D38)</f>
@@ -7476,15 +7476,15 @@
       </c>
       <c r="E38" s="10">
         <f>SUM(January:December!E38)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="10">
         <f>SUM(January:December!F38)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="10">
         <f>SUM(January:December!G38)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H38" s="10">
         <f>SUM(January:December!H38)</f>
@@ -7492,11 +7492,11 @@
       </c>
       <c r="I38" s="10">
         <f>SUM(January:December!I38)</f>
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="J38" s="11">
         <f>SUM(January:December!J38)</f>
-        <v>231</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -7505,15 +7505,15 @@
       </c>
       <c r="B39" s="7">
         <f>SUM(January:December!B39)</f>
-        <v>1898</v>
+        <v>1967</v>
       </c>
       <c r="C39" s="7">
         <f>SUM(January:December!C39)</f>
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="D39" s="7">
         <f>SUM(January:December!D39)</f>
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(January:December!E39)</f>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="G39" s="7">
         <f>SUM(January:December!G39)</f>
-        <v>728</v>
+        <v>756</v>
       </c>
       <c r="H39" s="7">
         <f>SUM(January:December!H39)</f>
@@ -7533,11 +7533,11 @@
       </c>
       <c r="I39" s="7">
         <f>SUM(January:December!I39)</f>
-        <v>936</v>
+        <v>966</v>
       </c>
       <c r="J39" s="8">
         <f>SUM(January:December!J39)</f>
-        <v>962</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="C42" s="19">
         <f>SUM(January:December!C42)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D42" s="19">
         <f>SUM(January:December!D42)</f>
@@ -7710,15 +7710,15 @@
       </c>
       <c r="B44" s="7">
         <f>SUM(January:December!B44)</f>
-        <v>500</v>
+        <v>608</v>
       </c>
       <c r="C44" s="7">
         <f>SUM(January:December!C44)</f>
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="D44" s="7">
         <f>SUM(January:December!D44)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" s="7">
         <f>SUM(January:December!E44)</f>
@@ -7726,11 +7726,11 @@
       </c>
       <c r="F44" s="7">
         <f>SUM(January:December!F44)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G44" s="7">
         <f>SUM(January:December!G44)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H44" s="7">
         <f>SUM(January:December!H44)</f>
@@ -7738,11 +7738,11 @@
       </c>
       <c r="I44" s="7">
         <f>SUM(January:December!I44)</f>
-        <v>216</v>
+        <v>278</v>
       </c>
       <c r="J44" s="8">
         <f>SUM(January:December!J44)</f>
-        <v>284</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -7751,39 +7751,39 @@
       </c>
       <c r="B45" s="10">
         <f>SUM(January:December!B45)</f>
-        <v>4646</v>
+        <v>5512</v>
       </c>
       <c r="C45" s="10">
         <f>SUM(January:December!C45)</f>
-        <v>2101</v>
+        <v>2448</v>
       </c>
       <c r="D45" s="10">
         <f>SUM(January:December!D45)</f>
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="E45" s="10">
         <f>SUM(January:December!E45)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F45" s="10">
         <f>SUM(January:December!F45)</f>
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="G45" s="10">
         <f>SUM(January:December!G45)</f>
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="H45" s="10">
         <f>SUM(January:December!H45)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="10">
         <f>SUM(January:December!I45)</f>
-        <v>1344</v>
+        <v>1724</v>
       </c>
       <c r="J45" s="11">
         <f>SUM(January:December!J45)</f>
-        <v>3302</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -7792,11 +7792,11 @@
       </c>
       <c r="B46" s="7">
         <f>SUM(January:December!B46)</f>
-        <v>7108</v>
+        <v>8414</v>
       </c>
       <c r="C46" s="7">
         <f>SUM(January:December!C46)</f>
-        <v>3448</v>
+        <v>4035</v>
       </c>
       <c r="D46" s="7">
         <f>SUM(January:December!D46)</f>
@@ -7804,15 +7804,15 @@
       </c>
       <c r="E46" s="7">
         <f>SUM(January:December!E46)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F46" s="7">
         <f>SUM(January:December!F46)</f>
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G46" s="7">
         <f>SUM(January:December!G46)</f>
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="H46" s="7">
         <f>SUM(January:December!H46)</f>
@@ -7820,11 +7820,11 @@
       </c>
       <c r="I46" s="7">
         <f>SUM(January:December!I46)</f>
-        <v>872</v>
+        <v>1110</v>
       </c>
       <c r="J46" s="8">
         <f>SUM(January:December!J46)</f>
-        <v>6236</v>
+        <v>7304</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -7833,27 +7833,27 @@
       </c>
       <c r="B47" s="10">
         <f>SUM(January:December!B47)</f>
-        <v>2258</v>
+        <v>2656</v>
       </c>
       <c r="C47" s="10">
         <f>SUM(January:December!C47)</f>
-        <v>911</v>
+        <v>1125</v>
       </c>
       <c r="D47" s="10">
         <f>SUM(January:December!D47)</f>
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E47" s="10">
         <f>SUM(January:December!E47)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F47" s="10">
         <f>SUM(January:December!F47)</f>
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="G47" s="10">
         <f>SUM(January:December!G47)</f>
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="H47" s="10">
         <f>SUM(January:December!H47)</f>
@@ -7861,11 +7861,11 @@
       </c>
       <c r="I47" s="10">
         <f>SUM(January:December!I47)</f>
-        <v>438</v>
+        <v>554</v>
       </c>
       <c r="J47" s="11">
         <f>SUM(January:December!J47)</f>
-        <v>1820</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -7874,27 +7874,27 @@
       </c>
       <c r="B48" s="7">
         <f>SUM(January:December!B48)</f>
-        <v>3354</v>
+        <v>3992</v>
       </c>
       <c r="C48" s="7">
         <f>SUM(January:December!C48)</f>
-        <v>1429</v>
+        <v>1613</v>
       </c>
       <c r="D48" s="7">
         <f>SUM(January:December!D48)</f>
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(January:December!E48)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(January:December!F48)</f>
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="G48" s="7">
         <f>SUM(January:December!G48)</f>
-        <v>271</v>
+        <v>382</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(January:December!H48)</f>
@@ -7902,11 +7902,11 @@
       </c>
       <c r="I48" s="7">
         <f>SUM(January:December!I48)</f>
-        <v>622</v>
+        <v>738</v>
       </c>
       <c r="J48" s="8">
         <f>SUM(January:December!J48)</f>
-        <v>2732</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -7915,39 +7915,39 @@
       </c>
       <c r="B49" s="10">
         <f>SUM(January:December!B49)</f>
-        <v>8812</v>
+        <v>10870</v>
       </c>
       <c r="C49" s="10">
         <f>SUM(January:December!C49)</f>
-        <v>3784</v>
+        <v>4647</v>
       </c>
       <c r="D49" s="10">
         <f>SUM(January:December!D49)</f>
-        <v>339</v>
+        <v>405</v>
       </c>
       <c r="E49" s="10">
         <f>SUM(January:December!E49)</f>
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F49" s="10">
         <f>SUM(January:December!F49)</f>
-        <v>214</v>
+        <v>254</v>
       </c>
       <c r="G49" s="10">
         <f>SUM(January:December!G49)</f>
-        <v>576</v>
+        <v>692</v>
       </c>
       <c r="H49" s="10">
         <f>SUM(January:December!H49)</f>
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="I49" s="10">
         <f>SUM(January:December!I49)</f>
-        <v>1826</v>
+        <v>2254</v>
       </c>
       <c r="J49" s="11">
         <f>SUM(January:December!J49)</f>
-        <v>6986</v>
+        <v>8616</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -7956,27 +7956,27 @@
       </c>
       <c r="B50" s="7">
         <f>SUM(January:December!B50)</f>
-        <v>1182</v>
+        <v>1289</v>
       </c>
       <c r="C50" s="7">
         <f>SUM(January:December!C50)</f>
-        <v>481</v>
+        <v>562</v>
       </c>
       <c r="D50" s="7">
         <f>SUM(January:December!D50)</f>
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="E50" s="7">
         <f>SUM(January:December!E50)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F50" s="7">
         <f>SUM(January:December!F50)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G50" s="7">
         <f>SUM(January:December!G50)</f>
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="H50" s="7">
         <f>SUM(January:December!H50)</f>
@@ -7984,11 +7984,11 @@
       </c>
       <c r="I50" s="7">
         <f>SUM(January:December!I50)</f>
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="J50" s="8">
         <f>SUM(January:December!J50)</f>
-        <v>772</v>
+        <v>851</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -7997,15 +7997,15 @@
       </c>
       <c r="B51" s="10">
         <f>SUM(January:December!B51)</f>
-        <v>4072</v>
+        <v>4620</v>
       </c>
       <c r="C51" s="10">
         <f>SUM(January:December!C51)</f>
-        <v>1756</v>
+        <v>2018</v>
       </c>
       <c r="D51" s="10">
         <f>SUM(January:December!D51)</f>
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="E51" s="10">
         <f>SUM(January:December!E51)</f>
@@ -8013,23 +8013,23 @@
       </c>
       <c r="F51" s="10">
         <f>SUM(January:December!F51)</f>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G51" s="10">
         <f>SUM(January:December!G51)</f>
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="H51" s="10">
         <f>SUM(January:December!H51)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="10">
         <f>SUM(January:December!I51)</f>
-        <v>588</v>
+        <v>692</v>
       </c>
       <c r="J51" s="11">
         <f>SUM(January:December!J51)</f>
-        <v>3484</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -8038,15 +8038,15 @@
       </c>
       <c r="B52" s="7">
         <f>SUM(January:December!B52)</f>
-        <v>770</v>
+        <v>825</v>
       </c>
       <c r="C52" s="7">
         <f>SUM(January:December!C52)</f>
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="D52" s="7">
         <f>SUM(January:December!D52)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(January:December!E52)</f>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="G52" s="7">
         <f>SUM(January:December!G52)</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H52" s="7">
         <f>SUM(January:December!H52)</f>
@@ -8066,11 +8066,11 @@
       </c>
       <c r="I52" s="7">
         <f>SUM(January:December!I52)</f>
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="J52" s="8">
         <f>SUM(January:December!J52)</f>
-        <v>528</v>
+        <v>571</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -8079,15 +8079,15 @@
       </c>
       <c r="B53" s="10">
         <f>SUM(January:December!B53)</f>
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="C53" s="10">
         <f>SUM(January:December!C53)</f>
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D53" s="10">
         <f>SUM(January:December!D53)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E53" s="10">
         <f>SUM(January:December!E53)</f>
@@ -8095,11 +8095,11 @@
       </c>
       <c r="F53" s="10">
         <f>SUM(January:December!F53)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G53" s="10">
         <f>SUM(January:December!G53)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H53" s="10">
         <f>SUM(January:December!H53)</f>
@@ -8107,11 +8107,11 @@
       </c>
       <c r="I53" s="10">
         <f>SUM(January:December!I53)</f>
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J53" s="11">
         <f>SUM(January:December!J53)</f>
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -8120,39 +8120,39 @@
       </c>
       <c r="B54" s="7">
         <f>SUM(January:December!B54)</f>
-        <v>3744</v>
+        <v>4316</v>
       </c>
       <c r="C54" s="7">
         <f>SUM(January:December!C54)</f>
-        <v>1774</v>
+        <v>2070</v>
       </c>
       <c r="D54" s="7">
         <f>SUM(January:December!D54)</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(January:December!E54)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" s="7">
         <f>SUM(January:December!F54)</f>
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G54" s="7">
         <f>SUM(January:December!G54)</f>
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="H54" s="7">
         <f>SUM(January:December!H54)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
         <f>SUM(January:December!I54)</f>
-        <v>1092</v>
+        <v>1372</v>
       </c>
       <c r="J54" s="8">
         <f>SUM(January:December!J54)</f>
-        <v>2652</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -8161,27 +8161,27 @@
       </c>
       <c r="B55" s="31">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>3197</v>
+        <v>3819</v>
       </c>
       <c r="C55" s="31">
         <f t="shared" ref="C55:J55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>1496</v>
+        <v>1772</v>
       </c>
       <c r="D55" s="31">
         <f t="shared" si="0"/>
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E55" s="31">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F55" s="31">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="G55" s="31">
         <f t="shared" si="0"/>
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="H55" s="31">
         <f t="shared" si="0"/>
@@ -8189,11 +8189,11 @@
       </c>
       <c r="I55" s="31">
         <f t="shared" si="0"/>
-        <v>1545</v>
+        <v>1827</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>1652</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="C56" s="28">
         <f t="shared" ref="C56:J56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D56" s="28">
         <f t="shared" si="1"/>
@@ -8243,39 +8243,39 @@
       </c>
       <c r="B57" s="25">
         <f>SUM(B2:B54)</f>
-        <v>177886</v>
+        <v>212966</v>
       </c>
       <c r="C57" s="25">
         <f t="shared" ref="C57:J57" si="2">SUM(C2:C54)</f>
-        <v>76089</v>
+        <v>90810</v>
       </c>
       <c r="D57" s="25">
         <f t="shared" si="2"/>
-        <v>8942</v>
+        <v>10788</v>
       </c>
       <c r="E57" s="25">
         <f t="shared" si="2"/>
-        <v>669</v>
+        <v>808</v>
       </c>
       <c r="F57" s="25">
         <f t="shared" si="2"/>
-        <v>4667</v>
+        <v>5563</v>
       </c>
       <c r="G57" s="25">
         <f t="shared" si="2"/>
-        <v>14278</v>
+        <v>17159</v>
       </c>
       <c r="H57" s="25">
         <f t="shared" si="2"/>
-        <v>491</v>
+        <v>617</v>
       </c>
       <c r="I57" s="25">
         <f t="shared" si="2"/>
-        <v>41691</v>
+        <v>50653</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="2"/>
-        <v>136195</v>
+        <v>162313</v>
       </c>
     </row>
   </sheetData>
@@ -15798,743 +15798,1697 @@
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
+      <c r="B2" s="4">
+        <v>3228</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1242</v>
+      </c>
+      <c r="D2" s="4">
+        <v>126</v>
+      </c>
+      <c r="E2" s="4">
+        <v>27</v>
+      </c>
+      <c r="F2" s="4">
+        <v>63</v>
+      </c>
+      <c r="G2" s="4">
+        <v>216</v>
+      </c>
+      <c r="H2" s="4">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
+        <v>490</v>
+      </c>
+      <c r="J2" s="5">
+        <v>2738</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
+      <c r="B3" s="7">
+        <v>1366</v>
+      </c>
+      <c r="C3" s="7">
+        <v>545</v>
+      </c>
+      <c r="D3" s="7">
+        <v>68</v>
+      </c>
+      <c r="E3" s="7">
+        <v>5</v>
+      </c>
+      <c r="F3" s="7">
+        <v>23</v>
+      </c>
+      <c r="G3" s="7">
+        <v>96</v>
+      </c>
+      <c r="H3" s="7">
+        <v>4</v>
+      </c>
+      <c r="I3" s="7">
+        <v>244</v>
+      </c>
+      <c r="J3" s="8">
+        <v>1122</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
+      <c r="B4" s="10">
+        <v>2714</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1143</v>
+      </c>
+      <c r="D4" s="10">
+        <v>136</v>
+      </c>
+      <c r="E4" s="10">
+        <v>10</v>
+      </c>
+      <c r="F4" s="10">
+        <v>83</v>
+      </c>
+      <c r="G4" s="10">
+        <v>229</v>
+      </c>
+      <c r="H4" s="10">
+        <v>1</v>
+      </c>
+      <c r="I4" s="10">
+        <v>518</v>
+      </c>
+      <c r="J4" s="11">
+        <v>2196</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
+      <c r="B5" s="7">
+        <v>72</v>
+      </c>
+      <c r="C5" s="7">
+        <v>27</v>
+      </c>
+      <c r="D5" s="7">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>4</v>
+      </c>
+      <c r="G5" s="7">
+        <v>8</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>52</v>
+      </c>
+      <c r="J5" s="8">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="11"/>
+      <c r="B6" s="10">
+        <v>2674</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1048</v>
+      </c>
+      <c r="D6" s="10">
+        <v>266</v>
+      </c>
+      <c r="E6" s="10">
+        <v>7</v>
+      </c>
+      <c r="F6" s="10">
+        <v>62</v>
+      </c>
+      <c r="G6" s="10">
+        <v>335</v>
+      </c>
+      <c r="H6" s="10">
+        <v>15</v>
+      </c>
+      <c r="I6" s="10">
+        <v>958</v>
+      </c>
+      <c r="J6" s="11">
+        <v>1716</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8"/>
+      <c r="B7" s="7">
+        <v>368</v>
+      </c>
+      <c r="C7" s="7">
+        <v>129</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="7">
+        <v>4</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="7">
+        <v>92</v>
+      </c>
+      <c r="J7" s="8">
+        <v>276</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="11"/>
+      <c r="B8" s="10">
+        <v>188</v>
+      </c>
+      <c r="C8" s="10">
+        <v>100</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>2</v>
+      </c>
+      <c r="G8" s="10">
+        <v>4</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>34</v>
+      </c>
+      <c r="J8" s="11">
+        <v>154</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8"/>
+      <c r="B9" s="7">
+        <v>74</v>
+      </c>
+      <c r="C9" s="7">
+        <v>41</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>2</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>30</v>
+      </c>
+      <c r="J9" s="8">
+        <v>44</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="11"/>
+      <c r="B10" s="10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
+      <c r="B11" s="7">
+        <v>0</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
+      <c r="B12" s="13">
+        <v>4</v>
+      </c>
+      <c r="C12" s="13">
+        <v>4</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>4</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
+      <c r="B13" s="16">
+        <v>88</v>
+      </c>
+      <c r="C13" s="16">
+        <v>33</v>
+      </c>
+      <c r="D13" s="16">
+        <v>5</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16">
+        <v>5</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
+        <v>38</v>
+      </c>
+      <c r="J13" s="17">
+        <v>50</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
+      <c r="B14" s="13">
+        <v>328</v>
+      </c>
+      <c r="C14" s="13">
+        <v>166</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1</v>
+      </c>
+      <c r="E14" s="13">
+        <v>4</v>
+      </c>
+      <c r="F14" s="13">
+        <v>9</v>
+      </c>
+      <c r="G14" s="13">
+        <v>14</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>148</v>
+      </c>
+      <c r="J14" s="14">
+        <v>180</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
+      <c r="B15" s="16">
+        <v>202</v>
+      </c>
+      <c r="C15" s="16">
+        <v>73</v>
+      </c>
+      <c r="D15" s="16">
+        <v>5</v>
+      </c>
+      <c r="E15" s="16">
+        <v>1</v>
+      </c>
+      <c r="F15" s="16">
+        <v>10</v>
+      </c>
+      <c r="G15" s="16">
+        <v>16</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0</v>
+      </c>
+      <c r="I15" s="16">
+        <v>92</v>
+      </c>
+      <c r="J15" s="17">
+        <v>110</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="11"/>
+      <c r="B16" s="10">
+        <v>102</v>
+      </c>
+      <c r="C16" s="10">
+        <v>48</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0</v>
+      </c>
+      <c r="F16" s="10">
+        <v>3</v>
+      </c>
+      <c r="G16" s="10">
+        <v>3</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
+        <v>60</v>
+      </c>
+      <c r="J16" s="11">
+        <v>42</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="8"/>
+      <c r="B17" s="7">
+        <v>1366</v>
+      </c>
+      <c r="C17" s="7">
+        <v>560</v>
+      </c>
+      <c r="D17" s="7">
+        <v>71</v>
+      </c>
+      <c r="E17" s="7">
+        <v>8</v>
+      </c>
+      <c r="F17" s="7">
+        <v>32</v>
+      </c>
+      <c r="G17" s="7">
+        <v>111</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7">
+        <v>448</v>
+      </c>
+      <c r="J17" s="8">
+        <v>918</v>
+      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="11"/>
+      <c r="B18" s="10">
+        <v>38</v>
+      </c>
+      <c r="C18" s="10">
+        <v>40</v>
+      </c>
+      <c r="D18" s="10">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10">
+        <v>0</v>
+      </c>
+      <c r="F18" s="10">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10">
+        <v>2</v>
+      </c>
+      <c r="H18" s="10">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10">
+        <v>20</v>
+      </c>
+      <c r="J18" s="11">
+        <v>18</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
+      <c r="B19" s="7">
+        <v>680</v>
+      </c>
+      <c r="C19" s="7">
+        <v>267</v>
+      </c>
+      <c r="D19" s="7">
+        <v>37</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7">
+        <v>14</v>
+      </c>
+      <c r="G19" s="7">
+        <v>52</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7">
+        <v>200</v>
+      </c>
+      <c r="J19" s="8">
+        <v>480</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="11"/>
+      <c r="B20" s="10">
+        <v>0</v>
+      </c>
+      <c r="C20" s="10">
+        <v>0</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0</v>
+      </c>
+      <c r="F20" s="10">
+        <v>1</v>
+      </c>
+      <c r="G20" s="10">
+        <v>1</v>
+      </c>
+      <c r="H20" s="10">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10">
+        <v>0</v>
+      </c>
+      <c r="J20" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="8"/>
+      <c r="B21" s="7">
+        <v>904</v>
+      </c>
+      <c r="C21" s="7">
+        <v>432</v>
+      </c>
+      <c r="D21" s="7">
+        <v>23</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7">
+        <v>11</v>
+      </c>
+      <c r="G21" s="7">
+        <v>35</v>
+      </c>
+      <c r="H21" s="7">
+        <v>6</v>
+      </c>
+      <c r="I21" s="7">
+        <v>230</v>
+      </c>
+      <c r="J21" s="8">
+        <v>674</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="11"/>
+      <c r="B22" s="10">
+        <v>88</v>
+      </c>
+      <c r="C22" s="10">
+        <v>56</v>
+      </c>
+      <c r="D22" s="10">
+        <v>1</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10">
+        <v>4</v>
+      </c>
+      <c r="G22" s="10">
+        <v>5</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
+        <v>36</v>
+      </c>
+      <c r="J22" s="11">
+        <v>52</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="8"/>
+      <c r="B23" s="7">
+        <v>1326</v>
+      </c>
+      <c r="C23" s="7">
+        <v>393</v>
+      </c>
+      <c r="D23" s="7">
+        <v>159</v>
+      </c>
+      <c r="E23" s="7">
+        <v>7</v>
+      </c>
+      <c r="F23" s="7">
+        <v>25</v>
+      </c>
+      <c r="G23" s="7">
+        <v>191</v>
+      </c>
+      <c r="H23" s="7">
+        <v>3</v>
+      </c>
+      <c r="I23" s="7">
+        <v>272</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1054</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="11"/>
+      <c r="B24" s="10">
+        <v>4024</v>
+      </c>
+      <c r="C24" s="10">
+        <v>1673</v>
+      </c>
+      <c r="D24" s="10">
+        <v>234</v>
+      </c>
+      <c r="E24" s="10">
+        <v>26</v>
+      </c>
+      <c r="F24" s="10">
+        <v>94</v>
+      </c>
+      <c r="G24" s="10">
+        <v>354</v>
+      </c>
+      <c r="H24" s="10">
+        <v>2</v>
+      </c>
+      <c r="I24" s="10">
+        <v>668</v>
+      </c>
+      <c r="J24" s="11">
+        <v>3356</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="8"/>
+      <c r="B25" s="7">
+        <v>268</v>
+      </c>
+      <c r="C25" s="7">
+        <v>110</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0</v>
+      </c>
+      <c r="F25" s="7">
+        <v>12</v>
+      </c>
+      <c r="G25" s="7">
+        <v>14</v>
+      </c>
+      <c r="H25" s="7">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7">
+        <v>70</v>
+      </c>
+      <c r="J25" s="8">
+        <v>198</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="11"/>
+      <c r="B26" s="10">
+        <v>0</v>
+      </c>
+      <c r="C26" s="10">
+        <v>0</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10">
+        <v>0</v>
+      </c>
+      <c r="J26" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="8"/>
+      <c r="B27" s="7">
+        <v>366</v>
+      </c>
+      <c r="C27" s="7">
+        <v>183</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7">
+        <v>9</v>
+      </c>
+      <c r="G27" s="7">
+        <v>11</v>
+      </c>
+      <c r="H27" s="7">
+        <v>3</v>
+      </c>
+      <c r="I27" s="7">
+        <v>102</v>
+      </c>
+      <c r="J27" s="8">
+        <v>264</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="11"/>
+      <c r="B28" s="10">
+        <v>328</v>
+      </c>
+      <c r="C28" s="10">
+        <v>139</v>
+      </c>
+      <c r="D28" s="10">
+        <v>16</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0</v>
+      </c>
+      <c r="F28" s="10">
+        <v>3</v>
+      </c>
+      <c r="G28" s="10">
+        <v>19</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
+        <v>112</v>
+      </c>
+      <c r="J28" s="11">
+        <v>216</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="8"/>
+      <c r="B29" s="7">
+        <v>1438</v>
+      </c>
+      <c r="C29" s="7">
+        <v>716</v>
+      </c>
+      <c r="D29" s="7">
+        <v>19</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3</v>
+      </c>
+      <c r="F29" s="7">
+        <v>24</v>
+      </c>
+      <c r="G29" s="7">
+        <v>46</v>
+      </c>
+      <c r="H29" s="7">
+        <v>1</v>
+      </c>
+      <c r="I29" s="7">
+        <v>428</v>
+      </c>
+      <c r="J29" s="8">
+        <v>1010</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="11"/>
+      <c r="B30" s="10">
+        <v>48</v>
+      </c>
+      <c r="C30" s="10">
+        <v>21</v>
+      </c>
+      <c r="D30" s="10">
+        <v>1</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0</v>
+      </c>
+      <c r="F30" s="10">
+        <v>3</v>
+      </c>
+      <c r="G30" s="10">
+        <v>4</v>
+      </c>
+      <c r="H30" s="10">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10">
+        <v>24</v>
+      </c>
+      <c r="J30" s="11">
+        <v>24</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="8"/>
+      <c r="B31" s="7">
+        <v>34</v>
+      </c>
+      <c r="C31" s="7">
+        <v>57</v>
+      </c>
+      <c r="D31" s="7">
+        <v>2</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7">
+        <v>2</v>
+      </c>
+      <c r="G31" s="7">
+        <v>4</v>
+      </c>
+      <c r="H31" s="7">
+        <v>1</v>
+      </c>
+      <c r="I31" s="7">
+        <v>18</v>
+      </c>
+      <c r="J31" s="8">
+        <v>16</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="11"/>
+      <c r="B32" s="10">
+        <v>934</v>
+      </c>
+      <c r="C32" s="10">
+        <v>335</v>
+      </c>
+      <c r="D32" s="10">
+        <v>59</v>
+      </c>
+      <c r="E32" s="10">
+        <v>3</v>
+      </c>
+      <c r="F32" s="10">
+        <v>45</v>
+      </c>
+      <c r="G32" s="10">
+        <v>107</v>
+      </c>
+      <c r="H32" s="10">
+        <v>13</v>
+      </c>
+      <c r="I32" s="10">
+        <v>392</v>
+      </c>
+      <c r="J32" s="11">
+        <v>542</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="8"/>
+      <c r="B33" s="7">
+        <v>702</v>
+      </c>
+      <c r="C33" s="7">
+        <v>331</v>
+      </c>
+      <c r="D33" s="7">
+        <v>18</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1</v>
+      </c>
+      <c r="F33" s="7">
+        <v>31</v>
+      </c>
+      <c r="G33" s="7">
+        <v>50</v>
+      </c>
+      <c r="H33" s="7">
+        <v>25</v>
+      </c>
+      <c r="I33" s="7">
+        <v>318</v>
+      </c>
+      <c r="J33" s="8">
+        <v>384</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="11"/>
+      <c r="B34" s="10">
+        <v>248</v>
+      </c>
+      <c r="C34" s="10">
+        <v>108</v>
+      </c>
+      <c r="D34" s="10">
+        <v>19</v>
+      </c>
+      <c r="E34" s="10">
+        <v>0</v>
+      </c>
+      <c r="F34" s="10">
+        <v>6</v>
+      </c>
+      <c r="G34" s="10">
+        <v>25</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
+        <v>98</v>
+      </c>
+      <c r="J34" s="11">
+        <v>150</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="8"/>
+      <c r="B35" s="7">
+        <v>2600</v>
+      </c>
+      <c r="C35" s="7">
+        <v>1121</v>
+      </c>
+      <c r="D35" s="7">
+        <v>203</v>
+      </c>
+      <c r="E35" s="7">
+        <v>8</v>
+      </c>
+      <c r="F35" s="7">
+        <v>69</v>
+      </c>
+      <c r="G35" s="7">
+        <v>280</v>
+      </c>
+      <c r="H35" s="7">
+        <v>15</v>
+      </c>
+      <c r="I35" s="7">
+        <v>510</v>
+      </c>
+      <c r="J35" s="8">
+        <v>2090</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="11"/>
+      <c r="B36" s="10">
+        <v>326</v>
+      </c>
+      <c r="C36" s="10">
+        <v>136</v>
+      </c>
+      <c r="D36" s="10">
+        <v>4</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0</v>
+      </c>
+      <c r="F36" s="10">
+        <v>11</v>
+      </c>
+      <c r="G36" s="10">
+        <v>15</v>
+      </c>
+      <c r="H36" s="10">
+        <v>4</v>
+      </c>
+      <c r="I36" s="10">
+        <v>122</v>
+      </c>
+      <c r="J36" s="11">
+        <v>204</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="8"/>
+      <c r="B37" s="7">
+        <v>1126</v>
+      </c>
+      <c r="C37" s="7">
+        <v>403</v>
+      </c>
+      <c r="D37" s="7">
+        <v>132</v>
+      </c>
+      <c r="E37" s="7">
+        <v>3</v>
+      </c>
+      <c r="F37" s="7">
+        <v>39</v>
+      </c>
+      <c r="G37" s="7">
+        <v>174</v>
+      </c>
+      <c r="H37" s="7">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7">
+        <v>318</v>
+      </c>
+      <c r="J37" s="8">
+        <v>808</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="11"/>
+      <c r="B38" s="10">
+        <v>78</v>
+      </c>
+      <c r="C38" s="10">
+        <v>76</v>
+      </c>
+      <c r="D38" s="10">
+        <v>0</v>
+      </c>
+      <c r="E38" s="10">
+        <v>1</v>
+      </c>
+      <c r="F38" s="10">
+        <v>1</v>
+      </c>
+      <c r="G38" s="10">
+        <v>2</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0</v>
+      </c>
+      <c r="I38" s="10">
+        <v>12</v>
+      </c>
+      <c r="J38" s="11">
+        <v>66</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="8"/>
+      <c r="B39" s="7">
+        <v>69</v>
+      </c>
+      <c r="C39" s="7">
+        <v>28</v>
+      </c>
+      <c r="D39" s="7">
+        <v>28</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7">
+        <v>0</v>
+      </c>
+      <c r="G39" s="7">
+        <v>28</v>
+      </c>
+      <c r="H39" s="7">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7">
+        <v>30</v>
+      </c>
+      <c r="J39" s="8">
+        <v>39</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="20"/>
+      <c r="B40" s="19">
+        <v>0</v>
+      </c>
+      <c r="C40" s="19">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19">
+        <v>0</v>
+      </c>
+      <c r="F40" s="19">
+        <v>0</v>
+      </c>
+      <c r="G40" s="19">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19">
+        <v>0</v>
+      </c>
+      <c r="I40" s="19">
+        <v>0</v>
+      </c>
+      <c r="J40" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="23"/>
+      <c r="B41" s="22">
+        <v>0</v>
+      </c>
+      <c r="C41" s="22">
+        <v>0</v>
+      </c>
+      <c r="D41" s="22">
+        <v>0</v>
+      </c>
+      <c r="E41" s="22">
+        <v>0</v>
+      </c>
+      <c r="F41" s="22">
+        <v>0</v>
+      </c>
+      <c r="G41" s="22">
+        <v>0</v>
+      </c>
+      <c r="H41" s="22">
+        <v>0</v>
+      </c>
+      <c r="I41" s="22">
+        <v>0</v>
+      </c>
+      <c r="J41" s="23">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="20"/>
+      <c r="B42" s="19">
+        <v>0</v>
+      </c>
+      <c r="C42" s="19">
+        <v>1</v>
+      </c>
+      <c r="D42" s="19">
+        <v>0</v>
+      </c>
+      <c r="E42" s="19">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19">
+        <v>0</v>
+      </c>
+      <c r="G42" s="19">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19">
+        <v>0</v>
+      </c>
+      <c r="I42" s="19">
+        <v>0</v>
+      </c>
+      <c r="J42" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="23"/>
+      <c r="B43" s="22">
+        <v>0</v>
+      </c>
+      <c r="C43" s="22">
+        <v>0</v>
+      </c>
+      <c r="D43" s="22">
+        <v>0</v>
+      </c>
+      <c r="E43" s="22">
+        <v>0</v>
+      </c>
+      <c r="F43" s="22">
+        <v>0</v>
+      </c>
+      <c r="G43" s="22">
+        <v>0</v>
+      </c>
+      <c r="H43" s="22">
+        <v>0</v>
+      </c>
+      <c r="I43" s="22">
+        <v>0</v>
+      </c>
+      <c r="J43" s="23">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="8"/>
+      <c r="B44" s="7">
+        <v>108</v>
+      </c>
+      <c r="C44" s="7">
+        <v>39</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <v>3</v>
+      </c>
+      <c r="G44" s="7">
+        <v>4</v>
+      </c>
+      <c r="H44" s="7">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7">
+        <v>62</v>
+      </c>
+      <c r="J44" s="8">
+        <v>46</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="11"/>
+      <c r="B45" s="10">
+        <v>866</v>
+      </c>
+      <c r="C45" s="10">
+        <v>347</v>
+      </c>
+      <c r="D45" s="10">
+        <v>33</v>
+      </c>
+      <c r="E45" s="10">
+        <v>2</v>
+      </c>
+      <c r="F45" s="10">
+        <v>17</v>
+      </c>
+      <c r="G45" s="10">
+        <v>52</v>
+      </c>
+      <c r="H45" s="10">
+        <v>1</v>
+      </c>
+      <c r="I45" s="10">
+        <v>380</v>
+      </c>
+      <c r="J45" s="11">
+        <v>486</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="8"/>
+      <c r="B46" s="7">
+        <v>1306</v>
+      </c>
+      <c r="C46" s="7">
+        <v>587</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1</v>
+      </c>
+      <c r="F46" s="7">
+        <v>29</v>
+      </c>
+      <c r="G46" s="7">
+        <v>30</v>
+      </c>
+      <c r="H46" s="7">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7">
+        <v>238</v>
+      </c>
+      <c r="J46" s="8">
+        <v>1068</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="11"/>
+      <c r="B47" s="10">
+        <v>398</v>
+      </c>
+      <c r="C47" s="10">
+        <v>214</v>
+      </c>
+      <c r="D47" s="10">
+        <v>12</v>
+      </c>
+      <c r="E47" s="10">
+        <v>5</v>
+      </c>
+      <c r="F47" s="10">
+        <v>17</v>
+      </c>
+      <c r="G47" s="10">
+        <v>34</v>
+      </c>
+      <c r="H47" s="10">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10">
+        <v>116</v>
+      </c>
+      <c r="J47" s="11">
+        <v>282</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="8"/>
+      <c r="B48" s="7">
+        <v>638</v>
+      </c>
+      <c r="C48" s="7">
+        <v>184</v>
+      </c>
+      <c r="D48" s="7">
+        <v>36</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1</v>
+      </c>
+      <c r="F48" s="7">
+        <v>74</v>
+      </c>
+      <c r="G48" s="7">
+        <v>111</v>
+      </c>
+      <c r="H48" s="7">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7">
+        <v>116</v>
+      </c>
+      <c r="J48" s="8">
+        <v>522</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="11"/>
+      <c r="B49" s="10">
+        <v>2058</v>
+      </c>
+      <c r="C49" s="10">
+        <v>863</v>
+      </c>
+      <c r="D49" s="10">
+        <v>66</v>
+      </c>
+      <c r="E49" s="10">
+        <v>10</v>
+      </c>
+      <c r="F49" s="10">
+        <v>40</v>
+      </c>
+      <c r="G49" s="10">
+        <v>116</v>
+      </c>
+      <c r="H49" s="10">
+        <v>25</v>
+      </c>
+      <c r="I49" s="10">
+        <v>428</v>
+      </c>
+      <c r="J49" s="11">
+        <v>1630</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="8"/>
+      <c r="B50" s="7">
+        <v>107</v>
+      </c>
+      <c r="C50" s="7">
+        <v>81</v>
+      </c>
+      <c r="D50" s="7">
+        <v>15</v>
+      </c>
+      <c r="E50" s="7">
+        <v>3</v>
+      </c>
+      <c r="F50" s="7">
+        <v>2</v>
+      </c>
+      <c r="G50" s="7">
+        <v>20</v>
+      </c>
+      <c r="H50" s="7">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7">
+        <v>28</v>
+      </c>
+      <c r="J50" s="8">
+        <v>79</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="11"/>
+      <c r="B51" s="10">
+        <v>548</v>
+      </c>
+      <c r="C51" s="10">
+        <v>262</v>
+      </c>
+      <c r="D51" s="10">
+        <v>29</v>
+      </c>
+      <c r="E51" s="10">
+        <v>0</v>
+      </c>
+      <c r="F51" s="10">
+        <v>4</v>
+      </c>
+      <c r="G51" s="10">
+        <v>33</v>
+      </c>
+      <c r="H51" s="10">
+        <v>1</v>
+      </c>
+      <c r="I51" s="10">
+        <v>104</v>
+      </c>
+      <c r="J51" s="11">
+        <v>444</v>
+      </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="8"/>
+      <c r="B52" s="7">
+        <v>55</v>
+      </c>
+      <c r="C52" s="7">
+        <v>41</v>
+      </c>
+      <c r="D52" s="7">
+        <v>3</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7">
+        <v>3</v>
+      </c>
+      <c r="H52" s="7">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7">
+        <v>12</v>
+      </c>
+      <c r="J52" s="8">
+        <v>43</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="11"/>
+      <c r="B53" s="10">
+        <v>24</v>
+      </c>
+      <c r="C53" s="10">
+        <v>22</v>
+      </c>
+      <c r="D53" s="10">
+        <v>2</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0</v>
+      </c>
+      <c r="F53" s="10">
+        <v>1</v>
+      </c>
+      <c r="G53" s="10">
+        <v>3</v>
+      </c>
+      <c r="H53" s="10">
+        <v>0</v>
+      </c>
+      <c r="I53" s="10">
+        <v>10</v>
+      </c>
+      <c r="J53" s="11">
+        <v>14</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="8"/>
+      <c r="B54" s="7">
+        <v>572</v>
+      </c>
+      <c r="C54" s="7">
+        <v>296</v>
+      </c>
+      <c r="D54" s="7">
+        <v>3</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1</v>
+      </c>
+      <c r="F54" s="7">
+        <v>9</v>
+      </c>
+      <c r="G54" s="7">
+        <v>13</v>
+      </c>
+      <c r="H54" s="7">
+        <v>1</v>
+      </c>
+      <c r="I54" s="7">
+        <v>280</v>
+      </c>
+      <c r="J54" s="8">
+        <v>292</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
@@ -16542,27 +17496,27 @@
       </c>
       <c r="B55" s="31">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="C55" s="31">
         <f t="shared" ref="C55:J55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="D55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H55" s="31">
         <f t="shared" si="0"/>
@@ -16570,11 +17524,11 @@
       </c>
       <c r="I55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -16587,7 +17541,7 @@
       </c>
       <c r="C56" s="28">
         <f t="shared" ref="C56:J56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="28">
         <f t="shared" si="1"/>
@@ -16624,39 +17578,39 @@
       </c>
       <c r="B57" s="25">
         <f>SUM(B2:B54)</f>
-        <v>0</v>
+        <v>35080</v>
       </c>
       <c r="C57" s="25">
         <f t="shared" ref="C57:J57" si="2">SUM(C2:C54)</f>
-        <v>0</v>
+        <v>14721</v>
       </c>
       <c r="D57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1846</v>
       </c>
       <c r="E57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="F57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="G57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2881</v>
       </c>
       <c r="H57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="I57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8962</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26118</v>
       </c>
     </row>
   </sheetData>

--- a/statistics_files/2026/2026_99_gb_requests.xlsx
+++ b/statistics_files/2026/2026_99_gb_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E2EE86-C309-4A56-A7C9-64214692946A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247FBF24-A06D-40C7-B2E7-31EBDDC36723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="843" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5988,39 +5988,39 @@
       </c>
       <c r="B2" s="4">
         <f>SUM(January:December!B2)</f>
-        <v>16698</v>
+        <v>19500</v>
       </c>
       <c r="C2" s="4">
         <f>SUM(January:December!C2)</f>
-        <v>7313</v>
+        <v>8659</v>
       </c>
       <c r="D2" s="4">
         <f>SUM(January:December!D2)</f>
-        <v>555</v>
+        <v>647</v>
       </c>
       <c r="E2" s="4">
         <f>SUM(January:December!E2)</f>
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F2" s="4">
         <f>SUM(January:December!F2)</f>
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="G2" s="4">
         <f>SUM(January:December!G2)</f>
-        <v>920</v>
+        <v>1059</v>
       </c>
       <c r="H2" s="4">
         <f>SUM(January:December!H2)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I2" s="4">
         <f>SUM(January:December!I2)</f>
-        <v>2462</v>
+        <v>2874</v>
       </c>
       <c r="J2" s="5">
         <f>SUM(January:December!J2)</f>
-        <v>14236</v>
+        <v>16626</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6029,39 +6029,39 @@
       </c>
       <c r="B3" s="7">
         <f>SUM(January:December!B3)</f>
-        <v>7026</v>
+        <v>8328</v>
       </c>
       <c r="C3" s="7">
         <f>SUM(January:December!C3)</f>
-        <v>2955</v>
+        <v>3651</v>
       </c>
       <c r="D3" s="7">
         <f>SUM(January:December!D3)</f>
-        <v>260</v>
+        <v>331</v>
       </c>
       <c r="E3" s="7">
         <f>SUM(January:December!E3)</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F3" s="7">
         <f>SUM(January:December!F3)</f>
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="G3" s="7">
         <f>SUM(January:December!G3)</f>
-        <v>428</v>
+        <v>532</v>
       </c>
       <c r="H3" s="7">
         <f>SUM(January:December!H3)</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I3" s="7">
         <f>SUM(January:December!I3)</f>
-        <v>1082</v>
+        <v>1308</v>
       </c>
       <c r="J3" s="8">
         <f>SUM(January:December!J3)</f>
-        <v>5944</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B4" s="10">
         <f>SUM(January:December!B4)</f>
-        <v>14882</v>
+        <v>17842</v>
       </c>
       <c r="C4" s="10">
         <f>SUM(January:December!C4)</f>
-        <v>6643</v>
+        <v>7878</v>
       </c>
       <c r="D4" s="10">
         <f>SUM(January:December!D4)</f>
-        <v>776</v>
+        <v>937</v>
       </c>
       <c r="E4" s="10">
         <f>SUM(January:December!E4)</f>
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F4" s="10">
         <f>SUM(January:December!F4)</f>
-        <v>538</v>
+        <v>634</v>
       </c>
       <c r="G4" s="10">
         <f>SUM(January:December!G4)</f>
-        <v>1392</v>
+        <v>1658</v>
       </c>
       <c r="H4" s="10">
         <f>SUM(January:December!H4)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I4" s="10">
         <f>SUM(January:December!I4)</f>
-        <v>2500</v>
+        <v>2958</v>
       </c>
       <c r="J4" s="11">
         <f>SUM(January:December!J4)</f>
-        <v>12382</v>
+        <v>14884</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6111,15 +6111,15 @@
       </c>
       <c r="B5" s="7">
         <f>SUM(January:December!B5)</f>
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C5" s="7">
         <f>SUM(January:December!C5)</f>
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D5" s="7">
         <f>SUM(January:December!D5)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="7">
         <f>SUM(January:December!E5)</f>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G5" s="7">
         <f>SUM(January:December!G5)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" s="7">
         <f>SUM(January:December!H5)</f>
@@ -6139,11 +6139,11 @@
       </c>
       <c r="I5" s="7">
         <f>SUM(January:December!I5)</f>
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J5" s="8">
         <f>SUM(January:December!J5)</f>
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -6152,39 +6152,39 @@
       </c>
       <c r="B6" s="10">
         <f>SUM(January:December!B6)</f>
-        <v>15916</v>
+        <v>18424</v>
       </c>
       <c r="C6" s="10">
         <f>SUM(January:December!C6)</f>
-        <v>6590</v>
+        <v>7541</v>
       </c>
       <c r="D6" s="10">
         <f>SUM(January:December!D6)</f>
-        <v>1674</v>
+        <v>1929</v>
       </c>
       <c r="E6" s="10">
         <f>SUM(January:December!E6)</f>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F6" s="10">
         <f>SUM(January:December!F6)</f>
-        <v>405</v>
+        <v>470</v>
       </c>
       <c r="G6" s="10">
         <f>SUM(January:December!G6)</f>
-        <v>2111</v>
+        <v>2434</v>
       </c>
       <c r="H6" s="10">
         <f>SUM(January:December!H6)</f>
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="I6" s="10">
         <f>SUM(January:December!I6)</f>
-        <v>4782</v>
+        <v>5630</v>
       </c>
       <c r="J6" s="11">
         <f>SUM(January:December!J6)</f>
-        <v>11134</v>
+        <v>12794</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -6193,15 +6193,15 @@
       </c>
       <c r="B7" s="7">
         <f>SUM(January:December!B7)</f>
-        <v>2072</v>
+        <v>2536</v>
       </c>
       <c r="C7" s="7">
         <f>SUM(January:December!C7)</f>
-        <v>946</v>
+        <v>1183</v>
       </c>
       <c r="D7" s="7">
         <f>SUM(January:December!D7)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(January:December!E7)</f>
@@ -6209,23 +6209,23 @@
       </c>
       <c r="F7" s="7">
         <f>SUM(January:December!F7)</f>
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="G7" s="7">
         <f>SUM(January:December!G7)</f>
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="H7" s="7">
         <f>SUM(January:December!H7)</f>
-        <v>31</v>
+        <v>171</v>
       </c>
       <c r="I7" s="7">
         <f>SUM(January:December!I7)</f>
-        <v>714</v>
+        <v>852</v>
       </c>
       <c r="J7" s="8">
         <f>SUM(January:December!J7)</f>
-        <v>1358</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -6234,15 +6234,15 @@
       </c>
       <c r="B8" s="10">
         <f>SUM(January:December!B8)</f>
-        <v>1272</v>
+        <v>1642</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(January:December!C8)</f>
-        <v>559</v>
+        <v>717</v>
       </c>
       <c r="D8" s="10">
         <f>SUM(January:December!D8)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="10">
         <f>SUM(January:December!E8)</f>
@@ -6250,23 +6250,23 @@
       </c>
       <c r="F8" s="10">
         <f>SUM(January:December!F8)</f>
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G8" s="10">
         <f>SUM(January:December!G8)</f>
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H8" s="10">
         <f>SUM(January:December!H8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="10">
         <f>SUM(January:December!I8)</f>
-        <v>370</v>
+        <v>434</v>
       </c>
       <c r="J8" s="11">
         <f>SUM(January:December!J8)</f>
-        <v>902</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -6275,11 +6275,11 @@
       </c>
       <c r="B9" s="7">
         <f>SUM(January:December!B9)</f>
-        <v>526</v>
+        <v>652</v>
       </c>
       <c r="C9" s="7">
         <f>SUM(January:December!C9)</f>
-        <v>268</v>
+        <v>323</v>
       </c>
       <c r="D9" s="7">
         <f>SUM(January:December!D9)</f>
@@ -6291,11 +6291,11 @@
       </c>
       <c r="F9" s="7">
         <f>SUM(January:December!F9)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G9" s="7">
         <f>SUM(January:December!G9)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H9" s="7">
         <f>SUM(January:December!H9)</f>
@@ -6303,11 +6303,11 @@
       </c>
       <c r="I9" s="7">
         <f>SUM(January:December!I9)</f>
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="J9" s="8">
         <f>SUM(January:December!J9)</f>
-        <v>386</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C10" s="10">
         <f>SUM(January:December!C10)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="10">
         <f>SUM(January:December!D10)</f>
@@ -6398,11 +6398,11 @@
       </c>
       <c r="B12" s="13">
         <f>SUM(January:December!B12)</f>
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(January:December!C12)</f>
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D12" s="13">
         <f>SUM(January:December!D12)</f>
@@ -6426,11 +6426,11 @@
       </c>
       <c r="I12" s="13">
         <f>SUM(January:December!I12)</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J12" s="14">
         <f>SUM(January:December!J12)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -6439,27 +6439,27 @@
       </c>
       <c r="B13" s="16">
         <f>SUM(January:December!B13)</f>
-        <v>724</v>
+        <v>778</v>
       </c>
       <c r="C13" s="16">
         <f>SUM(January:December!C13)</f>
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="D13" s="16">
         <f>SUM(January:December!D13)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E13" s="16">
         <f>SUM(January:December!E13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="16">
         <f>SUM(January:December!F13)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13" s="16">
         <f>SUM(January:December!G13)</f>
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H13" s="16">
         <f>SUM(January:December!H13)</f>
@@ -6467,11 +6467,11 @@
       </c>
       <c r="I13" s="16">
         <f>SUM(January:December!I13)</f>
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="J13" s="17">
         <f>SUM(January:December!J13)</f>
-        <v>386</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -6480,15 +6480,15 @@
       </c>
       <c r="B14" s="13">
         <f>SUM(January:December!B14)</f>
-        <v>2284</v>
+        <v>2596</v>
       </c>
       <c r="C14" s="13">
         <f>SUM(January:December!C14)</f>
-        <v>1075</v>
+        <v>1222</v>
       </c>
       <c r="D14" s="13">
         <f>SUM(January:December!D14)</f>
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E14" s="13">
         <f>SUM(January:December!E14)</f>
@@ -6496,23 +6496,23 @@
       </c>
       <c r="F14" s="13">
         <f>SUM(January:December!F14)</f>
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="G14" s="13">
         <f>SUM(January:December!G14)</f>
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="H14" s="13">
         <f>SUM(January:December!H14)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I14" s="13">
         <f>SUM(January:December!I14)</f>
-        <v>1112</v>
+        <v>1248</v>
       </c>
       <c r="J14" s="14">
         <f>SUM(January:December!J14)</f>
-        <v>1172</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -6521,39 +6521,39 @@
       </c>
       <c r="B15" s="16">
         <f>SUM(January:December!B15)</f>
-        <v>766</v>
+        <v>844</v>
       </c>
       <c r="C15" s="16">
         <f>SUM(January:December!C15)</f>
-        <v>330</v>
+        <v>400</v>
       </c>
       <c r="D15" s="16">
         <f>SUM(January:December!D15)</f>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E15" s="16">
         <f>SUM(January:December!E15)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F15" s="16">
         <f>SUM(January:December!F15)</f>
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G15" s="16">
         <f>SUM(January:December!G15)</f>
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="H15" s="16">
         <f>SUM(January:December!H15)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" s="16">
         <f>SUM(January:December!I15)</f>
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="J15" s="17">
         <f>SUM(January:December!J15)</f>
-        <v>420</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -6562,11 +6562,11 @@
       </c>
       <c r="B16" s="10">
         <f>SUM(January:December!B16)</f>
-        <v>732</v>
+        <v>834</v>
       </c>
       <c r="C16" s="10">
         <f>SUM(January:December!C16)</f>
-        <v>357</v>
+        <v>409</v>
       </c>
       <c r="D16" s="10">
         <f>SUM(January:December!D16)</f>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="I16" s="10">
         <f>SUM(January:December!I16)</f>
-        <v>356</v>
+        <v>424</v>
       </c>
       <c r="J16" s="11">
         <f>SUM(January:December!J16)</f>
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -6603,27 +6603,27 @@
       </c>
       <c r="B17" s="7">
         <f>SUM(January:December!B17)</f>
-        <v>7342</v>
+        <v>8622</v>
       </c>
       <c r="C17" s="7">
         <f>SUM(January:December!C17)</f>
-        <v>3080</v>
+        <v>3577</v>
       </c>
       <c r="D17" s="7">
         <f>SUM(January:December!D17)</f>
-        <v>368</v>
+        <v>418</v>
       </c>
       <c r="E17" s="7">
         <f>SUM(January:December!E17)</f>
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F17" s="7">
         <f>SUM(January:December!F17)</f>
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="G17" s="7">
         <f>SUM(January:December!G17)</f>
-        <v>562</v>
+        <v>659</v>
       </c>
       <c r="H17" s="7">
         <f>SUM(January:December!H17)</f>
@@ -6631,11 +6631,11 @@
       </c>
       <c r="I17" s="7">
         <f>SUM(January:December!I17)</f>
-        <v>2156</v>
+        <v>2582</v>
       </c>
       <c r="J17" s="8">
         <f>SUM(January:December!J17)</f>
-        <v>5186</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -6644,15 +6644,15 @@
       </c>
       <c r="B18" s="10">
         <f>SUM(January:December!B18)</f>
-        <v>474</v>
+        <v>554</v>
       </c>
       <c r="C18" s="10">
         <f>SUM(January:December!C18)</f>
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="D18" s="10">
         <f>SUM(January:December!D18)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18" s="10">
         <f>SUM(January:December!E18)</f>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="F18" s="10">
         <f>SUM(January:December!F18)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G18" s="10">
         <f>SUM(January:December!G18)</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(January:December!H18)</f>
@@ -6672,11 +6672,11 @@
       </c>
       <c r="I18" s="10">
         <f>SUM(January:December!I18)</f>
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="J18" s="11">
         <f>SUM(January:December!J18)</f>
-        <v>370</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -6685,39 +6685,39 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(January:December!B19)</f>
-        <v>5468</v>
+        <v>6182</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(January:December!C19)</f>
-        <v>2372</v>
+        <v>2707</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(January:December!D19)</f>
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(January:December!E19)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F19" s="7">
         <f>SUM(January:December!F19)</f>
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="G19" s="7">
         <f>SUM(January:December!G19)</f>
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="H19" s="7">
         <f>SUM(January:December!H19)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I19" s="7">
         <f>SUM(January:December!I19)</f>
-        <v>1570</v>
+        <v>1816</v>
       </c>
       <c r="J19" s="8">
         <f>SUM(January:December!J19)</f>
-        <v>3898</v>
+        <v>4366</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="B20" s="10">
         <f>SUM(January:December!B20)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C20" s="10">
         <f>SUM(January:December!C20)</f>
@@ -6742,11 +6742,11 @@
       </c>
       <c r="F20" s="10">
         <f>SUM(January:December!F20)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="10">
         <f>SUM(January:December!G20)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="10">
         <f>SUM(January:December!H20)</f>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="J20" s="11">
         <f>SUM(January:December!J20)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -6767,27 +6767,27 @@
       </c>
       <c r="B21" s="7">
         <f>SUM(January:December!B21)</f>
-        <v>5544</v>
+        <v>6552</v>
       </c>
       <c r="C21" s="7">
         <f>SUM(January:December!C21)</f>
-        <v>2491</v>
+        <v>2994</v>
       </c>
       <c r="D21" s="7">
         <f>SUM(January:December!D21)</f>
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(January:December!E21)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F21" s="7">
         <f>SUM(January:December!F21)</f>
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G21" s="7">
         <f>SUM(January:December!G21)</f>
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="H21" s="7">
         <f>SUM(January:December!H21)</f>
@@ -6795,11 +6795,11 @@
       </c>
       <c r="I21" s="7">
         <f>SUM(January:December!I21)</f>
-        <v>1338</v>
+        <v>1604</v>
       </c>
       <c r="J21" s="8">
         <f>SUM(January:December!J21)</f>
-        <v>4206</v>
+        <v>4948</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -6808,27 +6808,27 @@
       </c>
       <c r="B22" s="10">
         <f>SUM(January:December!B22)</f>
-        <v>778</v>
+        <v>928</v>
       </c>
       <c r="C22" s="10">
         <f>SUM(January:December!C22)</f>
-        <v>400</v>
+        <v>449</v>
       </c>
       <c r="D22" s="10">
         <f>SUM(January:December!D22)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E22" s="10">
         <f>SUM(January:December!E22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="10">
         <f>SUM(January:December!F22)</f>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G22" s="10">
         <f>SUM(January:December!G22)</f>
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H22" s="10">
         <f>SUM(January:December!H22)</f>
@@ -6836,11 +6836,11 @@
       </c>
       <c r="I22" s="10">
         <f>SUM(January:December!I22)</f>
-        <v>252</v>
+        <v>310</v>
       </c>
       <c r="J22" s="11">
         <f>SUM(January:December!J22)</f>
-        <v>526</v>
+        <v>618</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -6849,39 +6849,39 @@
       </c>
       <c r="B23" s="7">
         <f>SUM(January:December!B23)</f>
-        <v>7598</v>
+        <v>8910</v>
       </c>
       <c r="C23" s="7">
         <f>SUM(January:December!C23)</f>
-        <v>2466</v>
+        <v>2931</v>
       </c>
       <c r="D23" s="7">
         <f>SUM(January:December!D23)</f>
-        <v>939</v>
+        <v>1086</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(January:December!E23)</f>
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F23" s="7">
         <f>SUM(January:December!F23)</f>
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="G23" s="7">
         <f>SUM(January:December!G23)</f>
-        <v>1260</v>
+        <v>1445</v>
       </c>
       <c r="H23" s="7">
         <f>SUM(January:December!H23)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I23" s="7">
         <f>SUM(January:December!I23)</f>
-        <v>1674</v>
+        <v>1940</v>
       </c>
       <c r="J23" s="8">
         <f>SUM(January:December!J23)</f>
-        <v>5924</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -6890,39 +6890,39 @@
       </c>
       <c r="B24" s="10">
         <f>SUM(January:December!B24)</f>
-        <v>23608</v>
+        <v>27364</v>
       </c>
       <c r="C24" s="10">
         <f>SUM(January:December!C24)</f>
-        <v>10048</v>
+        <v>11627</v>
       </c>
       <c r="D24" s="10">
         <f>SUM(January:December!D24)</f>
-        <v>1056</v>
+        <v>1303</v>
       </c>
       <c r="E24" s="10">
         <f>SUM(January:December!E24)</f>
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="F24" s="10">
         <f>SUM(January:December!F24)</f>
-        <v>583</v>
+        <v>675</v>
       </c>
       <c r="G24" s="10">
         <f>SUM(January:December!G24)</f>
-        <v>1749</v>
+        <v>2103</v>
       </c>
       <c r="H24" s="10">
         <f>SUM(January:December!H24)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I24" s="10">
         <f>SUM(January:December!I24)</f>
-        <v>3174</v>
+        <v>3734</v>
       </c>
       <c r="J24" s="11">
         <f>SUM(January:December!J24)</f>
-        <v>20434</v>
+        <v>23630</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -6931,27 +6931,27 @@
       </c>
       <c r="B25" s="7">
         <f>SUM(January:December!B25)</f>
-        <v>1620</v>
+        <v>1900</v>
       </c>
       <c r="C25" s="7">
         <f>SUM(January:December!C25)</f>
-        <v>705</v>
+        <v>800</v>
       </c>
       <c r="D25" s="7">
         <f>SUM(January:December!D25)</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(January:December!E25)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="7">
         <f>SUM(January:December!F25)</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G25" s="7">
         <f>SUM(January:December!G25)</f>
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H25" s="7">
         <f>SUM(January:December!H25)</f>
@@ -6959,11 +6959,11 @@
       </c>
       <c r="I25" s="7">
         <f>SUM(January:December!I25)</f>
-        <v>494</v>
+        <v>592</v>
       </c>
       <c r="J25" s="8">
         <f>SUM(January:December!J25)</f>
-        <v>1126</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -7013,39 +7013,39 @@
       </c>
       <c r="B27" s="7">
         <f>SUM(January:December!B27)</f>
-        <v>2014</v>
+        <v>2322</v>
       </c>
       <c r="C27" s="7">
         <f>SUM(January:December!C27)</f>
-        <v>947</v>
+        <v>1107</v>
       </c>
       <c r="D27" s="7">
         <f>SUM(January:December!D27)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(January:December!E27)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" s="7">
         <f>SUM(January:December!F27)</f>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G27" s="7">
         <f>SUM(January:December!G27)</f>
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H27" s="7">
         <f>SUM(January:December!H27)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I27" s="7">
         <f>SUM(January:December!I27)</f>
-        <v>598</v>
+        <v>702</v>
       </c>
       <c r="J27" s="8">
         <f>SUM(January:December!J27)</f>
-        <v>1416</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -7054,15 +7054,15 @@
       </c>
       <c r="B28" s="10">
         <f>SUM(January:December!B28)</f>
-        <v>1549</v>
+        <v>1803</v>
       </c>
       <c r="C28" s="10">
         <f>SUM(January:December!C28)</f>
-        <v>669</v>
+        <v>794</v>
       </c>
       <c r="D28" s="10">
         <f>SUM(January:December!D28)</f>
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E28" s="10">
         <f>SUM(January:December!E28)</f>
@@ -7070,11 +7070,11 @@
       </c>
       <c r="F28" s="10">
         <f>SUM(January:December!F28)</f>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G28" s="10">
         <f>SUM(January:December!G28)</f>
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="H28" s="10">
         <f>SUM(January:December!H28)</f>
@@ -7082,11 +7082,11 @@
       </c>
       <c r="I28" s="10">
         <f>SUM(January:December!I28)</f>
-        <v>506</v>
+        <v>580</v>
       </c>
       <c r="J28" s="11">
         <f>SUM(January:December!J28)</f>
-        <v>1043</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -7095,27 +7095,27 @@
       </c>
       <c r="B29" s="7">
         <f>SUM(January:December!B29)</f>
-        <v>7964</v>
+        <v>9392</v>
       </c>
       <c r="C29" s="7">
         <f>SUM(January:December!C29)</f>
-        <v>3746</v>
+        <v>4368</v>
       </c>
       <c r="D29" s="7">
         <f>SUM(January:December!D29)</f>
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(January:December!E29)</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="7">
         <f>SUM(January:December!F29)</f>
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="G29" s="7">
         <f>SUM(January:December!G29)</f>
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="H29" s="7">
         <f>SUM(January:December!H29)</f>
@@ -7123,11 +7123,11 @@
       </c>
       <c r="I29" s="7">
         <f>SUM(January:December!I29)</f>
-        <v>2002</v>
+        <v>2324</v>
       </c>
       <c r="J29" s="8">
         <f>SUM(January:December!J29)</f>
-        <v>5962</v>
+        <v>7068</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -7136,15 +7136,15 @@
       </c>
       <c r="B30" s="10">
         <f>SUM(January:December!B30)</f>
-        <v>328</v>
+        <v>428</v>
       </c>
       <c r="C30" s="10">
         <f>SUM(January:December!C30)</f>
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="D30" s="10">
         <f>SUM(January:December!D30)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E30" s="10">
         <f>SUM(January:December!E30)</f>
@@ -7152,23 +7152,23 @@
       </c>
       <c r="F30" s="10">
         <f>SUM(January:December!F30)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G30" s="10">
         <f>SUM(January:December!G30)</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H30" s="10">
         <f>SUM(January:December!H30)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I30" s="10">
         <f>SUM(January:December!I30)</f>
-        <v>160</v>
+        <v>214</v>
       </c>
       <c r="J30" s="11">
         <f>SUM(January:December!J30)</f>
-        <v>168</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -7177,15 +7177,15 @@
       </c>
       <c r="B31" s="7">
         <f>SUM(January:December!B31)</f>
-        <v>1035</v>
+        <v>1076</v>
       </c>
       <c r="C31" s="7">
         <f>SUM(January:December!C31)</f>
-        <v>483</v>
+        <v>524</v>
       </c>
       <c r="D31" s="7">
         <f>SUM(January:December!D31)</f>
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(January:December!E31)</f>
@@ -7193,23 +7193,23 @@
       </c>
       <c r="F31" s="7">
         <f>SUM(January:December!F31)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G31" s="7">
         <f>SUM(January:December!G31)</f>
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H31" s="7">
         <f>SUM(January:December!H31)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I31" s="7">
         <f>SUM(January:December!I31)</f>
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="J31" s="8">
         <f>SUM(January:December!J31)</f>
-        <v>925</v>
+        <v>958</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -7218,39 +7218,39 @@
       </c>
       <c r="B32" s="10">
         <f>SUM(January:December!B32)</f>
-        <v>5858</v>
+        <v>6936</v>
       </c>
       <c r="C32" s="10">
         <f>SUM(January:December!C32)</f>
-        <v>2088</v>
+        <v>2514</v>
       </c>
       <c r="D32" s="10">
         <f>SUM(January:December!D32)</f>
-        <v>503</v>
+        <v>571</v>
       </c>
       <c r="E32" s="10">
         <f>SUM(January:December!E32)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F32" s="10">
         <f>SUM(January:December!F32)</f>
-        <v>267</v>
+        <v>330</v>
       </c>
       <c r="G32" s="10">
         <f>SUM(January:December!G32)</f>
-        <v>787</v>
+        <v>921</v>
       </c>
       <c r="H32" s="10">
         <f>SUM(January:December!H32)</f>
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="I32" s="10">
         <f>SUM(January:December!I32)</f>
-        <v>2336</v>
+        <v>2810</v>
       </c>
       <c r="J32" s="11">
         <f>SUM(January:December!J32)</f>
-        <v>3522</v>
+        <v>4126</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -7259,39 +7259,39 @@
       </c>
       <c r="B33" s="7">
         <f>SUM(January:December!B33)</f>
-        <v>4888</v>
+        <v>5678</v>
       </c>
       <c r="C33" s="7">
         <f>SUM(January:December!C33)</f>
-        <v>2068</v>
+        <v>2427</v>
       </c>
       <c r="D33" s="7">
         <f>SUM(January:December!D33)</f>
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(January:December!E33)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F33" s="7">
         <f>SUM(January:December!F33)</f>
-        <v>256</v>
+        <v>330</v>
       </c>
       <c r="G33" s="7">
         <f>SUM(January:December!G33)</f>
-        <v>337</v>
+        <v>422</v>
       </c>
       <c r="H33" s="7">
         <f>SUM(January:December!H33)</f>
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="I33" s="7">
         <f>SUM(January:December!I33)</f>
-        <v>2094</v>
+        <v>2396</v>
       </c>
       <c r="J33" s="8">
         <f>SUM(January:December!J33)</f>
-        <v>2794</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -7300,27 +7300,27 @@
       </c>
       <c r="B34" s="10">
         <f>SUM(January:December!B34)</f>
-        <v>1504</v>
+        <v>1768</v>
       </c>
       <c r="C34" s="10">
         <f>SUM(January:December!C34)</f>
-        <v>678</v>
+        <v>791</v>
       </c>
       <c r="D34" s="10">
         <f>SUM(January:December!D34)</f>
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E34" s="10">
         <f>SUM(January:December!E34)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" s="10">
         <f>SUM(January:December!F34)</f>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G34" s="10">
         <f>SUM(January:December!G34)</f>
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="H34" s="10">
         <f>SUM(January:December!H34)</f>
@@ -7328,11 +7328,11 @@
       </c>
       <c r="I34" s="10">
         <f>SUM(January:December!I34)</f>
-        <v>554</v>
+        <v>692</v>
       </c>
       <c r="J34" s="11">
         <f>SUM(January:December!J34)</f>
-        <v>950</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -7341,39 +7341,39 @@
       </c>
       <c r="B35" s="7">
         <f>SUM(January:December!B35)</f>
-        <v>16682</v>
+        <v>19238</v>
       </c>
       <c r="C35" s="7">
         <f>SUM(January:December!C35)</f>
-        <v>6801</v>
+        <v>7793</v>
       </c>
       <c r="D35" s="7">
         <f>SUM(January:December!D35)</f>
-        <v>1170</v>
+        <v>1361</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(January:December!E35)</f>
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="F35" s="7">
         <f>SUM(January:December!F35)</f>
-        <v>366</v>
+        <v>470</v>
       </c>
       <c r="G35" s="7">
         <f>SUM(January:December!G35)</f>
-        <v>1577</v>
+        <v>1896</v>
       </c>
       <c r="H35" s="7">
         <f>SUM(January:December!H35)</f>
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I35" s="7">
         <f>SUM(January:December!I35)</f>
-        <v>3660</v>
+        <v>4114</v>
       </c>
       <c r="J35" s="8">
         <f>SUM(January:December!J35)</f>
-        <v>13022</v>
+        <v>15124</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -7382,15 +7382,15 @@
       </c>
       <c r="B36" s="10">
         <f>SUM(January:December!B36)</f>
-        <v>1990</v>
+        <v>2256</v>
       </c>
       <c r="C36" s="10">
         <f>SUM(January:December!C36)</f>
-        <v>878</v>
+        <v>1029</v>
       </c>
       <c r="D36" s="10">
         <f>SUM(January:December!D36)</f>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E36" s="10">
         <f>SUM(January:December!E36)</f>
@@ -7398,11 +7398,11 @@
       </c>
       <c r="F36" s="10">
         <f>SUM(January:December!F36)</f>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G36" s="10">
         <f>SUM(January:December!G36)</f>
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H36" s="10">
         <f>SUM(January:December!H36)</f>
@@ -7410,11 +7410,11 @@
       </c>
       <c r="I36" s="10">
         <f>SUM(January:December!I36)</f>
-        <v>682</v>
+        <v>794</v>
       </c>
       <c r="J36" s="11">
         <f>SUM(January:December!J36)</f>
-        <v>1308</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -7423,39 +7423,39 @@
       </c>
       <c r="B37" s="7">
         <f>SUM(January:December!B37)</f>
-        <v>6800</v>
+        <v>7996</v>
       </c>
       <c r="C37" s="7">
         <f>SUM(January:December!C37)</f>
-        <v>2484</v>
+        <v>2941</v>
       </c>
       <c r="D37" s="7">
         <f>SUM(January:December!D37)</f>
-        <v>666</v>
+        <v>759</v>
       </c>
       <c r="E37" s="7">
         <f>SUM(January:December!E37)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F37" s="7">
         <f>SUM(January:December!F37)</f>
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="G37" s="7">
         <f>SUM(January:December!G37)</f>
-        <v>910</v>
+        <v>1041</v>
       </c>
       <c r="H37" s="7">
         <f>SUM(January:December!H37)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I37" s="7">
         <f>SUM(January:December!I37)</f>
-        <v>1758</v>
+        <v>2020</v>
       </c>
       <c r="J37" s="8">
         <f>SUM(January:December!J37)</f>
-        <v>5042</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -7464,15 +7464,15 @@
       </c>
       <c r="B38" s="10">
         <f>SUM(January:December!B38)</f>
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="C38" s="10">
         <f>SUM(January:December!C38)</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D38" s="10">
         <f>SUM(January:December!D38)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="10">
         <f>SUM(January:December!E38)</f>
@@ -7480,11 +7480,11 @@
       </c>
       <c r="F38" s="10">
         <f>SUM(January:December!F38)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" s="10">
         <f>SUM(January:December!G38)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H38" s="10">
         <f>SUM(January:December!H38)</f>
@@ -7492,11 +7492,11 @@
       </c>
       <c r="I38" s="10">
         <f>SUM(January:December!I38)</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J38" s="11">
         <f>SUM(January:December!J38)</f>
-        <v>297</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -7505,15 +7505,15 @@
       </c>
       <c r="B39" s="7">
         <f>SUM(January:December!B39)</f>
-        <v>1967</v>
+        <v>2175</v>
       </c>
       <c r="C39" s="7">
         <f>SUM(January:December!C39)</f>
-        <v>348</v>
+        <v>451</v>
       </c>
       <c r="D39" s="7">
         <f>SUM(January:December!D39)</f>
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(January:December!E39)</f>
@@ -7521,11 +7521,11 @@
       </c>
       <c r="F39" s="7">
         <f>SUM(January:December!F39)</f>
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G39" s="7">
         <f>SUM(January:December!G39)</f>
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="H39" s="7">
         <f>SUM(January:December!H39)</f>
@@ -7533,11 +7533,11 @@
       </c>
       <c r="I39" s="7">
         <f>SUM(January:December!I39)</f>
-        <v>966</v>
+        <v>1060</v>
       </c>
       <c r="J39" s="8">
         <f>SUM(January:December!J39)</f>
-        <v>1001</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -7710,11 +7710,11 @@
       </c>
       <c r="B44" s="7">
         <f>SUM(January:December!B44)</f>
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="C44" s="7">
         <f>SUM(January:December!C44)</f>
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="D44" s="7">
         <f>SUM(January:December!D44)</f>
@@ -7726,23 +7726,23 @@
       </c>
       <c r="F44" s="7">
         <f>SUM(January:December!F44)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G44" s="7">
         <f>SUM(January:December!G44)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H44" s="7">
         <f>SUM(January:December!H44)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="7">
         <f>SUM(January:December!I44)</f>
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="J44" s="8">
         <f>SUM(January:December!J44)</f>
-        <v>330</v>
+        <v>358</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -7751,39 +7751,39 @@
       </c>
       <c r="B45" s="10">
         <f>SUM(January:December!B45)</f>
-        <v>5512</v>
+        <v>6338</v>
       </c>
       <c r="C45" s="10">
         <f>SUM(January:December!C45)</f>
-        <v>2448</v>
+        <v>2862</v>
       </c>
       <c r="D45" s="10">
         <f>SUM(January:December!D45)</f>
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="E45" s="10">
         <f>SUM(January:December!E45)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F45" s="10">
         <f>SUM(January:December!F45)</f>
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G45" s="10">
         <f>SUM(January:December!G45)</f>
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="H45" s="10">
         <f>SUM(January:December!H45)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I45" s="10">
         <f>SUM(January:December!I45)</f>
-        <v>1724</v>
+        <v>1926</v>
       </c>
       <c r="J45" s="11">
         <f>SUM(January:December!J45)</f>
-        <v>3788</v>
+        <v>4412</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -7792,11 +7792,11 @@
       </c>
       <c r="B46" s="7">
         <f>SUM(January:December!B46)</f>
-        <v>8414</v>
+        <v>9556</v>
       </c>
       <c r="C46" s="7">
         <f>SUM(January:December!C46)</f>
-        <v>4035</v>
+        <v>4667</v>
       </c>
       <c r="D46" s="7">
         <f>SUM(January:December!D46)</f>
@@ -7804,15 +7804,15 @@
       </c>
       <c r="E46" s="7">
         <f>SUM(January:December!E46)</f>
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F46" s="7">
         <f>SUM(January:December!F46)</f>
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="G46" s="7">
         <f>SUM(January:December!G46)</f>
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="H46" s="7">
         <f>SUM(January:December!H46)</f>
@@ -7820,11 +7820,11 @@
       </c>
       <c r="I46" s="7">
         <f>SUM(January:December!I46)</f>
-        <v>1110</v>
+        <v>1326</v>
       </c>
       <c r="J46" s="8">
         <f>SUM(January:December!J46)</f>
-        <v>7304</v>
+        <v>8230</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -7833,27 +7833,27 @@
       </c>
       <c r="B47" s="10">
         <f>SUM(January:December!B47)</f>
-        <v>2656</v>
+        <v>3020</v>
       </c>
       <c r="C47" s="10">
         <f>SUM(January:December!C47)</f>
-        <v>1125</v>
+        <v>1307</v>
       </c>
       <c r="D47" s="10">
         <f>SUM(January:December!D47)</f>
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E47" s="10">
         <f>SUM(January:December!E47)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F47" s="10">
         <f>SUM(January:December!F47)</f>
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G47" s="10">
         <f>SUM(January:December!G47)</f>
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="H47" s="10">
         <f>SUM(January:December!H47)</f>
@@ -7861,11 +7861,11 @@
       </c>
       <c r="I47" s="10">
         <f>SUM(January:December!I47)</f>
-        <v>554</v>
+        <v>660</v>
       </c>
       <c r="J47" s="11">
         <f>SUM(January:December!J47)</f>
-        <v>2102</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -7874,15 +7874,15 @@
       </c>
       <c r="B48" s="7">
         <f>SUM(January:December!B48)</f>
-        <v>3992</v>
+        <v>4446</v>
       </c>
       <c r="C48" s="7">
         <f>SUM(January:December!C48)</f>
-        <v>1613</v>
+        <v>1794</v>
       </c>
       <c r="D48" s="7">
         <f>SUM(January:December!D48)</f>
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(January:December!E48)</f>
@@ -7890,11 +7890,11 @@
       </c>
       <c r="F48" s="7">
         <f>SUM(January:December!F48)</f>
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G48" s="7">
         <f>SUM(January:December!G48)</f>
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(January:December!H48)</f>
@@ -7902,11 +7902,11 @@
       </c>
       <c r="I48" s="7">
         <f>SUM(January:December!I48)</f>
-        <v>738</v>
+        <v>840</v>
       </c>
       <c r="J48" s="8">
         <f>SUM(January:December!J48)</f>
-        <v>3254</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -7915,39 +7915,39 @@
       </c>
       <c r="B49" s="10">
         <f>SUM(January:December!B49)</f>
-        <v>10870</v>
+        <v>12636</v>
       </c>
       <c r="C49" s="10">
         <f>SUM(January:December!C49)</f>
-        <v>4647</v>
+        <v>5417</v>
       </c>
       <c r="D49" s="10">
         <f>SUM(January:December!D49)</f>
-        <v>405</v>
+        <v>541</v>
       </c>
       <c r="E49" s="10">
         <f>SUM(January:December!E49)</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F49" s="10">
         <f>SUM(January:December!F49)</f>
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="G49" s="10">
         <f>SUM(January:December!G49)</f>
-        <v>692</v>
+        <v>869</v>
       </c>
       <c r="H49" s="10">
         <f>SUM(January:December!H49)</f>
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I49" s="10">
         <f>SUM(January:December!I49)</f>
-        <v>2254</v>
+        <v>2558</v>
       </c>
       <c r="J49" s="11">
         <f>SUM(January:December!J49)</f>
-        <v>8616</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -7956,39 +7956,39 @@
       </c>
       <c r="B50" s="7">
         <f>SUM(January:December!B50)</f>
-        <v>1289</v>
+        <v>1471</v>
       </c>
       <c r="C50" s="7">
         <f>SUM(January:December!C50)</f>
-        <v>562</v>
+        <v>637</v>
       </c>
       <c r="D50" s="7">
         <f>SUM(January:December!D50)</f>
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E50" s="7">
         <f>SUM(January:December!E50)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F50" s="7">
         <f>SUM(January:December!F50)</f>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G50" s="7">
         <f>SUM(January:December!G50)</f>
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="H50" s="7">
         <f>SUM(January:December!H50)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="7">
         <f>SUM(January:December!I50)</f>
-        <v>438</v>
+        <v>496</v>
       </c>
       <c r="J50" s="8">
         <f>SUM(January:December!J50)</f>
-        <v>851</v>
+        <v>975</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -7997,15 +7997,15 @@
       </c>
       <c r="B51" s="10">
         <f>SUM(January:December!B51)</f>
-        <v>4620</v>
+        <v>5186</v>
       </c>
       <c r="C51" s="10">
         <f>SUM(January:December!C51)</f>
-        <v>2018</v>
+        <v>2245</v>
       </c>
       <c r="D51" s="10">
         <f>SUM(January:December!D51)</f>
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="E51" s="10">
         <f>SUM(January:December!E51)</f>
@@ -8013,23 +8013,23 @@
       </c>
       <c r="F51" s="10">
         <f>SUM(January:December!F51)</f>
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="G51" s="10">
         <f>SUM(January:December!G51)</f>
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="H51" s="10">
         <f>SUM(January:December!H51)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I51" s="10">
         <f>SUM(January:December!I51)</f>
-        <v>692</v>
+        <v>856</v>
       </c>
       <c r="J51" s="11">
         <f>SUM(January:December!J51)</f>
-        <v>3928</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -8038,15 +8038,15 @@
       </c>
       <c r="B52" s="7">
         <f>SUM(January:December!B52)</f>
-        <v>825</v>
+        <v>852</v>
       </c>
       <c r="C52" s="7">
         <f>SUM(January:December!C52)</f>
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="D52" s="7">
         <f>SUM(January:December!D52)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(January:December!E52)</f>
@@ -8054,11 +8054,11 @@
       </c>
       <c r="F52" s="7">
         <f>SUM(January:December!F52)</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G52" s="7">
         <f>SUM(January:December!G52)</f>
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H52" s="7">
         <f>SUM(January:December!H52)</f>
@@ -8066,11 +8066,11 @@
       </c>
       <c r="I52" s="7">
         <f>SUM(January:December!I52)</f>
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J52" s="8">
         <f>SUM(January:December!J52)</f>
-        <v>571</v>
+        <v>596</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -8079,15 +8079,15 @@
       </c>
       <c r="B53" s="10">
         <f>SUM(January:December!B53)</f>
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="C53" s="10">
         <f>SUM(January:December!C53)</f>
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D53" s="10">
         <f>SUM(January:December!D53)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E53" s="10">
         <f>SUM(January:December!E53)</f>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="G53" s="10">
         <f>SUM(January:December!G53)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H53" s="10">
         <f>SUM(January:December!H53)</f>
@@ -8107,11 +8107,11 @@
       </c>
       <c r="I53" s="10">
         <f>SUM(January:December!I53)</f>
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="J53" s="11">
         <f>SUM(January:December!J53)</f>
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -8120,27 +8120,27 @@
       </c>
       <c r="B54" s="7">
         <f>SUM(January:December!B54)</f>
-        <v>4316</v>
+        <v>4914</v>
       </c>
       <c r="C54" s="7">
         <f>SUM(January:December!C54)</f>
-        <v>2070</v>
+        <v>2357</v>
       </c>
       <c r="D54" s="7">
         <f>SUM(January:December!D54)</f>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(January:December!E54)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="7">
         <f>SUM(January:December!F54)</f>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G54" s="7">
         <f>SUM(January:December!G54)</f>
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="H54" s="7">
         <f>SUM(January:December!H54)</f>
@@ -8148,11 +8148,11 @@
       </c>
       <c r="I54" s="7">
         <f>SUM(January:December!I54)</f>
-        <v>1372</v>
+        <v>1542</v>
       </c>
       <c r="J54" s="8">
         <f>SUM(January:December!J54)</f>
-        <v>2944</v>
+        <v>3372</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -8161,39 +8161,39 @@
       </c>
       <c r="B55" s="31">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>3819</v>
+        <v>4271</v>
       </c>
       <c r="C55" s="31">
         <f t="shared" ref="C55:J55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>1772</v>
+        <v>2025</v>
       </c>
       <c r="D55" s="31">
         <f t="shared" si="0"/>
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E55" s="31">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F55" s="31">
         <f t="shared" si="0"/>
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="G55" s="31">
         <f t="shared" si="0"/>
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="H55" s="31">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I55" s="31">
         <f t="shared" si="0"/>
-        <v>1827</v>
+        <v>2029</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>1992</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -8243,39 +8243,39 @@
       </c>
       <c r="B57" s="25">
         <f>SUM(B2:B54)</f>
-        <v>212966</v>
+        <v>247202</v>
       </c>
       <c r="C57" s="25">
         <f t="shared" ref="C57:J57" si="2">SUM(C2:C54)</f>
-        <v>90810</v>
+        <v>105826</v>
       </c>
       <c r="D57" s="25">
         <f t="shared" si="2"/>
-        <v>10788</v>
+        <v>12564</v>
       </c>
       <c r="E57" s="25">
         <f t="shared" si="2"/>
-        <v>808</v>
+        <v>939</v>
       </c>
       <c r="F57" s="25">
         <f t="shared" si="2"/>
-        <v>5563</v>
+        <v>6641</v>
       </c>
       <c r="G57" s="25">
         <f t="shared" si="2"/>
-        <v>17159</v>
+        <v>20144</v>
       </c>
       <c r="H57" s="25">
         <f t="shared" si="2"/>
-        <v>617</v>
+        <v>946</v>
       </c>
       <c r="I57" s="25">
         <f t="shared" si="2"/>
-        <v>50653</v>
+        <v>58829</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="2"/>
-        <v>162313</v>
+        <v>188373</v>
       </c>
     </row>
   </sheetData>
@@ -17665,743 +17665,1697 @@
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
+      <c r="B2" s="4">
+        <v>2802</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1346</v>
+      </c>
+      <c r="D2" s="4">
+        <v>92</v>
+      </c>
+      <c r="E2" s="4">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4">
+        <v>39</v>
+      </c>
+      <c r="G2" s="4">
+        <v>139</v>
+      </c>
+      <c r="H2" s="4">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
+        <v>412</v>
+      </c>
+      <c r="J2" s="5">
+        <v>2390</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
+      <c r="B3" s="7">
+        <v>1302</v>
+      </c>
+      <c r="C3" s="7">
+        <v>696</v>
+      </c>
+      <c r="D3" s="7">
+        <v>71</v>
+      </c>
+      <c r="E3" s="7">
+        <v>5</v>
+      </c>
+      <c r="F3" s="7">
+        <v>28</v>
+      </c>
+      <c r="G3" s="7">
+        <v>104</v>
+      </c>
+      <c r="H3" s="7">
+        <v>4</v>
+      </c>
+      <c r="I3" s="7">
+        <v>226</v>
+      </c>
+      <c r="J3" s="8">
+        <v>1076</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
+      <c r="B4" s="10">
+        <v>2960</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1235</v>
+      </c>
+      <c r="D4" s="10">
+        <v>161</v>
+      </c>
+      <c r="E4" s="10">
+        <v>9</v>
+      </c>
+      <c r="F4" s="10">
+        <v>96</v>
+      </c>
+      <c r="G4" s="10">
+        <v>266</v>
+      </c>
+      <c r="H4" s="10">
+        <v>3</v>
+      </c>
+      <c r="I4" s="10">
+        <v>458</v>
+      </c>
+      <c r="J4" s="11">
+        <v>2502</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
+      <c r="B5" s="7">
+        <v>20</v>
+      </c>
+      <c r="C5" s="7">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>10</v>
+      </c>
+      <c r="J5" s="8">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="11"/>
+      <c r="B6" s="10">
+        <v>2508</v>
+      </c>
+      <c r="C6" s="10">
+        <v>951</v>
+      </c>
+      <c r="D6" s="10">
+        <v>255</v>
+      </c>
+      <c r="E6" s="10">
+        <v>3</v>
+      </c>
+      <c r="F6" s="10">
+        <v>65</v>
+      </c>
+      <c r="G6" s="10">
+        <v>323</v>
+      </c>
+      <c r="H6" s="10">
+        <v>20</v>
+      </c>
+      <c r="I6" s="10">
+        <v>848</v>
+      </c>
+      <c r="J6" s="11">
+        <v>1660</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8"/>
+      <c r="B7" s="7">
+        <v>464</v>
+      </c>
+      <c r="C7" s="7">
+        <v>237</v>
+      </c>
+      <c r="D7" s="7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>142</v>
+      </c>
+      <c r="G7" s="7">
+        <v>145</v>
+      </c>
+      <c r="H7" s="7">
+        <v>140</v>
+      </c>
+      <c r="I7" s="7">
+        <v>138</v>
+      </c>
+      <c r="J7" s="8">
+        <v>326</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="11"/>
+      <c r="B8" s="10">
+        <v>370</v>
+      </c>
+      <c r="C8" s="10">
+        <v>158</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>10</v>
+      </c>
+      <c r="G8" s="10">
+        <v>11</v>
+      </c>
+      <c r="H8" s="10">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10">
+        <v>64</v>
+      </c>
+      <c r="J8" s="11">
+        <v>306</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8"/>
+      <c r="B9" s="7">
+        <v>126</v>
+      </c>
+      <c r="C9" s="7">
+        <v>55</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>4</v>
+      </c>
+      <c r="G9" s="7">
+        <v>4</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>30</v>
+      </c>
+      <c r="J9" s="8">
+        <v>96</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="11"/>
+      <c r="B10" s="10">
+        <v>0</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
+      <c r="B11" s="7">
+        <v>0</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
+      <c r="B12" s="13">
+        <v>8</v>
+      </c>
+      <c r="C12" s="13">
+        <v>8</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>6</v>
+      </c>
+      <c r="J12" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
+      <c r="B13" s="16">
+        <v>54</v>
+      </c>
+      <c r="C13" s="16">
+        <v>28</v>
+      </c>
+      <c r="D13" s="16">
+        <v>2</v>
+      </c>
+      <c r="E13" s="16">
+        <v>1</v>
+      </c>
+      <c r="F13" s="16">
+        <v>2</v>
+      </c>
+      <c r="G13" s="16">
+        <v>5</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
+        <v>24</v>
+      </c>
+      <c r="J13" s="17">
+        <v>30</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
+      <c r="B14" s="13">
+        <v>312</v>
+      </c>
+      <c r="C14" s="13">
+        <v>147</v>
+      </c>
+      <c r="D14" s="13">
+        <v>6</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13">
+        <v>15</v>
+      </c>
+      <c r="G14" s="13">
+        <v>21</v>
+      </c>
+      <c r="H14" s="13">
+        <v>8</v>
+      </c>
+      <c r="I14" s="13">
+        <v>136</v>
+      </c>
+      <c r="J14" s="14">
+        <v>176</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
+      <c r="B15" s="16">
+        <v>78</v>
+      </c>
+      <c r="C15" s="16">
+        <v>70</v>
+      </c>
+      <c r="D15" s="16">
+        <v>6</v>
+      </c>
+      <c r="E15" s="16">
+        <v>5</v>
+      </c>
+      <c r="F15" s="16">
+        <v>10</v>
+      </c>
+      <c r="G15" s="16">
+        <v>21</v>
+      </c>
+      <c r="H15" s="16">
+        <v>2</v>
+      </c>
+      <c r="I15" s="16">
+        <v>36</v>
+      </c>
+      <c r="J15" s="17">
+        <v>42</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="11"/>
+      <c r="B16" s="10">
+        <v>102</v>
+      </c>
+      <c r="C16" s="10">
+        <v>52</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
+        <v>68</v>
+      </c>
+      <c r="J16" s="11">
+        <v>34</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="8"/>
+      <c r="B17" s="7">
+        <v>1280</v>
+      </c>
+      <c r="C17" s="7">
+        <v>497</v>
+      </c>
+      <c r="D17" s="7">
+        <v>50</v>
+      </c>
+      <c r="E17" s="7">
+        <v>9</v>
+      </c>
+      <c r="F17" s="7">
+        <v>38</v>
+      </c>
+      <c r="G17" s="7">
+        <v>97</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7">
+        <v>426</v>
+      </c>
+      <c r="J17" s="8">
+        <v>854</v>
+      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="11"/>
+      <c r="B18" s="10">
+        <v>80</v>
+      </c>
+      <c r="C18" s="10">
+        <v>25</v>
+      </c>
+      <c r="D18" s="10">
+        <v>4</v>
+      </c>
+      <c r="E18" s="10">
+        <v>0</v>
+      </c>
+      <c r="F18" s="10">
+        <v>2</v>
+      </c>
+      <c r="G18" s="10">
+        <v>6</v>
+      </c>
+      <c r="H18" s="10">
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
+        <v>30</v>
+      </c>
+      <c r="J18" s="11">
+        <v>50</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
+      <c r="B19" s="7">
+        <v>714</v>
+      </c>
+      <c r="C19" s="7">
+        <v>335</v>
+      </c>
+      <c r="D19" s="7">
+        <v>28</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2</v>
+      </c>
+      <c r="F19" s="7">
+        <v>15</v>
+      </c>
+      <c r="G19" s="7">
+        <v>45</v>
+      </c>
+      <c r="H19" s="7">
+        <v>2</v>
+      </c>
+      <c r="I19" s="7">
+        <v>246</v>
+      </c>
+      <c r="J19" s="8">
+        <v>468</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="11"/>
+      <c r="B20" s="10">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10">
+        <v>0</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0</v>
+      </c>
+      <c r="F20" s="10">
+        <v>2</v>
+      </c>
+      <c r="G20" s="10">
+        <v>2</v>
+      </c>
+      <c r="H20" s="10">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10">
+        <v>0</v>
+      </c>
+      <c r="J20" s="11">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="8"/>
+      <c r="B21" s="7">
+        <v>1008</v>
+      </c>
+      <c r="C21" s="7">
+        <v>503</v>
+      </c>
+      <c r="D21" s="7">
+        <v>18</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2</v>
+      </c>
+      <c r="F21" s="7">
+        <v>14</v>
+      </c>
+      <c r="G21" s="7">
+        <v>34</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0</v>
+      </c>
+      <c r="I21" s="7">
+        <v>266</v>
+      </c>
+      <c r="J21" s="8">
+        <v>742</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="11"/>
+      <c r="B22" s="10">
+        <v>150</v>
+      </c>
+      <c r="C22" s="10">
+        <v>49</v>
+      </c>
+      <c r="D22" s="10">
+        <v>3</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1</v>
+      </c>
+      <c r="F22" s="10">
+        <v>4</v>
+      </c>
+      <c r="G22" s="10">
+        <v>8</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
+        <v>58</v>
+      </c>
+      <c r="J22" s="11">
+        <v>92</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="8"/>
+      <c r="B23" s="7">
+        <v>1312</v>
+      </c>
+      <c r="C23" s="7">
+        <v>465</v>
+      </c>
+      <c r="D23" s="7">
+        <v>147</v>
+      </c>
+      <c r="E23" s="7">
+        <v>10</v>
+      </c>
+      <c r="F23" s="7">
+        <v>28</v>
+      </c>
+      <c r="G23" s="7">
+        <v>185</v>
+      </c>
+      <c r="H23" s="7">
+        <v>3</v>
+      </c>
+      <c r="I23" s="7">
+        <v>266</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1046</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="11"/>
+      <c r="B24" s="10">
+        <v>3756</v>
+      </c>
+      <c r="C24" s="10">
+        <v>1579</v>
+      </c>
+      <c r="D24" s="10">
+        <v>247</v>
+      </c>
+      <c r="E24" s="10">
+        <v>15</v>
+      </c>
+      <c r="F24" s="10">
+        <v>92</v>
+      </c>
+      <c r="G24" s="10">
+        <v>354</v>
+      </c>
+      <c r="H24" s="10">
+        <v>3</v>
+      </c>
+      <c r="I24" s="10">
+        <v>560</v>
+      </c>
+      <c r="J24" s="11">
+        <v>3196</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="8"/>
+      <c r="B25" s="7">
+        <v>280</v>
+      </c>
+      <c r="C25" s="7">
+        <v>95</v>
+      </c>
+      <c r="D25" s="7">
+        <v>7</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1</v>
+      </c>
+      <c r="F25" s="7">
+        <v>6</v>
+      </c>
+      <c r="G25" s="7">
+        <v>14</v>
+      </c>
+      <c r="H25" s="7">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7">
+        <v>98</v>
+      </c>
+      <c r="J25" s="8">
+        <v>182</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="11"/>
+      <c r="B26" s="10">
+        <v>0</v>
+      </c>
+      <c r="C26" s="10">
+        <v>0</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10">
+        <v>0</v>
+      </c>
+      <c r="J26" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="8"/>
+      <c r="B27" s="7">
+        <v>308</v>
+      </c>
+      <c r="C27" s="7">
+        <v>160</v>
+      </c>
+      <c r="D27" s="7">
+        <v>3</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2</v>
+      </c>
+      <c r="F27" s="7">
+        <v>4</v>
+      </c>
+      <c r="G27" s="7">
+        <v>9</v>
+      </c>
+      <c r="H27" s="7">
+        <v>4</v>
+      </c>
+      <c r="I27" s="7">
+        <v>104</v>
+      </c>
+      <c r="J27" s="8">
+        <v>204</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="11"/>
+      <c r="B28" s="10">
+        <v>254</v>
+      </c>
+      <c r="C28" s="10">
+        <v>125</v>
+      </c>
+      <c r="D28" s="10">
+        <v>12</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0</v>
+      </c>
+      <c r="F28" s="10">
+        <v>7</v>
+      </c>
+      <c r="G28" s="10">
+        <v>19</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
+        <v>74</v>
+      </c>
+      <c r="J28" s="11">
+        <v>180</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="8"/>
+      <c r="B29" s="7">
+        <v>1428</v>
+      </c>
+      <c r="C29" s="7">
+        <v>622</v>
+      </c>
+      <c r="D29" s="7">
+        <v>7</v>
+      </c>
+      <c r="E29" s="7">
+        <v>4</v>
+      </c>
+      <c r="F29" s="7">
+        <v>32</v>
+      </c>
+      <c r="G29" s="7">
+        <v>43</v>
+      </c>
+      <c r="H29" s="7">
+        <v>0</v>
+      </c>
+      <c r="I29" s="7">
+        <v>322</v>
+      </c>
+      <c r="J29" s="8">
+        <v>1106</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="11"/>
+      <c r="B30" s="10">
+        <v>100</v>
+      </c>
+      <c r="C30" s="10">
+        <v>42</v>
+      </c>
+      <c r="D30" s="10">
+        <v>5</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0</v>
+      </c>
+      <c r="F30" s="10">
+        <v>2</v>
+      </c>
+      <c r="G30" s="10">
+        <v>7</v>
+      </c>
+      <c r="H30" s="10">
+        <v>2</v>
+      </c>
+      <c r="I30" s="10">
+        <v>54</v>
+      </c>
+      <c r="J30" s="11">
+        <v>46</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="8"/>
+      <c r="B31" s="7">
+        <v>41</v>
+      </c>
+      <c r="C31" s="7">
+        <v>41</v>
+      </c>
+      <c r="D31" s="7">
+        <v>4</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7">
+        <v>1</v>
+      </c>
+      <c r="G31" s="7">
+        <v>5</v>
+      </c>
+      <c r="H31" s="7">
+        <v>1</v>
+      </c>
+      <c r="I31" s="7">
+        <v>8</v>
+      </c>
+      <c r="J31" s="8">
+        <v>33</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="11"/>
+      <c r="B32" s="10">
+        <v>1078</v>
+      </c>
+      <c r="C32" s="10">
+        <v>426</v>
+      </c>
+      <c r="D32" s="10">
+        <v>68</v>
+      </c>
+      <c r="E32" s="10">
+        <v>3</v>
+      </c>
+      <c r="F32" s="10">
+        <v>63</v>
+      </c>
+      <c r="G32" s="10">
+        <v>134</v>
+      </c>
+      <c r="H32" s="10">
+        <v>31</v>
+      </c>
+      <c r="I32" s="10">
+        <v>474</v>
+      </c>
+      <c r="J32" s="11">
+        <v>604</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="8"/>
+      <c r="B33" s="7">
+        <v>790</v>
+      </c>
+      <c r="C33" s="7">
+        <v>359</v>
+      </c>
+      <c r="D33" s="7">
+        <v>9</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2</v>
+      </c>
+      <c r="F33" s="7">
+        <v>74</v>
+      </c>
+      <c r="G33" s="7">
+        <v>85</v>
+      </c>
+      <c r="H33" s="7">
+        <v>30</v>
+      </c>
+      <c r="I33" s="7">
+        <v>302</v>
+      </c>
+      <c r="J33" s="8">
+        <v>488</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="11"/>
+      <c r="B34" s="10">
+        <v>264</v>
+      </c>
+      <c r="C34" s="10">
+        <v>113</v>
+      </c>
+      <c r="D34" s="10">
+        <v>3</v>
+      </c>
+      <c r="E34" s="10">
+        <v>1</v>
+      </c>
+      <c r="F34" s="10">
+        <v>13</v>
+      </c>
+      <c r="G34" s="10">
+        <v>17</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
+        <v>138</v>
+      </c>
+      <c r="J34" s="11">
+        <v>126</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="8"/>
+      <c r="B35" s="7">
+        <v>2556</v>
+      </c>
+      <c r="C35" s="7">
+        <v>992</v>
+      </c>
+      <c r="D35" s="7">
+        <v>191</v>
+      </c>
+      <c r="E35" s="7">
+        <v>24</v>
+      </c>
+      <c r="F35" s="7">
+        <v>104</v>
+      </c>
+      <c r="G35" s="7">
+        <v>319</v>
+      </c>
+      <c r="H35" s="7">
+        <v>50</v>
+      </c>
+      <c r="I35" s="7">
+        <v>454</v>
+      </c>
+      <c r="J35" s="8">
+        <v>2102</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="11"/>
+      <c r="B36" s="10">
+        <v>266</v>
+      </c>
+      <c r="C36" s="10">
+        <v>151</v>
+      </c>
+      <c r="D36" s="10">
+        <v>4</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0</v>
+      </c>
+      <c r="F36" s="10">
+        <v>4</v>
+      </c>
+      <c r="G36" s="10">
+        <v>8</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0</v>
+      </c>
+      <c r="I36" s="10">
+        <v>112</v>
+      </c>
+      <c r="J36" s="11">
+        <v>154</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="8"/>
+      <c r="B37" s="7">
+        <v>1196</v>
+      </c>
+      <c r="C37" s="7">
+        <v>457</v>
+      </c>
+      <c r="D37" s="7">
+        <v>93</v>
+      </c>
+      <c r="E37" s="7">
+        <v>2</v>
+      </c>
+      <c r="F37" s="7">
+        <v>36</v>
+      </c>
+      <c r="G37" s="7">
+        <v>131</v>
+      </c>
+      <c r="H37" s="7">
+        <v>2</v>
+      </c>
+      <c r="I37" s="7">
+        <v>262</v>
+      </c>
+      <c r="J37" s="8">
+        <v>934</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="11"/>
+      <c r="B38" s="10">
+        <v>40</v>
+      </c>
+      <c r="C38" s="10">
+        <v>20</v>
+      </c>
+      <c r="D38" s="10">
+        <v>1</v>
+      </c>
+      <c r="E38" s="10">
+        <v>0</v>
+      </c>
+      <c r="F38" s="10">
+        <v>1</v>
+      </c>
+      <c r="G38" s="10">
+        <v>2</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0</v>
+      </c>
+      <c r="I38" s="10">
+        <v>10</v>
+      </c>
+      <c r="J38" s="11">
+        <v>30</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="8"/>
+      <c r="B39" s="7">
+        <v>208</v>
+      </c>
+      <c r="C39" s="7">
+        <v>103</v>
+      </c>
+      <c r="D39" s="7">
+        <v>26</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7">
+        <v>2</v>
+      </c>
+      <c r="G39" s="7">
+        <v>28</v>
+      </c>
+      <c r="H39" s="7">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7">
+        <v>94</v>
+      </c>
+      <c r="J39" s="8">
+        <v>114</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="20"/>
+      <c r="B40" s="19">
+        <v>0</v>
+      </c>
+      <c r="C40" s="19">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19">
+        <v>0</v>
+      </c>
+      <c r="F40" s="19">
+        <v>0</v>
+      </c>
+      <c r="G40" s="19">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19">
+        <v>0</v>
+      </c>
+      <c r="I40" s="19">
+        <v>0</v>
+      </c>
+      <c r="J40" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="23"/>
+      <c r="B41" s="22">
+        <v>0</v>
+      </c>
+      <c r="C41" s="22">
+        <v>0</v>
+      </c>
+      <c r="D41" s="22">
+        <v>0</v>
+      </c>
+      <c r="E41" s="22">
+        <v>0</v>
+      </c>
+      <c r="F41" s="22">
+        <v>0</v>
+      </c>
+      <c r="G41" s="22">
+        <v>0</v>
+      </c>
+      <c r="H41" s="22">
+        <v>0</v>
+      </c>
+      <c r="I41" s="22">
+        <v>0</v>
+      </c>
+      <c r="J41" s="23">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="20"/>
+      <c r="B42" s="19">
+        <v>0</v>
+      </c>
+      <c r="C42" s="19">
+        <v>0</v>
+      </c>
+      <c r="D42" s="19">
+        <v>0</v>
+      </c>
+      <c r="E42" s="19">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19">
+        <v>0</v>
+      </c>
+      <c r="G42" s="19">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19">
+        <v>0</v>
+      </c>
+      <c r="I42" s="19">
+        <v>0</v>
+      </c>
+      <c r="J42" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="23"/>
+      <c r="B43" s="22">
+        <v>0</v>
+      </c>
+      <c r="C43" s="22">
+        <v>0</v>
+      </c>
+      <c r="D43" s="22">
+        <v>0</v>
+      </c>
+      <c r="E43" s="22">
+        <v>0</v>
+      </c>
+      <c r="F43" s="22">
+        <v>0</v>
+      </c>
+      <c r="G43" s="22">
+        <v>0</v>
+      </c>
+      <c r="H43" s="22">
+        <v>0</v>
+      </c>
+      <c r="I43" s="22">
+        <v>0</v>
+      </c>
+      <c r="J43" s="23">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="8"/>
+      <c r="B44" s="7">
+        <v>44</v>
+      </c>
+      <c r="C44" s="7">
+        <v>47</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <v>2</v>
+      </c>
+      <c r="G44" s="7">
+        <v>2</v>
+      </c>
+      <c r="H44" s="7">
+        <v>1</v>
+      </c>
+      <c r="I44" s="7">
+        <v>16</v>
+      </c>
+      <c r="J44" s="8">
+        <v>28</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="11"/>
+      <c r="B45" s="10">
+        <v>826</v>
+      </c>
+      <c r="C45" s="10">
+        <v>414</v>
+      </c>
+      <c r="D45" s="10">
+        <v>52</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1</v>
+      </c>
+      <c r="F45" s="10">
+        <v>9</v>
+      </c>
+      <c r="G45" s="10">
+        <v>62</v>
+      </c>
+      <c r="H45" s="10">
+        <v>2</v>
+      </c>
+      <c r="I45" s="10">
+        <v>202</v>
+      </c>
+      <c r="J45" s="11">
+        <v>624</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="8"/>
+      <c r="B46" s="7">
+        <v>1142</v>
+      </c>
+      <c r="C46" s="7">
+        <v>632</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7">
+        <v>9</v>
+      </c>
+      <c r="F46" s="7">
+        <v>27</v>
+      </c>
+      <c r="G46" s="7">
+        <v>36</v>
+      </c>
+      <c r="H46" s="7">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7">
+        <v>216</v>
+      </c>
+      <c r="J46" s="8">
+        <v>926</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="11"/>
+      <c r="B47" s="10">
+        <v>364</v>
+      </c>
+      <c r="C47" s="10">
+        <v>182</v>
+      </c>
+      <c r="D47" s="10">
+        <v>7</v>
+      </c>
+      <c r="E47" s="10">
+        <v>2</v>
+      </c>
+      <c r="F47" s="10">
+        <v>12</v>
+      </c>
+      <c r="G47" s="10">
+        <v>21</v>
+      </c>
+      <c r="H47" s="10">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10">
+        <v>106</v>
+      </c>
+      <c r="J47" s="11">
+        <v>258</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="8"/>
+      <c r="B48" s="7">
+        <v>454</v>
+      </c>
+      <c r="C48" s="7">
+        <v>181</v>
+      </c>
+      <c r="D48" s="7">
+        <v>2</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7">
+        <v>7</v>
+      </c>
+      <c r="G48" s="7">
+        <v>9</v>
+      </c>
+      <c r="H48" s="7">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7">
+        <v>102</v>
+      </c>
+      <c r="J48" s="8">
+        <v>352</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="11"/>
+      <c r="B49" s="10">
+        <v>1766</v>
+      </c>
+      <c r="C49" s="10">
+        <v>770</v>
+      </c>
+      <c r="D49" s="10">
+        <v>136</v>
+      </c>
+      <c r="E49" s="10">
+        <v>6</v>
+      </c>
+      <c r="F49" s="10">
+        <v>35</v>
+      </c>
+      <c r="G49" s="10">
+        <v>177</v>
+      </c>
+      <c r="H49" s="10">
+        <v>14</v>
+      </c>
+      <c r="I49" s="10">
+        <v>304</v>
+      </c>
+      <c r="J49" s="11">
+        <v>1462</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="8"/>
+      <c r="B50" s="7">
+        <v>182</v>
+      </c>
+      <c r="C50" s="7">
+        <v>75</v>
+      </c>
+      <c r="D50" s="7">
+        <v>14</v>
+      </c>
+      <c r="E50" s="7">
+        <v>3</v>
+      </c>
+      <c r="F50" s="7">
+        <v>7</v>
+      </c>
+      <c r="G50" s="7">
+        <v>24</v>
+      </c>
+      <c r="H50" s="7">
+        <v>1</v>
+      </c>
+      <c r="I50" s="7">
+        <v>58</v>
+      </c>
+      <c r="J50" s="8">
+        <v>124</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="11"/>
+      <c r="B51" s="10">
+        <v>566</v>
+      </c>
+      <c r="C51" s="10">
+        <v>227</v>
+      </c>
+      <c r="D51" s="10">
+        <v>24</v>
+      </c>
+      <c r="E51" s="10">
+        <v>0</v>
+      </c>
+      <c r="F51" s="10">
+        <v>12</v>
+      </c>
+      <c r="G51" s="10">
+        <v>36</v>
+      </c>
+      <c r="H51" s="10">
+        <v>2</v>
+      </c>
+      <c r="I51" s="10">
+        <v>164</v>
+      </c>
+      <c r="J51" s="11">
+        <v>402</v>
+      </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="8"/>
+      <c r="B52" s="7">
+        <v>27</v>
+      </c>
+      <c r="C52" s="7">
+        <v>25</v>
+      </c>
+      <c r="D52" s="7">
+        <v>4</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>7</v>
+      </c>
+      <c r="G52" s="7">
+        <v>11</v>
+      </c>
+      <c r="H52" s="7">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7">
+        <v>2</v>
+      </c>
+      <c r="J52" s="8">
+        <v>25</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="11"/>
+      <c r="B53" s="10">
+        <v>50</v>
+      </c>
+      <c r="C53" s="10">
+        <v>21</v>
+      </c>
+      <c r="D53" s="10">
+        <v>2</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0</v>
+      </c>
+      <c r="F53" s="10">
+        <v>0</v>
+      </c>
+      <c r="G53" s="10">
+        <v>2</v>
+      </c>
+      <c r="H53" s="10">
+        <v>0</v>
+      </c>
+      <c r="I53" s="10">
+        <v>22</v>
+      </c>
+      <c r="J53" s="11">
+        <v>28</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="8"/>
+      <c r="B54" s="7">
+        <v>598</v>
+      </c>
+      <c r="C54" s="7">
+        <v>287</v>
+      </c>
+      <c r="D54" s="7">
+        <v>7</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1</v>
+      </c>
+      <c r="F54" s="7">
+        <v>5</v>
+      </c>
+      <c r="G54" s="7">
+        <v>13</v>
+      </c>
+      <c r="H54" s="7">
+        <v>0</v>
+      </c>
+      <c r="I54" s="7">
+        <v>170</v>
+      </c>
+      <c r="J54" s="8">
+        <v>428</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
@@ -18409,39 +19363,39 @@
       </c>
       <c r="B55" s="31">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="C55" s="31">
         <f t="shared" ref="C55:J55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="D55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -18491,39 +19445,39 @@
       </c>
       <c r="B57" s="25">
         <f>SUM(B2:B54)</f>
-        <v>0</v>
+        <v>34236</v>
       </c>
       <c r="C57" s="25">
         <f t="shared" ref="C57:J57" si="2">SUM(C2:C54)</f>
-        <v>0</v>
+        <v>15016</v>
       </c>
       <c r="D57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1776</v>
       </c>
       <c r="E57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="F57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1078</v>
       </c>
       <c r="G57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2985</v>
       </c>
       <c r="H57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="I57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8176</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26060</v>
       </c>
     </row>
   </sheetData>
